--- a/Evaluation_Schema.xlsx
+++ b/Evaluation_Schema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kim_W\Ekkono_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48233EF0-97AB-4778-BEF6-52A9E8CF08EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C60AF83-60FB-4E98-93CF-0DF603BDD12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="13884" windowHeight="12336" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="139">
   <si>
     <t>Metric</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>LLaVA</t>
+  </si>
+  <si>
+    <t>d?</t>
   </si>
 </sst>
 </file>
@@ -858,44 +861,50 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ECF850D-99CD-4307-BFB4-690876BCFF53}">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C1" t="s">
         <v>126</v>
       </c>
       <c r="D1" t="s">
         <v>127</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>128</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
         <v>129</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
         <v>130</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>132</v>
       </c>
       <c r="D2" t="s">
         <v>132</v>
       </c>
+      <c r="E2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F2" t="s">
+        <v>138</v>
+      </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="H2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="I2" t="s">
         <v>132</v>
@@ -903,8 +912,14 @@
       <c r="J2" t="s">
         <v>132</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="K2" t="s">
+        <v>132</v>
+      </c>
+      <c r="L2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>133</v>
       </c>
@@ -912,12 +927,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>136</v>
       </c>
@@ -925,12 +940,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>137</v>
       </c>
@@ -938,7 +953,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>134</v>
       </c>

--- a/Evaluation_Schema.xlsx
+++ b/Evaluation_Schema.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kim_W\Ekkono_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C60AF83-60FB-4E98-93CF-0DF603BDD12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78406D98-68B0-4F47-B1CC-E2485F62BA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="13884" windowHeight="12336" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
   </bookViews>
   <sheets>
-    <sheet name="Big" sheetId="3" r:id="rId1"/>
-    <sheet name="Schema #1" sheetId="1" r:id="rId2"/>
-    <sheet name="Schema #2" sheetId="2" r:id="rId3"/>
+    <sheet name="Evaluation Table" sheetId="3" r:id="rId1"/>
+    <sheet name="d88 #1" sheetId="1" r:id="rId2"/>
+    <sheet name="d131 #1" sheetId="4" r:id="rId3"/>
+    <sheet name="d88 #2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="200">
   <si>
     <t>Metric</t>
   </si>
@@ -284,15 +285,21 @@
     <t>Please explain why this anomaly occurred and what it means for the weather station's prediction model.</t>
   </si>
   <si>
-    <t>deepseek-r1:latest</t>
-  </si>
-  <si>
     <t>  "Weather Station Information": {</t>
   </si>
   <si>
     <t>    "weather_station_classification": "Partial Outlier",</t>
   </si>
   <si>
+    <t>      "terrain": "lowland",</t>
+  </si>
+  <si>
+    <t>      "tz": "UTC-5",</t>
+  </si>
+  <si>
+    <t>      "urbanization": "rural",</t>
+  </si>
+  <si>
     <t>    "trend": "stable",</t>
   </si>
   <si>
@@ -308,12 +315,24 @@
     <t>    "top_3_features_average_historical_models": {</t>
   </si>
   <si>
+    <t>    "rural": {</t>
+  </si>
+  <si>
     <t>      "outlier_score": "moderate"</t>
   </si>
   <si>
+    <t>    "UTC-5": {</t>
+  </si>
+  <si>
     <t>      "outlier_score": "no_outlier"</t>
   </si>
   <si>
+    <t>    "lowland": {</t>
+  </si>
+  <si>
+    <t>    "problem_pattern": "tag_specific",</t>
+  </si>
+  <si>
     <t>Based on the information provided in the schema and additional information that helps to provide a good answer, provide an easy to understand interpretation for why this weather station is an anomaly. </t>
   </si>
   <si>
@@ -428,29 +447,194 @@
     <t>d88</t>
   </si>
   <si>
-    <t>Mistral</t>
-  </si>
-  <si>
     <t>AM</t>
   </si>
   <si>
     <t>WS</t>
   </si>
   <si>
-    <t>Deepseek</t>
-  </si>
-  <si>
-    <t>LLaVA</t>
-  </si>
-  <si>
     <t>d?</t>
+  </si>
+  <si>
+    <t>FI</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>FI + P</t>
+  </si>
+  <si>
+    <t>gwen3.5</t>
+  </si>
+  <si>
+    <t>deepseek-v3.2</t>
+  </si>
+  <si>
+    <t>kimi-k2.5</t>
+  </si>
+  <si>
+    <t>SA</t>
+  </si>
+  <si>
+    <t>gwen3.5 | FI</t>
+  </si>
+  <si>
+    <t>gwen3.5 | P</t>
+  </si>
+  <si>
+    <t>gwen3.5 | FI + P</t>
+  </si>
+  <si>
+    <t>deepseek-v3.2 | FI</t>
+  </si>
+  <si>
+    <t>deepseek-v3.2 | P</t>
+  </si>
+  <si>
+    <t>deepseek-v3.2 | FI + P</t>
+  </si>
+  <si>
+    <t>kimi-k2.5 | FI</t>
+  </si>
+  <si>
+    <t>kimi-k2.5 | P</t>
+  </si>
+  <si>
+    <t>kimi-k2.5 | FI + P</t>
+  </si>
+  <si>
+    <t>d131</t>
+  </si>
+  <si>
+    <t>      "name": "OGOKI POST A",</t>
+  </si>
+  <si>
+    <t>      "country": "Canada",</t>
+  </si>
+  <si>
+    <t>      "station_id": "CAN06075786",</t>
+  </si>
+  <si>
+    <t>      "city": "Greenstone",</t>
+  </si>
+  <si>
+    <t>      "state": "Ontario"</t>
+  </si>
+  <si>
+    <t>    "version": 8,</t>
+  </si>
+  <si>
+    <t>    "model_age_days": 1547,</t>
+  </si>
+  <si>
+    <t>    "training_recency_bucket": "outdated"</t>
+  </si>
+  <si>
+    <t>      "MAE": 16.670150637626648,</t>
+  </si>
+  <si>
+    <t>      "RMSE": 4.384457421302796,</t>
+  </si>
+  <si>
+    <t>      "MAPE": 17.724907338619232</t>
+  </si>
+  <si>
+    <t>    "overall_error_score": 12.977009995000667,</t>
+  </si>
+  <si>
+    <t>    "worst_performance_error_score": 8.035996518007464,</t>
+  </si>
+  <si>
+    <t>    "worst_time_stamp": "2025-01-30 11:10:05"</t>
+  </si>
+  <si>
+    <t>    "versions_available": 7,</t>
+  </si>
+  <si>
+    <t>      "MAE": 9.934088706970215,</t>
+  </si>
+  <si>
+    <t>      "MAPE": 11.332808494567871,</t>
+  </si>
+  <si>
+    <t>      "temperature": 1.1146011545138748,</t>
+  </si>
+  <si>
+    <t>      "temperature-yesterday": 0.4962712226487427,</t>
+  </si>
+  <si>
+    <t>      "wind_direction-yesterday": 0.40130767566484826</t>
+  </si>
+  <si>
+    <t>      "temperature": 1.02739787517374,</t>
+  </si>
+  <si>
+    <t>      "temperature-yesterday": 0.4735450398292181,</t>
+  </si>
+  <si>
+    <t>      "wind_direction-yesterday": 0.39752670587760425</t>
+  </si>
+  <si>
+    <t>    "Ontario": {</t>
+  </si>
+  <si>
+    <t>      "performance": 17.98217862877089,</t>
+  </si>
+  <si>
+    <t>      "outlier_score_value": -1.366132667701791,</t>
+  </si>
+  <si>
+    <t>      "performance": 7.640220805374328,</t>
+  </si>
+  <si>
+    <t>      "outlier_score_value": -1.0190773503365347,</t>
+  </si>
+  <si>
+    <t>      "performance": 7.53930731207449,</t>
+  </si>
+  <si>
+    <t>      "outlier_score_value": -1.0337059444528445,</t>
+  </si>
+  <si>
+    <t>      "performance": 7.3411128988871,</t>
+  </si>
+  <si>
+    <t>      "outlier_score_value": -1.0640332777780408,</t>
+  </si>
+  <si>
+    <t>      "performance": 6.598249308290366,</t>
+  </si>
+  <si>
+    <t>      "outlier_score_value": -1.0575524354781733,</t>
+  </si>
+  <si>
+    <t>    "Canada": {</t>
+  </si>
+  <si>
+    <t>      "performance": 4.863609290113009,</t>
+  </si>
+  <si>
+    <t>      "outlier_score_value": -1.2802194401780667,</t>
+  </si>
+  <si>
+    <t>      "Ontario"</t>
+  </si>
+  <si>
+    <t>    "worst_performance_tag": "Ontario",</t>
+  </si>
+  <si>
+    <t>    "worst_outlier_tag": "Ontario",</t>
+  </si>
+  <si>
+    <t>    "extreme_outlier_ratio": 0.0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -493,8 +677,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -504,6 +696,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -532,7 +736,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -546,6 +750,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -861,104 +1074,770 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ECF850D-99CD-4307-BFB4-690876BCFF53}">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:AA37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
+    <col min="5" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C1" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1" t="s">
-        <v>127</v>
-      </c>
-      <c r="I1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J1" t="s">
-        <v>129</v>
-      </c>
-      <c r="K1" t="s">
-        <v>130</v>
-      </c>
-      <c r="L1" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="C2" t="s">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D1" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="D2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="E1" s="13"/>
+      <c r="F1" s="13" t="s">
+        <v>133</v>
+      </c>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13" t="s">
+        <v>134</v>
+      </c>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="D2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="K2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="L2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="M2" s="12" t="s">
         <v>138</v>
       </c>
-      <c r="I2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J2" t="s">
-        <v>132</v>
-      </c>
-      <c r="K2" t="s">
-        <v>132</v>
-      </c>
-      <c r="L2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>133</v>
+      <c r="N2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="O2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="P2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="R2" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="S2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="T2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="U2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="V2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="W2" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="X2" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z2" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA2" s="12" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>145</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>136</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>137</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>134</v>
+        <v>140</v>
+      </c>
+      <c r="C3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10"/>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C5" t="s">
+        <v>144</v>
+      </c>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+      <c r="Q5" s="10"/>
+      <c r="R5" s="10"/>
+      <c r="S5" s="10"/>
+      <c r="T5" s="10"/>
+      <c r="U5" s="10"/>
+      <c r="V5" s="10"/>
+      <c r="W5" s="10"/>
+      <c r="X5" s="10"/>
+      <c r="Y5" s="10"/>
+      <c r="Z5" s="10"/>
+      <c r="AA5" s="10"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B6" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+      <c r="J6" s="11"/>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+      <c r="Q6" s="11"/>
+      <c r="R6" s="11"/>
+      <c r="S6" s="11"/>
+      <c r="T6" s="11"/>
+      <c r="U6" s="11"/>
+      <c r="V6" s="11"/>
+      <c r="W6" s="11"/>
+      <c r="X6" s="11"/>
+      <c r="Y6" s="11"/>
+      <c r="Z6" s="11"/>
+      <c r="AA6" s="11"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
+      <c r="J7" s="11"/>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
+      <c r="N7" s="11"/>
+      <c r="O7" s="11"/>
+      <c r="P7" s="11"/>
+      <c r="Q7" s="11"/>
+      <c r="R7" s="11"/>
+      <c r="S7" s="11"/>
+      <c r="T7" s="11"/>
+      <c r="U7" s="11"/>
+      <c r="V7" s="11"/>
+      <c r="W7" s="11"/>
+      <c r="X7" s="11"/>
+      <c r="Y7" s="11"/>
+      <c r="Z7" s="11"/>
+      <c r="AA7" s="11"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C8" t="s">
+        <v>144</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="11"/>
+      <c r="J8" s="11"/>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
+      <c r="N8" s="11"/>
+      <c r="O8" s="11"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="11"/>
+      <c r="R8" s="11"/>
+      <c r="S8" s="11"/>
+      <c r="T8" s="11"/>
+      <c r="U8" s="11"/>
+      <c r="V8" s="11"/>
+      <c r="W8" s="11"/>
+      <c r="X8" s="11"/>
+      <c r="Y8" s="11"/>
+      <c r="Z8" s="11"/>
+      <c r="AA8" s="11"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="10"/>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="10"/>
+      <c r="AA12" s="10"/>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>143</v>
+      </c>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
+      <c r="P13" s="10"/>
+      <c r="Q13" s="10"/>
+      <c r="R13" s="10"/>
+      <c r="S13" s="10"/>
+      <c r="T13" s="10"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="10"/>
+      <c r="W13" s="10"/>
+      <c r="X13" s="10"/>
+      <c r="Y13" s="10"/>
+      <c r="Z13" s="10"/>
+      <c r="AA13" s="10"/>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C14" t="s">
+        <v>144</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="10"/>
+      <c r="T14" s="10"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="10"/>
+      <c r="W14" s="10"/>
+      <c r="X14" s="10"/>
+      <c r="Y14" s="10"/>
+      <c r="Z14" s="10"/>
+      <c r="AA14" s="10"/>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B15" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="11"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
+      <c r="K15" s="11"/>
+      <c r="L15" s="11"/>
+      <c r="M15" s="11"/>
+      <c r="N15" s="11"/>
+      <c r="O15" s="11"/>
+      <c r="P15" s="11"/>
+      <c r="Q15" s="11"/>
+      <c r="R15" s="11"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="11"/>
+      <c r="U15" s="11"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="11"/>
+      <c r="X15" s="11"/>
+      <c r="Y15" s="11"/>
+      <c r="Z15" s="11"/>
+      <c r="AA15" s="11"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="11"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="11"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
+      <c r="K17" s="11"/>
+      <c r="L17" s="11"/>
+      <c r="M17" s="11"/>
+      <c r="N17" s="11"/>
+      <c r="O17" s="11"/>
+      <c r="P17" s="11"/>
+      <c r="Q17" s="11"/>
+      <c r="R17" s="11"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="11"/>
+      <c r="U17" s="11"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="11"/>
+      <c r="X17" s="11"/>
+      <c r="Y17" s="11"/>
+      <c r="Z17" s="11"/>
+      <c r="AA17" s="11"/>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" t="s">
+        <v>142</v>
+      </c>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
+      <c r="P21" s="10"/>
+      <c r="Q21" s="10"/>
+      <c r="R21" s="10"/>
+      <c r="S21" s="10"/>
+      <c r="T21" s="10"/>
+      <c r="U21" s="10"/>
+      <c r="V21" s="10"/>
+      <c r="W21" s="10"/>
+      <c r="X21" s="10"/>
+      <c r="Y21" s="10"/>
+      <c r="Z21" s="10"/>
+      <c r="AA21" s="10"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C22" t="s">
+        <v>143</v>
+      </c>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
+      <c r="S22" s="10"/>
+      <c r="T22" s="10"/>
+      <c r="U22" s="10"/>
+      <c r="V22" s="10"/>
+      <c r="W22" s="10"/>
+      <c r="X22" s="10"/>
+      <c r="Y22" s="10"/>
+      <c r="Z22" s="10"/>
+      <c r="AA22" s="10"/>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
+      <c r="P23" s="10"/>
+      <c r="Q23" s="10"/>
+      <c r="R23" s="10"/>
+      <c r="S23" s="10"/>
+      <c r="T23" s="10"/>
+      <c r="U23" s="10"/>
+      <c r="V23" s="10"/>
+      <c r="W23" s="10"/>
+      <c r="X23" s="10"/>
+      <c r="Y23" s="10"/>
+      <c r="Z23" s="10"/>
+      <c r="AA23" s="10"/>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B24" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="C24" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
+      <c r="H24" s="11"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="11"/>
+      <c r="K24" s="11"/>
+      <c r="L24" s="11"/>
+      <c r="M24" s="11"/>
+      <c r="N24" s="11"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="11"/>
+      <c r="Q24" s="11"/>
+      <c r="R24" s="11"/>
+      <c r="S24" s="11"/>
+      <c r="T24" s="11"/>
+      <c r="U24" s="11"/>
+      <c r="V24" s="11"/>
+      <c r="W24" s="11"/>
+      <c r="X24" s="11"/>
+      <c r="Y24" s="11"/>
+      <c r="Z24" s="11"/>
+      <c r="AA24" s="11"/>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
+      <c r="H25" s="11"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="11"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="11"/>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
+      <c r="H26" s="11"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="11"/>
+      <c r="L26" s="11"/>
+      <c r="M26" s="11"/>
+      <c r="N26" s="11"/>
+      <c r="O26" s="11"/>
+      <c r="P26" s="11"/>
+      <c r="Q26" s="11"/>
+      <c r="R26" s="11"/>
+      <c r="S26" s="11"/>
+      <c r="T26" s="11"/>
+      <c r="U26" s="11"/>
+      <c r="V26" s="11"/>
+      <c r="W26" s="11"/>
+      <c r="X26" s="11"/>
+      <c r="Y26" s="11"/>
+      <c r="Z26" s="11"/>
+      <c r="AA26" s="11"/>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="C29" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="M1:Q1"/>
+    <mergeCell ref="R1:V1"/>
+    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="D1:E1"/>
+  </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -966,7 +1845,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2280AAA2-2247-4D64-B955-D76F2C3D2B75}">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="59.44140625" bestFit="1" customWidth="1"/>
@@ -976,23 +1855,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>85</v>
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="5">
+        <f>B5*1 + B6*1 +B7*1+B8*1+B9*1+B10*1+B11*1+B12*1+B13*1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1002,35 +1873,24 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <f>C3*B3</f>
-        <v>0.2</v>
+        <v>149</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D10" si="0">C4*B4</f>
-        <v>0</v>
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="G4" s="7" t="s">
         <v>8</v>
@@ -1038,17 +1898,17 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B5" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
+        <f>C5*B5</f>
+        <v>0.2</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>9</v>
@@ -1056,41 +1916,41 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D6:D12" si="0">C6*B6</f>
         <v>0</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B8" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1105,10 +1965,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B9" s="3">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1123,17 +1983,17 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B10" s="3">
         <v>0.1</v>
       </c>
       <c r="C10">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>12</v>
@@ -1141,7 +2001,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
@@ -1150,491 +2010,1662 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <f>C11*B11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="4">
-        <f>SUM(B3:B11)</f>
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
-        <f>SUM(D3:D11)</f>
-        <v>0.35000000000000003</v>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f>C13*B13</f>
+        <v>0</v>
+      </c>
       <c r="G13" s="7" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="4">
+        <f>SUM(B5:B13)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>SUM(D5:D13)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G14" s="7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="5">
-        <f>B3*1 + B4*1 +B5*1+B6*1+B7*1+B8*1+B9*1+B10*1+B11*1</f>
-        <v>1</v>
-      </c>
+    <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>150</v>
+      </c>
       <c r="G16" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G17" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <f>C18*B18</f>
+        <v>0.2</v>
+      </c>
       <c r="G18" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ref="D19:D25" si="1">C19*B19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
       <c r="G20" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="G21" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="G22" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="G23" s="7" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="G24" s="7" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C25">
+        <v>0.5</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
       <c r="G25" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f>C26*B26</f>
+        <v>0</v>
+      </c>
       <c r="G26" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="27" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="4">
+        <f>SUM(B18:B26)</f>
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <f>SUM(D18:D26)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G27" s="7" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="28" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G28" s="7" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="29" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>151</v>
+      </c>
       <c r="G29" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G30" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <f>C31*B31</f>
+        <v>0.2</v>
+      </c>
       <c r="G31" s="7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <f t="shared" ref="D32:D38" si="2">C32*B32</f>
+        <v>0</v>
+      </c>
       <c r="G32" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
       <c r="G33" s="7" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G34" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G35" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G36" s="7" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G37" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C38">
+        <v>0.5</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
       <c r="G38" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="39" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f>C39*B39</f>
+        <v>0</v>
+      </c>
       <c r="G39" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="40" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="4">
+        <f>SUM(B31:B39)</f>
+        <v>1</v>
+      </c>
+      <c r="D40" s="6">
+        <f>SUM(D31:D39)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G40" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="42" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>152</v>
+      </c>
       <c r="G42" s="7" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G43" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <f>C44*B44</f>
+        <v>0.2</v>
+      </c>
       <c r="G44" s="7" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="45" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <f t="shared" ref="D45:D51" si="3">C45*B45</f>
+        <v>0</v>
+      </c>
       <c r="G45" s="7" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
       <c r="G46" s="7" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="G47" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="G48" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="G49" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="50" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="G50" s="7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="51" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C51">
+        <v>0.5</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="3"/>
+        <v>0.05</v>
+      </c>
       <c r="G51" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="52" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <f>C52*B52</f>
+        <v>0</v>
+      </c>
       <c r="G52" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="4">
+        <f>SUM(B44:B52)</f>
+        <v>1</v>
+      </c>
+      <c r="D53" s="6">
+        <f>SUM(D44:D52)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G53" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="54" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="55" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>153</v>
+      </c>
       <c r="G55" s="7" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="56" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G56" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="57" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <f>C57*B57</f>
+        <v>0.2</v>
+      </c>
       <c r="G57" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="58" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <f t="shared" ref="D58:D64" si="4">C58*B58</f>
+        <v>0</v>
+      </c>
       <c r="G58" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
       <c r="G59" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G60" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="61" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G61" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="62" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G62" s="7" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="63" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G63" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="64" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C64">
+        <v>0.5</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="4"/>
+        <v>0.05</v>
+      </c>
       <c r="G64" s="7" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="65" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <f>C65*B65</f>
+        <v>0</v>
+      </c>
       <c r="G65" s="7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="66" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="4">
+        <f>SUM(B57:B65)</f>
+        <v>1</v>
+      </c>
+      <c r="D66" s="6">
+        <f>SUM(D57:D65)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G66" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="67" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="68" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>154</v>
+      </c>
       <c r="G68" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G69" s="7" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <f>C70*B70</f>
+        <v>0.2</v>
+      </c>
       <c r="G70" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>124</v>
+      </c>
+      <c r="B71" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <f t="shared" ref="D71:D77" si="5">C71*B71</f>
+        <v>0</v>
+      </c>
       <c r="G71" s="7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="72" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="5"/>
+        <v>0.1</v>
+      </c>
       <c r="G72" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="73" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="G73" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="74" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="G74" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="75" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="G75" s="7" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="76" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="G76" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="77" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C77">
+        <v>0.5</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
       <c r="G77" s="7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <f>C78*B78</f>
+        <v>0</v>
+      </c>
       <c r="G78" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="79" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="4">
+        <f>SUM(B70:B78)</f>
+        <v>1</v>
+      </c>
+      <c r="D79" s="6">
+        <f>SUM(D70:D78)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G79" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="80" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G80" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="81" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>155</v>
+      </c>
       <c r="G81" s="7" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G82" s="7" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="83" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <f>C83*B83</f>
+        <v>0.2</v>
+      </c>
       <c r="G83" s="7" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="84" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ref="D84:D90" si="6">C84*B84</f>
+        <v>0</v>
+      </c>
       <c r="G84" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>125</v>
+      </c>
+      <c r="B85" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="6"/>
+        <v>0.1</v>
+      </c>
       <c r="G85" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="86" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="G86" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="87" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>130</v>
+      </c>
+      <c r="B87" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="G87" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="88" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>129</v>
+      </c>
+      <c r="B88" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="G88" s="7" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="89" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="G89" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="90" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>127</v>
+      </c>
+      <c r="B90" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C90">
+        <v>0.5</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="6"/>
+        <v>0.05</v>
+      </c>
       <c r="G90" s="7" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="91" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <f>C91*B91</f>
+        <v>0</v>
+      </c>
       <c r="G91" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="4">
+        <f>SUM(B83:B91)</f>
+        <v>1</v>
+      </c>
+      <c r="D92" s="6">
+        <f>SUM(D83:D91)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G92" s="7" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="93" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G93" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="94" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>156</v>
+      </c>
       <c r="G94" s="7" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="95" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G95" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="96" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>123</v>
+      </c>
+      <c r="B96" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <f>C96*B96</f>
+        <v>0.2</v>
+      </c>
       <c r="G96" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="97" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <f t="shared" ref="D97:D103" si="7">C97*B97</f>
+        <v>0</v>
+      </c>
       <c r="G97" s="7" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>125</v>
+      </c>
+      <c r="B98" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="7"/>
+        <v>0.1</v>
+      </c>
       <c r="G98" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="99" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>131</v>
+      </c>
+      <c r="B99" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="G99" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="100" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>130</v>
+      </c>
+      <c r="B100" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="G100" s="7" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="101" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>129</v>
+      </c>
+      <c r="B101" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="G101" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="102" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
       <c r="G102" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="104" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>127</v>
+      </c>
+      <c r="B103" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C103">
+        <v>0.5</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="7"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>126</v>
+      </c>
+      <c r="B104" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <f>C104*B104</f>
+        <v>0</v>
+      </c>
       <c r="G104" s="7" t="s">
         <v>84</v>
       </c>
     </row>
+    <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="4">
+        <f>SUM(B96:B104)</f>
+        <v>1</v>
+      </c>
+      <c r="D105" s="6">
+        <f>SUM(D96:D104)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>123</v>
+      </c>
+      <c r="B109" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <f>C109*B109</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>124</v>
+      </c>
+      <c r="B110" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <f t="shared" ref="D110:D116" si="8">C110*B110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>125</v>
+      </c>
+      <c r="B111" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="8"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+      <c r="B113" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>129</v>
+      </c>
+      <c r="B114" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>128</v>
+      </c>
+      <c r="B115" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>127</v>
+      </c>
+      <c r="B116" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C116">
+        <v>0.5</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="8"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <f>C117*B117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="4">
+        <f>SUM(B109:B117)</f>
+        <v>1</v>
+      </c>
+      <c r="D118" s="6">
+        <f>SUM(D109:D117)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72F4B99-410F-4CA4-B693-39F19F503C7B}">
-  <dimension ref="A1:G82"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BDBC0AD-197E-4D10-AF87-015CB58E32B7}">
+  <dimension ref="A1:G119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="59.44140625" bestFit="1" customWidth="1"/>
@@ -1644,96 +3675,1915 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>85</v>
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="5">
+        <f>B5*1 + B6*1 +B7*1+B8*1+B9*1+B10*1+B11*1+B12*1+B13*1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>105</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>117</v>
-      </c>
-      <c r="B3" s="3">
+        <v>149</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="3">
         <v>0.2</v>
       </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <f>C3*B3</f>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <f>C5*B5</f>
         <v>0.2</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D12" si="0">C6*B6</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f>C13*B13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="4">
+        <f>SUM(B5:B13)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>SUM(D5:D13)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G15" s="7" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <f>C18*B18</f>
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ref="D19:D25" si="1">C19*B19</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C25">
+        <v>0.5</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f>C26*B26</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="4">
+        <f>SUM(B18:B26)</f>
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <f>SUM(D18:D26)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G28" s="7" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <f>C31*B31</f>
+        <v>0.2</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <f t="shared" ref="D32:D38" si="2">C32*B32</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C38">
+        <v>0.5</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f>C39*B39</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="4">
+        <f>SUM(B31:B39)</f>
+        <v>1</v>
+      </c>
+      <c r="D40" s="6">
+        <f>SUM(D31:D39)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G41" s="7" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <f>C44*B44</f>
+        <v>0.2</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <f t="shared" ref="D45:D51" si="3">C45*B45</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C51">
+        <v>0.5</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="3"/>
+        <v>0.05</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <f>C52*B52</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="4">
+        <f>SUM(B44:B52)</f>
+        <v>1</v>
+      </c>
+      <c r="D53" s="6">
+        <f>SUM(D44:D52)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G54" s="7" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>153</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <f>C57*B57</f>
+        <v>0.2</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <f t="shared" ref="D58:D64" si="4">C58*B58</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C64">
+        <v>0.5</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="4"/>
+        <v>0.05</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <f>C65*B65</f>
+        <v>0</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="4">
+        <f>SUM(B57:B65)</f>
+        <v>1</v>
+      </c>
+      <c r="D66" s="6">
+        <f>SUM(D57:D65)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="7" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>154</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <f>C70*B70</f>
+        <v>0.2</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>124</v>
+      </c>
+      <c r="B71" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <f t="shared" ref="D71:D77" si="5">C71*B71</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="5"/>
+        <v>0.1</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G73" s="7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G75" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C77">
+        <v>0.5</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <f>C78*B78</f>
+        <v>0</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="4">
+        <f>SUM(B70:B78)</f>
+        <v>1</v>
+      </c>
+      <c r="D79" s="6">
+        <f>SUM(D70:D78)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G79" s="7" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G80" s="7" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>155</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <f>C83*B83</f>
+        <v>0.2</v>
+      </c>
+      <c r="G83" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ref="D84:D90" si="6">C84*B84</f>
+        <v>0</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>125</v>
+      </c>
+      <c r="B85" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="6"/>
+        <v>0.1</v>
+      </c>
+      <c r="G85" s="7" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G86" s="7" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>130</v>
+      </c>
+      <c r="B87" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>129</v>
+      </c>
+      <c r="B88" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G88" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G89" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>127</v>
+      </c>
+      <c r="B90" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C90">
+        <v>0.5</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="6"/>
+        <v>0.05</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <f>C91*B91</f>
+        <v>0</v>
+      </c>
+      <c r="G91" s="7" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="4">
+        <f>SUM(B83:B91)</f>
+        <v>1</v>
+      </c>
+      <c r="D92" s="6">
+        <f>SUM(D83:D91)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G92" s="7" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G93" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>156</v>
+      </c>
+      <c r="G94" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G95" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>123</v>
+      </c>
+      <c r="B96" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <f>C96*B96</f>
+        <v>0.2</v>
+      </c>
+      <c r="G96" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <f t="shared" ref="D97:D103" si="7">C97*B97</f>
+        <v>0</v>
+      </c>
+      <c r="G97" s="7" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>125</v>
+      </c>
+      <c r="B98" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="7"/>
+        <v>0.1</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>131</v>
+      </c>
+      <c r="B99" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G99" s="7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>130</v>
+      </c>
+      <c r="B100" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G100" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>129</v>
+      </c>
+      <c r="B101" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G101" s="7" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="G102" s="7" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>127</v>
+      </c>
+      <c r="B103" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C103">
+        <v>0.5</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="7"/>
+        <v>0.05</v>
+      </c>
+      <c r="G103" s="7" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>126</v>
+      </c>
+      <c r="B104" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <f>C104*B104</f>
+        <v>0</v>
+      </c>
+      <c r="G104" s="7" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="4">
+        <f>SUM(B96:B104)</f>
+        <v>1</v>
+      </c>
+      <c r="D105" s="6">
+        <f>SUM(D96:D104)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G105" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G106" s="7" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G108" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>123</v>
+      </c>
+      <c r="B109" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <f>C109*B109</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>124</v>
+      </c>
+      <c r="B110" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <f t="shared" ref="D110:D116" si="8">C110*B110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>125</v>
+      </c>
+      <c r="B111" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="8"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+      <c r="B113" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>129</v>
+      </c>
+      <c r="B114" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>128</v>
+      </c>
+      <c r="B115" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>127</v>
+      </c>
+      <c r="B116" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C116">
+        <v>0.5</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="8"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <f>C117*B117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="4">
+        <f>SUM(B109:B117)</f>
+        <v>1</v>
+      </c>
+      <c r="D118" s="6">
+        <f>SUM(D109:D117)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B72F4B99-410F-4CA4-B693-39F19F503C7B}">
+  <dimension ref="A1:G119"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="59.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="5">
+        <f>B5*1 + B6*1 +B7*1+B8*1+B9*1+B10*1+B11*1+B12*1+B13*1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>149</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>118</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="C4">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <f t="shared" ref="D4:D10" si="0">C4*B4</f>
-        <v>0</v>
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B5" s="3">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
       <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0.1</v>
+        <f>C5*B5</f>
+        <v>0.2</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B6" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D6:D12" si="0">C6*B6</f>
         <v>0</v>
       </c>
       <c r="G6" s="7" t="s">
@@ -1742,17 +5592,17 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7" s="3">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>14</v>
@@ -1760,10 +5610,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B8" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1778,17 +5628,17 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B9" s="3">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="C9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>16</v>
@@ -1796,17 +5646,17 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B10" s="3">
         <v>0.1</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>17</v>
@@ -1814,7 +5664,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
@@ -1823,357 +5673,1575 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <f>C11*B11</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="4">
-        <f>SUM(B3:B11)</f>
-        <v>1</v>
-      </c>
-      <c r="D12" s="6">
-        <f>SUM(D3:D11)</f>
-        <v>0.45000000000000007</v>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f>C13*B13</f>
+        <v>0</v>
+      </c>
       <c r="G13" s="7" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="4">
+        <f>SUM(B5:B13)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>SUM(D5:D13)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G14" s="7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="5">
-        <f>B3*1 + B4*1 +B5*1+B6*1+B7*1+B8*1+B9*1+B10*1+B11*1</f>
-        <v>1</v>
-      </c>
+    <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>150</v>
+      </c>
       <c r="G16" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G17" s="7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="18" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <f>C18*B18</f>
+        <v>0.2</v>
+      </c>
       <c r="G18" s="7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="7:7" x14ac:dyDescent="0.3">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ref="D19:D25" si="1">C19*B19</f>
+        <v>0</v>
+      </c>
       <c r="G19" s="7" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="20" spans="7:7" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
       <c r="G20" s="7" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="21" spans="7:7" x14ac:dyDescent="0.3">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="G21" s="7" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="7:7" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="G22" s="7" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="23" spans="7:7" x14ac:dyDescent="0.3">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="G23" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
       <c r="G24" s="7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C25">
+        <v>0.5</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
       <c r="G25" s="7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f>C26*B26</f>
+        <v>0</v>
+      </c>
       <c r="G26" s="7" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="7:7" x14ac:dyDescent="0.3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="4">
+        <f>SUM(B18:B26)</f>
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <f>SUM(D18:D26)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G27" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="28" spans="7:7" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G28" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>151</v>
+      </c>
       <c r="G29" s="7" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="7:7" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G30" s="7" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="7:7" x14ac:dyDescent="0.3">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <f>C31*B31</f>
+        <v>0.2</v>
+      </c>
       <c r="G31" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="32" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <f t="shared" ref="D32:D38" si="2">C32*B32</f>
+        <v>0</v>
+      </c>
       <c r="G32" s="7" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
       <c r="G33" s="7" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G34" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G35" s="7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="7:7" x14ac:dyDescent="0.3">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G36" s="7" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="37" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
       <c r="G37" s="7" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="38" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C38">
+        <v>0.5</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
       <c r="G38" s="7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="39" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f>C39*B39</f>
+        <v>0</v>
+      </c>
       <c r="G39" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="4">
+        <f>SUM(B31:B39)</f>
+        <v>1</v>
+      </c>
+      <c r="D40" s="6">
+        <f>SUM(D31:D39)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G40" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>152</v>
+      </c>
       <c r="G42" s="7" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="43" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G43" s="7" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="44" spans="7:7" x14ac:dyDescent="0.3">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <f>C44*B44</f>
+        <v>0.2</v>
+      </c>
       <c r="G44" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="45" spans="7:7" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <f t="shared" ref="D45:D51" si="3">C45*B45</f>
+        <v>0</v>
+      </c>
       <c r="G45" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
       <c r="G46" s="7" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="47" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="G47" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="7:7" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="G48" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="49" spans="7:7" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="G49" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="50" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
       <c r="G50" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="51" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C51">
+        <v>0.5</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="3"/>
+        <v>0.05</v>
+      </c>
       <c r="G51" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="52" spans="7:7" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <f>C52*B52</f>
+        <v>0</v>
+      </c>
       <c r="G52" s="7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="53" spans="7:7" x14ac:dyDescent="0.3">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="4">
+        <f>SUM(B44:B52)</f>
+        <v>1</v>
+      </c>
+      <c r="D53" s="6">
+        <f>SUM(D44:D52)</f>
+        <v>0.35000000000000003</v>
+      </c>
       <c r="G53" s="7" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="54" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="55" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>153</v>
+      </c>
       <c r="G55" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="56" spans="7:7" x14ac:dyDescent="0.3">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G56" s="7" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="57" spans="7:7" x14ac:dyDescent="0.3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <f>C57*B57</f>
+        <v>0.2</v>
+      </c>
       <c r="G57" s="7" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <f t="shared" ref="D58:D64" si="4">C58*B58</f>
+        <v>0</v>
+      </c>
       <c r="G58" s="7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="59" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
       <c r="G59" s="7" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="60" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G60" s="7" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="61" spans="7:7" x14ac:dyDescent="0.3">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G61" s="7" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="62" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G62" s="7" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="63" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
       <c r="G63" s="7" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="64" spans="7:7" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C64">
+        <v>0.5</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="4"/>
+        <v>0.05</v>
+      </c>
       <c r="G64" s="7" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="65" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <f>C65*B65</f>
+        <v>0</v>
+      </c>
       <c r="G65" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="67" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="4">
+        <f>SUM(B57:B65)</f>
+        <v>1</v>
+      </c>
+      <c r="D66" s="6">
+        <f>SUM(D57:D65)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="68" spans="7:7" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>154</v>
+      </c>
       <c r="G68" s="7" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="70" spans="7:7" x14ac:dyDescent="0.3">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <f>C70*B70</f>
+        <v>0.2</v>
+      </c>
       <c r="G70" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="71" spans="7:7" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>124</v>
+      </c>
+      <c r="B71" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <f t="shared" ref="D71:D77" si="5">C71*B71</f>
+        <v>0</v>
+      </c>
       <c r="G71" s="7" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="72" spans="7:7" x14ac:dyDescent="0.3">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="5"/>
+        <v>0.1</v>
+      </c>
       <c r="G72" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="73" spans="7:7" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="G73" s="7" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="74" spans="7:7" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="G74" s="7" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="76" spans="7:7" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
       <c r="G76" s="7" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="77" spans="7:7" x14ac:dyDescent="0.3">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C77">
+        <v>0.5</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
       <c r="G77" s="7" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="78" spans="7:7" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <f>C78*B78</f>
+        <v>0</v>
+      </c>
       <c r="G78" s="7" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="80" spans="7:7" x14ac:dyDescent="0.3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="4">
+        <f>SUM(B70:B78)</f>
+        <v>1</v>
+      </c>
+      <c r="D79" s="6">
+        <f>SUM(D70:D78)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G80" s="7"/>
     </row>
-    <row r="81" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>155</v>
+      </c>
       <c r="G81" s="7"/>
     </row>
-    <row r="82" spans="7:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="G82" s="7"/>
     </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <f>C83*B83</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ref="D84:D90" si="6">C84*B84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>125</v>
+      </c>
+      <c r="B85" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="6"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>130</v>
+      </c>
+      <c r="B87" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>129</v>
+      </c>
+      <c r="B88" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>127</v>
+      </c>
+      <c r="B90" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C90">
+        <v>0.5</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="6"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <f>C91*B91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="4">
+        <f>SUM(B83:B91)</f>
+        <v>1</v>
+      </c>
+      <c r="D92" s="6">
+        <f>SUM(D83:D91)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>123</v>
+      </c>
+      <c r="B96" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <f>C96*B96</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <f t="shared" ref="D97:D103" si="7">C97*B97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>125</v>
+      </c>
+      <c r="B98" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="7"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>131</v>
+      </c>
+      <c r="B99" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>130</v>
+      </c>
+      <c r="B100" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>129</v>
+      </c>
+      <c r="B101" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>127</v>
+      </c>
+      <c r="B103" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C103">
+        <v>0.5</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="7"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>126</v>
+      </c>
+      <c r="B104" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <f>C104*B104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="4">
+        <f>SUM(B96:B104)</f>
+        <v>1</v>
+      </c>
+      <c r="D105" s="6">
+        <f>SUM(D96:D104)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>123</v>
+      </c>
+      <c r="B109" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <f>C109*B109</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>124</v>
+      </c>
+      <c r="B110" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <f t="shared" ref="D110:D116" si="8">C110*B110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>125</v>
+      </c>
+      <c r="B111" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="8"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+      <c r="B113" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>129</v>
+      </c>
+      <c r="B114" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>128</v>
+      </c>
+      <c r="B115" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>127</v>
+      </c>
+      <c r="B116" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C116">
+        <v>0.5</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="8"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <f>C117*B117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="4">
+        <f>SUM(B109:B117)</f>
+        <v>1</v>
+      </c>
+      <c r="D118" s="6">
+        <f>SUM(D109:D117)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Evaluation_Schema.xlsx
+++ b/Evaluation_Schema.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kim_W\Ekkono_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78406D98-68B0-4F47-B1CC-E2485F62BA1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363D961A-C6AB-41B3-9225-B858B2870615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation Table" sheetId="3" r:id="rId1"/>
     <sheet name="d88 #1" sheetId="1" r:id="rId2"/>
     <sheet name="d131 #1" sheetId="4" r:id="rId3"/>
     <sheet name="d88 #2" sheetId="2" r:id="rId4"/>
+    <sheet name="d131 #2" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="737" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="255">
   <si>
     <t>Metric</t>
   </si>
@@ -628,6 +629,171 @@
   </si>
   <si>
     <t>    "extreme_outlier_ratio": 0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Schema:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "Weather Station Information": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "weather_station_classification": "Underperforming",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "tags": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "terrain": "lowland",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "name": "OGOKI POST A",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "tz": "UTC-5",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "country": "Canada",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "station_id": "CAN06075786",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "urbanization": "rural",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "city": "Greenstone",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "state": "Ontario"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "Model Performance Context": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "latest_error_score": 27.577198028564453,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "trend": "stable",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "worst_time_stamp": "2023-11-15 23:00:00.000000",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "worst_value": 16.642723083496094,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "metric_used_for_worst_value": "MAPE"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "Model Version History": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "trend": "degrading",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "active_model_error_score": 27.577198028564453,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "historical_models_error_score": 24.133050101143972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "Feature Importance": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "top_3_features_active_model": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "temperature": 1.1146011545138748,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "temperature-yesterday": 0.4962712226487427,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "wind_direction-yesterday": 0.40130767566484826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    },</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "top_3_features_average_historical_models": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "temperature": 1.02739787517374,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "temperature-yesterday": 0.4735450398292181,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "wind_direction-yesterday": 0.39752670587760425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "Tag Diagnostics": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "lowland": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "error_score": 27.19187355041504,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "outlier_score": "no_outlier"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "rural": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "error_score": 24.56330680847168,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "UTC-5": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "error_score": 23.5322208404541,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "Ontario": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "error_score": 13.072118759155273,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "Canada": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      "error_score": 11.482319831848145,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  "Cross Tag Context": {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "worst_performance_tag": "lowland",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "worst_outlier_tag": "Ontario",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "problem_pattern": "peer_specific",</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    "outlier_ratio": 0.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on the information provided in the schema and additional information that helps to provide a good answer, provide an easy to understand interpretation for why this weather station is an anomaly. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">What does that mean for future predictions of the weather station? </t>
+  </si>
+  <si>
+    <t>* Every weather station has multiple tags that show the attributes of the device.  For each of these tags an outlier score exists that signalizes how different the weather station performance is compared to weather stations with the same tag.</t>
   </si>
 </sst>
 </file>
@@ -7245,4 +7411,1761 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{759218BE-F15E-47D5-9329-393A877DE4EB}">
+  <dimension ref="A1:G119"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="59.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="5">
+        <f>B5*1 + B6*1 +B7*1+B8*1+B9*1+B10*1+B11*1+B12*1+B13*1</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>149</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>123</v>
+      </c>
+      <c r="B5" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <f>C5*B5</f>
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" ref="D6:D12" si="0">C6*B6</f>
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B7" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+      <c r="B8" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="B10" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>128</v>
+      </c>
+      <c r="B11" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>127</v>
+      </c>
+      <c r="B12" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C12">
+        <v>0.5</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>126</v>
+      </c>
+      <c r="B13" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f>C13*B13</f>
+        <v>0</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B14" s="4">
+        <f>SUM(B5:B13)</f>
+        <v>1</v>
+      </c>
+      <c r="D14" s="6">
+        <f>SUM(D5:D13)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G15" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B18" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <f>C18*B18</f>
+        <v>0.2</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>124</v>
+      </c>
+      <c r="B19" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19">
+        <f t="shared" ref="D19:D25" si="1">C19*B19</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B20" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>131</v>
+      </c>
+      <c r="B21" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C22">
+        <v>0</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>129</v>
+      </c>
+      <c r="B23" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G23" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+      <c r="B24" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>127</v>
+      </c>
+      <c r="B25" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C25">
+        <v>0.5</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="1"/>
+        <v>0.05</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>126</v>
+      </c>
+      <c r="B26" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <f>C26*B26</f>
+        <v>0</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B27" s="4">
+        <f>SUM(B18:B26)</f>
+        <v>1</v>
+      </c>
+      <c r="D27" s="6">
+        <f>SUM(D18:D26)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G28" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>151</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G30" s="7" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31">
+        <f>C31*B31</f>
+        <v>0.2</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <f t="shared" ref="D32:D38" si="2">C32*B32</f>
+        <v>0</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="2"/>
+        <v>0.1</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>131</v>
+      </c>
+      <c r="B34" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>130</v>
+      </c>
+      <c r="B35" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>129</v>
+      </c>
+      <c r="B36" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B37" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C38">
+        <v>0.5</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="2"/>
+        <v>0.05</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>126</v>
+      </c>
+      <c r="B39" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C39">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f>C39*B39</f>
+        <v>0</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B40" s="4">
+        <f>SUM(B31:B39)</f>
+        <v>1</v>
+      </c>
+      <c r="D40" s="6">
+        <f>SUM(D31:D39)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G41" s="7" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A43" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>123</v>
+      </c>
+      <c r="B44" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C44">
+        <v>1</v>
+      </c>
+      <c r="D44">
+        <f>C44*B44</f>
+        <v>0.2</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>124</v>
+      </c>
+      <c r="B45" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <f t="shared" ref="D45:D51" si="3">C45*B45</f>
+        <v>0</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>125</v>
+      </c>
+      <c r="B46" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>131</v>
+      </c>
+      <c r="B47" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>130</v>
+      </c>
+      <c r="B48" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C50">
+        <v>0</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>127</v>
+      </c>
+      <c r="B51" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C51">
+        <v>0.5</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="3"/>
+        <v>0.05</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>126</v>
+      </c>
+      <c r="B52" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <f>C52*B52</f>
+        <v>0</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B53" s="4">
+        <f>SUM(B44:B52)</f>
+        <v>1</v>
+      </c>
+      <c r="D53" s="6">
+        <f>SUM(D44:D52)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G54" s="7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>153</v>
+      </c>
+      <c r="G55" s="7" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A56" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G56" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>123</v>
+      </c>
+      <c r="B57" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <f>C57*B57</f>
+        <v>0.2</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>124</v>
+      </c>
+      <c r="B58" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <f t="shared" ref="D58:D64" si="4">C58*B58</f>
+        <v>0</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>125</v>
+      </c>
+      <c r="B59" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>131</v>
+      </c>
+      <c r="B60" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>130</v>
+      </c>
+      <c r="B61" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>129</v>
+      </c>
+      <c r="B62" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G62" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>128</v>
+      </c>
+      <c r="B63" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G63" s="7" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C64">
+        <v>0.5</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="4"/>
+        <v>0.05</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>126</v>
+      </c>
+      <c r="B65" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C65">
+        <v>0</v>
+      </c>
+      <c r="D65">
+        <f>C65*B65</f>
+        <v>0</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="4">
+        <f>SUM(B57:B65)</f>
+        <v>1</v>
+      </c>
+      <c r="D66" s="6">
+        <f>SUM(D57:D65)</f>
+        <v>0.35000000000000003</v>
+      </c>
+      <c r="G66" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G67" s="7" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>154</v>
+      </c>
+      <c r="G68" s="7" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A69" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G69" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>123</v>
+      </c>
+      <c r="B70" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C70">
+        <v>1</v>
+      </c>
+      <c r="D70">
+        <f>C70*B70</f>
+        <v>0.2</v>
+      </c>
+      <c r="G70" s="7"/>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>124</v>
+      </c>
+      <c r="B71" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <f t="shared" ref="D71:D77" si="5">C71*B71</f>
+        <v>0</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C72">
+        <v>1</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="5"/>
+        <v>0.1</v>
+      </c>
+      <c r="G72" s="7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G73" s="7"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G74" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G75" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>128</v>
+      </c>
+      <c r="B76" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G76" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>127</v>
+      </c>
+      <c r="B77" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C77">
+        <v>0.5</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="5"/>
+        <v>0.05</v>
+      </c>
+      <c r="G77" s="7" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>126</v>
+      </c>
+      <c r="B78" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <f>C78*B78</f>
+        <v>0</v>
+      </c>
+      <c r="G78" s="7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B79" s="4">
+        <f>SUM(B70:B78)</f>
+        <v>1</v>
+      </c>
+      <c r="D79" s="6">
+        <f>SUM(D70:D78)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G80" s="7" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>155</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A82" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G82" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A83" t="s">
+        <v>123</v>
+      </c>
+      <c r="B83" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C83">
+        <v>1</v>
+      </c>
+      <c r="D83">
+        <f>C83*B83</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A84" t="s">
+        <v>124</v>
+      </c>
+      <c r="B84" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <f t="shared" ref="D84:D90" si="6">C84*B84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A85" t="s">
+        <v>125</v>
+      </c>
+      <c r="B85" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C85">
+        <v>1</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="6"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A86" t="s">
+        <v>131</v>
+      </c>
+      <c r="B86" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A87" t="s">
+        <v>130</v>
+      </c>
+      <c r="B87" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A88" t="s">
+        <v>129</v>
+      </c>
+      <c r="B88" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A89" t="s">
+        <v>128</v>
+      </c>
+      <c r="B89" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A90" t="s">
+        <v>127</v>
+      </c>
+      <c r="B90" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C90">
+        <v>0.5</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="6"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A91" t="s">
+        <v>126</v>
+      </c>
+      <c r="B91" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <f>C91*B91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B92" s="4">
+        <f>SUM(B83:B91)</f>
+        <v>1</v>
+      </c>
+      <c r="D92" s="6">
+        <f>SUM(D83:D91)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A94" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A95" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A96" t="s">
+        <v>123</v>
+      </c>
+      <c r="B96" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <f>C96*B96</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97" t="s">
+        <v>124</v>
+      </c>
+      <c r="B97" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <f t="shared" ref="D97:D103" si="7">C97*B97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98" t="s">
+        <v>125</v>
+      </c>
+      <c r="B98" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="7"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99" t="s">
+        <v>131</v>
+      </c>
+      <c r="B99" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100" t="s">
+        <v>130</v>
+      </c>
+      <c r="B100" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101" t="s">
+        <v>129</v>
+      </c>
+      <c r="B101" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103" t="s">
+        <v>127</v>
+      </c>
+      <c r="B103" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C103">
+        <v>0.5</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="7"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104" t="s">
+        <v>126</v>
+      </c>
+      <c r="B104" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <f>C104*B104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B105" s="4">
+        <f>SUM(B96:B104)</f>
+        <v>1</v>
+      </c>
+      <c r="D105" s="6">
+        <f>SUM(D96:D104)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109" t="s">
+        <v>123</v>
+      </c>
+      <c r="B109" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="C109">
+        <v>1</v>
+      </c>
+      <c r="D109">
+        <f>C109*B109</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110" t="s">
+        <v>124</v>
+      </c>
+      <c r="B110" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <f t="shared" ref="D110:D116" si="8">C110*B110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111" t="s">
+        <v>125</v>
+      </c>
+      <c r="B111" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C111">
+        <v>1</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="8"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112" t="s">
+        <v>131</v>
+      </c>
+      <c r="B112" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113" t="s">
+        <v>130</v>
+      </c>
+      <c r="B113" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114" t="s">
+        <v>129</v>
+      </c>
+      <c r="B114" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115" t="s">
+        <v>128</v>
+      </c>
+      <c r="B115" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116" t="s">
+        <v>127</v>
+      </c>
+      <c r="B116" s="3">
+        <v>0.1</v>
+      </c>
+      <c r="C116">
+        <v>0.5</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="8"/>
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117" t="s">
+        <v>126</v>
+      </c>
+      <c r="B117" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <f>C117*B117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B118" s="4">
+        <f>SUM(B109:B117)</f>
+        <v>1</v>
+      </c>
+      <c r="D118" s="6">
+        <f>SUM(D109:D117)</f>
+        <v>0.35000000000000003</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Evaluation_Schema.xlsx
+++ b/Evaluation_Schema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kim_W\Ekkono_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{363D961A-C6AB-41B3-9225-B858B2870615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE7CB72-B1BA-4EC0-95F6-F9584CBFAFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation Table" sheetId="3" r:id="rId1"/>
@@ -40,9 +40,6 @@
     <t>Input Structure:</t>
   </si>
   <si>
-    <t>Score [0, 1]</t>
-  </si>
-  <si>
     <t>Weighted Score</t>
   </si>
   <si>
@@ -400,27 +397,12 @@
     <t>    "outlier_ratio": 0.75</t>
   </si>
   <si>
-    <t>Does it answer the question of why this is an anomaly?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feature Importance integrated into reasoning? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Performance integrated into reasoning? </t>
-  </si>
-  <si>
     <t xml:space="preserve">Does it help the decision-making and provide actionability? </t>
   </si>
   <si>
     <t>Is it clear and easy to understand for non-experts?</t>
   </si>
   <si>
-    <t>Does it avoid irrelevant or excessive information?</t>
-  </si>
-  <si>
-    <t>Does it cover all the relevant aspects without missing key information?</t>
-  </si>
-  <si>
     <t>Is external or domain knowledge integrated into reasoning?</t>
   </si>
   <si>
@@ -794,6 +776,24 @@
   </si>
   <si>
     <t>* Every weather station has multiple tags that show the attributes of the device.  For each of these tags an outlier score exists that signalizes how different the weather station performance is compared to weather stations with the same tag.</t>
+  </si>
+  <si>
+    <t>Score [1,5]</t>
+  </si>
+  <si>
+    <t>Is all the available information used for the reasoning? (Performance/Feature Importance)</t>
+  </si>
+  <si>
+    <t>Does it provide a clear and concise explanation? (writing style)</t>
+  </si>
+  <si>
+    <t>Does it avoid irrelevant or excessive information? (information provided)</t>
+  </si>
+  <si>
+    <t>Does it answer the question of why this is an anomaly or performs bad?</t>
+  </si>
+  <si>
+    <t>Is there a coherent argumentation and reasoning provided for the interpretation?</t>
   </si>
 </sst>
 </file>
@@ -902,7 +902,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -925,6 +925,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1252,36 +1253,36 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D1" s="13" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E1" s="13"/>
       <c r="F1" s="13" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="G1" s="13"/>
       <c r="H1" s="13" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
       <c r="L1" s="13"/>
       <c r="M1" s="13" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
       <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
       <c r="R1" s="13" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="S1" s="13"/>
       <c r="T1" s="13"/>
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="X1" s="13"/>
       <c r="Y1" s="13"/>
@@ -1290,89 +1291,92 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D2" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="U2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="AA2" s="12" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C3" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="10"/>
+        <v>136</v>
+      </c>
+      <c r="D3" s="10">
+        <f>'d88 #1'!D14</f>
+        <v>3.25</v>
+      </c>
       <c r="E3" s="10"/>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -1399,9 +1403,12 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>143</v>
-      </c>
-      <c r="D4" s="10"/>
+        <v>137</v>
+      </c>
+      <c r="D4" s="10">
+        <f>'d88 #1'!D27</f>
+        <v>3.4000000000000004</v>
+      </c>
       <c r="E4" s="10"/>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
@@ -1428,9 +1435,12 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D5" s="10"/>
+        <v>138</v>
+      </c>
+      <c r="D5" s="10">
+        <f>'d88 #1'!D40</f>
+        <v>3.4000000000000004</v>
+      </c>
       <c r="E5" s="10"/>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
@@ -1457,13 +1467,17 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+        <v>136</v>
+      </c>
+      <c r="D6" s="11">
+        <v>3.6</v>
+      </c>
+      <c r="E6" s="11">
+        <v>3.3</v>
+      </c>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -1489,10 +1503,14 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>143</v>
-      </c>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+        <v>137</v>
+      </c>
+      <c r="D7" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="E7" s="11">
+        <v>3.6</v>
+      </c>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -1518,10 +1536,14 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>144</v>
-      </c>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+        <v>138</v>
+      </c>
+      <c r="D8" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="E8" s="11">
+        <v>3.4</v>
+      </c>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
@@ -1547,33 +1569,36 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C12" t="s">
-        <v>142</v>
-      </c>
-      <c r="D12" s="10"/>
+        <v>136</v>
+      </c>
+      <c r="D12" s="10">
+        <f>'d88 #1'!D53</f>
+        <v>0</v>
+      </c>
       <c r="E12" s="10"/>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -1600,9 +1625,12 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D13" s="10"/>
+        <v>137</v>
+      </c>
+      <c r="D13" s="10">
+        <f>'d88 #1'!D66</f>
+        <v>0</v>
+      </c>
       <c r="E13" s="10"/>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -1629,9 +1657,12 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D14" s="10"/>
+        <v>138</v>
+      </c>
+      <c r="D14" s="10">
+        <f>'d88 #1'!D79</f>
+        <v>0</v>
+      </c>
       <c r="E14" s="10"/>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -1658,13 +1689,17 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B15" s="9" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C15" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
+        <v>136</v>
+      </c>
+      <c r="D15" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="E15" s="11">
+        <v>3.2</v>
+      </c>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
@@ -1690,10 +1725,14 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>143</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11"/>
+        <v>137</v>
+      </c>
+      <c r="D16" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="E16" s="11">
+        <v>3.2</v>
+      </c>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
@@ -1719,10 +1758,14 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>144</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11"/>
+        <v>138</v>
+      </c>
+      <c r="D17" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="E17" s="11">
+        <v>3.6</v>
+      </c>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
@@ -1748,33 +1791,36 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C18" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
-      </c>
-      <c r="D21" s="10"/>
+        <v>136</v>
+      </c>
+      <c r="D21" s="10">
+        <f>'d88 #1'!D92</f>
+        <v>0</v>
+      </c>
       <c r="E21" s="10"/>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
@@ -1801,9 +1847,12 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>143</v>
-      </c>
-      <c r="D22" s="10"/>
+        <v>137</v>
+      </c>
+      <c r="D22" s="10">
+        <f>'d88 #1'!D105</f>
+        <v>0</v>
+      </c>
       <c r="E22" s="10"/>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
@@ -1830,9 +1879,12 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>144</v>
-      </c>
-      <c r="D23" s="10"/>
+        <v>138</v>
+      </c>
+      <c r="D23" s="10">
+        <f>'d88 #1'!D118</f>
+        <v>0</v>
+      </c>
       <c r="E23" s="10"/>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -1859,13 +1911,17 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B24" s="9" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
-      </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11"/>
+        <v>136</v>
+      </c>
+      <c r="D24" s="11">
+        <v>2.8</v>
+      </c>
+      <c r="E24" s="11">
+        <v>3.6</v>
+      </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
@@ -1891,10 +1947,14 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>143</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11"/>
+        <v>137</v>
+      </c>
+      <c r="D25" s="11">
+        <v>3.1</v>
+      </c>
+      <c r="E25" s="11">
+        <v>3.3</v>
+      </c>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
@@ -1920,10 +1980,14 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>144</v>
-      </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11"/>
+        <v>138</v>
+      </c>
+      <c r="D26" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="E26" s="11">
+        <v>3.3</v>
+      </c>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
@@ -1949,50 +2013,50 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2014,7 +2078,7 @@
   <dimension ref="A1:G119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="59.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="75.77734375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="6.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
@@ -2022,11 +2086,11 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5">
+        <f>B5*5 + B6*5 +B7*5+B8*5+B9*5+B10*5+B11*5+B12*5+B13*5</f>
         <v>5</v>
-      </c>
-      <c r="B1" s="5">
-        <f>B5*1 + B6*1 +B7*1+B8*1+B9*1+B10*1+B11*1+B12*1+B13*1</f>
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -2034,15 +2098,15 @@
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2053,196 +2117,196 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>123</v>
+      <c r="A5" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <f>C5*B5</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>124</v>
+      <c r="A6" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D12" si="0">C6*B6</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>125</v>
+      <c r="A7" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>131</v>
+      <c r="A8" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B8" s="3">
         <v>0.15</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B9" s="3">
         <v>0.15</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>129</v>
+      <c r="A10" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B10" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>128</v>
+      <c r="A11" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>127</v>
+      <c r="A12" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B12" s="3">
         <v>0.1</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>126</v>
+      <c r="A13" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B13" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <f>SUM(B5:B13)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -2253,198 +2317,198 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>123</v>
+      <c r="A18" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
         <f>C18*B18</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>124</v>
+      <c r="A19" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <f t="shared" ref="D19:D25" si="1">C19*B19</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>125</v>
+      <c r="A20" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>131</v>
+      <c r="A21" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B21" s="3">
         <v>0.15</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B22" s="3">
         <v>0.15</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>129</v>
+      <c r="A23" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B23" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>128</v>
+      <c r="A24" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>127</v>
+      <c r="A25" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B25" s="3">
         <v>0.1</v>
       </c>
       <c r="C25">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>126</v>
+      <c r="A26" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B26" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4">
         <f>SUM(B18:B26)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
-        <v>0.35000000000000003</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G28" s="7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2455,201 +2519,201 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>123</v>
+      <c r="A31" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31">
         <f>C31*B31</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>124</v>
+      <c r="A32" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D38" si="2">C32*B32</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>125</v>
+      <c r="A33" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>131</v>
+      <c r="A34" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B34" s="3">
         <v>0.15</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B35" s="3">
         <v>0.15</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>129</v>
+      <c r="A36" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B36" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>128</v>
+      <c r="A37" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>127</v>
+      <c r="A38" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B38" s="3">
         <v>0.1</v>
       </c>
       <c r="C38">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>126</v>
+      <c r="A39" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B39" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4">
         <f>SUM(B31:B39)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
-        <v>0.35000000000000003</v>
+        <v>3.4000000000000004</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2660,201 +2724,174 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>123</v>
+      <c r="A44" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
       </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>124</v>
+      <c r="A45" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C45">
-        <v>0</v>
       </c>
       <c r="D45">
         <f t="shared" ref="D45:D51" si="3">C45*B45</f>
         <v>0</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>125</v>
+      <c r="A46" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
       </c>
       <c r="D46">
         <f t="shared" si="3"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>131</v>
+      <c r="A47" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
       </c>
-      <c r="C47">
-        <v>0</v>
-      </c>
       <c r="D47">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B48" s="3">
         <v>0.15</v>
       </c>
-      <c r="C48">
-        <v>0</v>
-      </c>
       <c r="D48">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>129</v>
+      <c r="A49" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B49" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="C49">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D49">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>128</v>
+      <c r="A50" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
       </c>
-      <c r="C50">
-        <v>0</v>
-      </c>
       <c r="D50">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>127</v>
+      <c r="A51" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B51" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C51">
-        <v>0.5</v>
       </c>
       <c r="D51">
         <f t="shared" si="3"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>126</v>
+      <c r="A52" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B52" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="C52">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
         <v>0</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="4">
         <f>SUM(B44:B52)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
-        <v>0.35000000000000003</v>
+        <v>0</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2865,201 +2902,174 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>123</v>
+      <c r="A57" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
       </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>124</v>
+      <c r="A58" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C58">
-        <v>0</v>
       </c>
       <c r="D58">
         <f t="shared" ref="D58:D64" si="4">C58*B58</f>
         <v>0</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>125</v>
+      <c r="A59" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
       </c>
       <c r="D59">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>131</v>
+      <c r="A60" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
       </c>
-      <c r="C60">
-        <v>0</v>
-      </c>
       <c r="D60">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B61" s="3">
         <v>0.15</v>
       </c>
-      <c r="C61">
-        <v>0</v>
-      </c>
       <c r="D61">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>129</v>
+      <c r="A62" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B62" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="C62">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D62">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>128</v>
+      <c r="A63" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
       </c>
-      <c r="C63">
-        <v>0</v>
-      </c>
       <c r="D63">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>127</v>
+      <c r="A64" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B64" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C64">
-        <v>0.5</v>
       </c>
       <c r="D64">
         <f t="shared" si="4"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>126</v>
+      <c r="A65" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B65" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="C65">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
         <v>0</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="4">
         <f>SUM(B57:B65)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
-        <v>0.35000000000000003</v>
+        <v>0</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -3070,201 +3080,174 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>123</v>
+      <c r="A70" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
       </c>
-      <c r="C70">
-        <v>1</v>
-      </c>
       <c r="D70">
         <f>C70*B70</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>124</v>
+      <c r="A71" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C71">
-        <v>0</v>
       </c>
       <c r="D71">
         <f t="shared" ref="D71:D77" si="5">C71*B71</f>
         <v>0</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>125</v>
+      <c r="A72" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C72">
-        <v>1</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>131</v>
+      <c r="A73" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
       </c>
-      <c r="C73">
-        <v>0</v>
-      </c>
       <c r="D73">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B74" s="3">
         <v>0.15</v>
       </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
       <c r="D74">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>129</v>
+      <c r="A75" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B75" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="C75">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D75">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>128</v>
+      <c r="A76" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
       </c>
-      <c r="C76">
-        <v>0</v>
-      </c>
       <c r="D76">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>127</v>
+      <c r="A77" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C77">
-        <v>0.5</v>
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>126</v>
+      <c r="A78" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B78" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="C78">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
         <v>0</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="4">
         <f>SUM(B70:B78)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
-        <v>0.35000000000000003</v>
+        <v>0</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G80" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3275,201 +3258,174 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>123</v>
+      <c r="A83" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
       </c>
-      <c r="C83">
-        <v>1</v>
-      </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>124</v>
+      <c r="A84" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C84">
-        <v>0</v>
       </c>
       <c r="D84">
         <f t="shared" ref="D84:D90" si="6">C84*B84</f>
         <v>0</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>125</v>
+      <c r="A85" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C85">
-        <v>1</v>
       </c>
       <c r="D85">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>131</v>
+      <c r="A86" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
       </c>
-      <c r="C86">
-        <v>0</v>
-      </c>
       <c r="D86">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B87" s="3">
         <v>0.15</v>
       </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
       <c r="D87">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>129</v>
+      <c r="A88" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B88" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="C88">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D88">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>128</v>
+      <c r="A89" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
       </c>
-      <c r="C89">
-        <v>0</v>
-      </c>
       <c r="D89">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>127</v>
+      <c r="A90" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B90" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C90">
-        <v>0.5</v>
       </c>
       <c r="D90">
         <f t="shared" si="6"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>126</v>
+      <c r="A91" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B91" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="C91">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
         <v>0</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="4">
         <f>SUM(B83:B91)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
-        <v>0.35000000000000003</v>
+        <v>0</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G93" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -3480,188 +3436,161 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>123</v>
+      <c r="A96" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
       </c>
-      <c r="C96">
-        <v>1</v>
-      </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>124</v>
+      <c r="A97" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C97">
-        <v>0</v>
       </c>
       <c r="D97">
         <f t="shared" ref="D97:D103" si="7">C97*B97</f>
         <v>0</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>125</v>
+      <c r="A98" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C98">
-        <v>1</v>
       </c>
       <c r="D98">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>131</v>
+      <c r="A99" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
       </c>
-      <c r="C99">
-        <v>0</v>
-      </c>
       <c r="D99">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B100" s="3">
         <v>0.15</v>
       </c>
-      <c r="C100">
-        <v>0</v>
-      </c>
       <c r="D100">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>129</v>
+      <c r="A101" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B101" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="C101">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D101">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>128</v>
+      <c r="A102" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
       </c>
-      <c r="C102">
-        <v>0</v>
-      </c>
       <c r="D102">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>127</v>
+      <c r="A103" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B103" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C103">
-        <v>0.5</v>
       </c>
       <c r="D103">
         <f t="shared" si="7"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>126</v>
+      <c r="A104" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B104" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="C104">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
         <v>0</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="4">
         <f>SUM(B96:B104)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
-        <v>0.35000000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -3672,36 +3601,30 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>123</v>
+      <c r="A109" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
       </c>
-      <c r="C109">
-        <v>1</v>
-      </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>124</v>
+      <c r="A110" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C110">
-        <v>0</v>
       </c>
       <c r="D110">
         <f t="shared" ref="D110:D116" si="8">C110*B110</f>
@@ -3709,30 +3632,24 @@
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>125</v>
+      <c r="A111" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C111">
-        <v>1</v>
       </c>
       <c r="D111">
         <f t="shared" si="8"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>131</v>
+      <c r="A112" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
       </c>
-      <c r="C112">
-        <v>0</v>
-      </c>
       <c r="D112">
         <f t="shared" si="8"/>
         <v>0</v>
@@ -3740,28 +3657,22 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B113" s="3">
         <v>0.15</v>
       </c>
-      <c r="C113">
-        <v>0</v>
-      </c>
       <c r="D113">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>129</v>
+      <c r="A114" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B114" s="3">
-        <v>0.1</v>
-      </c>
-      <c r="C114">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="D114">
         <f t="shared" si="8"/>
@@ -3769,44 +3680,35 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>128</v>
+      <c r="A115" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
       </c>
-      <c r="C115">
-        <v>0</v>
-      </c>
       <c r="D115">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>127</v>
+      <c r="A116" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B116" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C116">
-        <v>0.5</v>
       </c>
       <c r="D116">
         <f t="shared" si="8"/>
-        <v>0.05</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>126</v>
+      <c r="A117" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B117" s="3">
-        <v>0.05</v>
-      </c>
-      <c r="C117">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
@@ -3816,11 +3718,11 @@
     <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
-        <v>0.35000000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -3842,11 +3744,11 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5">
+        <f>B5*5 + B6*5 +B7*5+B8*5+B9*5+B10*5+B11*5+B12*5+B13*5</f>
         <v>5</v>
-      </c>
-      <c r="B1" s="5">
-        <f>B5*1 + B6*1 +B7*1+B8*1+B9*1+B10*1+B11*1+B12*1+B13*1</f>
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -3854,15 +3756,15 @@
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3873,198 +3775,198 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>123</v>
+      <c r="A5" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <f>C5*B5</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>124</v>
+      <c r="A6" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D12" si="0">C6*B6</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>125</v>
+      <c r="A7" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>131</v>
+      <c r="A8" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B8" s="3">
         <v>0.15</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B9" s="3">
         <v>0.15</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>129</v>
+      <c r="A10" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B10" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>128</v>
+      <c r="A11" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>127</v>
+      <c r="A12" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B12" s="3">
         <v>0.1</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>126</v>
+      <c r="A13" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B13" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <f>SUM(B5:B13)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -4075,201 +3977,201 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>123</v>
+      <c r="A18" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
         <f>C18*B18</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>124</v>
+      <c r="A19" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <f t="shared" ref="D19:D25" si="1">C19*B19</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>125</v>
+      <c r="A20" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>131</v>
+      <c r="A21" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B21" s="3">
         <v>0.15</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B22" s="3">
         <v>0.15</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>129</v>
+      <c r="A23" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B23" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>128</v>
+      <c r="A24" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>127</v>
+      <c r="A25" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B25" s="3">
         <v>0.1</v>
       </c>
       <c r="C25">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>126</v>
+      <c r="A26" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B26" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4">
         <f>SUM(B18:B26)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G28" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -4280,201 +4182,201 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>123</v>
+      <c r="A31" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31">
         <f>C31*B31</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>124</v>
+      <c r="A32" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D38" si="2">C32*B32</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>125</v>
+      <c r="A33" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>131</v>
+      <c r="A34" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B34" s="3">
         <v>0.15</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B35" s="3">
         <v>0.15</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>129</v>
+      <c r="A36" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B36" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>128</v>
+      <c r="A37" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>127</v>
+      <c r="A38" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B38" s="3">
         <v>0.1</v>
       </c>
       <c r="C38">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>126</v>
+      <c r="A39" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B39" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4">
         <f>SUM(B31:B39)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -4485,201 +4387,201 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>123</v>
+      <c r="A44" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>124</v>
+      <c r="A45" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <f t="shared" ref="D45:D51" si="3">C45*B45</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>125</v>
+      <c r="A46" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46">
         <f t="shared" si="3"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>131</v>
+      <c r="A47" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B48" s="3">
         <v>0.15</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D48">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>129</v>
+      <c r="A49" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B49" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>128</v>
+      <c r="A50" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>127</v>
+      <c r="A51" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B51" s="3">
         <v>0.1</v>
       </c>
       <c r="C51">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D51">
         <f t="shared" si="3"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>126</v>
+      <c r="A52" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B52" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="4">
         <f>SUM(B44:B52)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -4690,201 +4592,201 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>123</v>
+      <c r="A57" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>124</v>
+      <c r="A58" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D58">
         <f t="shared" ref="D58:D64" si="4">C58*B58</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>125</v>
+      <c r="A59" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>131</v>
+      <c r="A60" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D60">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B61" s="3">
         <v>0.15</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D61">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>129</v>
+      <c r="A62" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B62" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>128</v>
+      <c r="A63" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>127</v>
+      <c r="A64" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B64" s="3">
         <v>0.1</v>
       </c>
       <c r="C64">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D64">
         <f t="shared" si="4"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>126</v>
+      <c r="A65" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B65" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="4">
         <f>SUM(B57:B65)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -4895,201 +4797,201 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>123</v>
+      <c r="A70" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <f>C70*B70</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>124</v>
+      <c r="A71" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D71">
         <f t="shared" ref="D71:D77" si="5">C71*B71</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>125</v>
+      <c r="A72" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>131</v>
+      <c r="A73" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B74" s="3">
         <v>0.15</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D74">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>129</v>
+      <c r="A75" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B75" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>128</v>
+      <c r="A76" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>127</v>
+      <c r="A77" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
       </c>
       <c r="C77">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>126</v>
+      <c r="A78" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B78" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="4">
         <f>SUM(B70:B78)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G80" s="7" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -5100,201 +5002,201 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>123</v>
+      <c r="A83" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>124</v>
+      <c r="A84" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D84">
         <f t="shared" ref="D84:D90" si="6">C84*B84</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>125</v>
+      <c r="A85" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>131</v>
+      <c r="A86" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D86">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B87" s="3">
         <v>0.15</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D87">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>129</v>
+      <c r="A88" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B88" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>128</v>
+      <c r="A89" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>127</v>
+      <c r="A90" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B90" s="3">
         <v>0.1</v>
       </c>
       <c r="C90">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D90">
         <f t="shared" si="6"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>126</v>
+      <c r="A91" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B91" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="4">
         <f>SUM(B83:B91)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G93" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -5305,198 +5207,198 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>123</v>
+      <c r="A96" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>124</v>
+      <c r="A97" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D97">
         <f t="shared" ref="D97:D103" si="7">C97*B97</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>125</v>
+      <c r="A98" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>131</v>
+      <c r="A99" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B100" s="3">
         <v>0.15</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D100">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>129</v>
+      <c r="A101" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B101" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D101">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>128</v>
+      <c r="A102" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>127</v>
+      <c r="A103" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B103" s="3">
         <v>0.1</v>
       </c>
       <c r="C103">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D103">
         <f t="shared" si="7"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>126</v>
+      <c r="A104" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B104" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="4">
         <f>SUM(B96:B104)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G106" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -5507,158 +5409,158 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G108" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>123</v>
+      <c r="A109" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>124</v>
+      <c r="A110" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D110">
         <f t="shared" ref="D110:D116" si="8">C110*B110</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>125</v>
+      <c r="A111" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D111">
         <f t="shared" si="8"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>131</v>
+      <c r="A112" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B113" s="3">
         <v>0.15</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D113">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>129</v>
+      <c r="A114" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B114" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>128</v>
+      <c r="A115" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>127</v>
+      <c r="A116" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B116" s="3">
         <v>0.1</v>
       </c>
       <c r="C116">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D116">
         <f t="shared" si="8"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>126</v>
+      <c r="A117" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B117" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -5680,11 +5582,11 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5">
+        <f>B5*5 + B6*5 +B7*5+B8*5+B9*5+B10*5+B11*5+B12*5+B13*5</f>
         <v>5</v>
-      </c>
-      <c r="B1" s="5">
-        <f>B5*1 + B6*1 +B7*1+B8*1+B9*1+B10*1+B11*1+B12*1+B13*1</f>
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -5692,15 +5594,15 @@
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -5711,201 +5613,201 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>123</v>
+      <c r="A5" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <f>C5*B5</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>124</v>
+      <c r="A6" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D12" si="0">C6*B6</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>125</v>
+      <c r="A7" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>131</v>
+      <c r="A8" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B8" s="3">
         <v>0.15</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B9" s="3">
         <v>0.15</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>129</v>
+      <c r="A10" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B10" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>128</v>
+      <c r="A11" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>127</v>
+      <c r="A12" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B12" s="3">
         <v>0.1</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>126</v>
+      <c r="A13" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B13" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <f>SUM(B5:B13)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -5916,201 +5818,201 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>123</v>
+      <c r="A18" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
         <f>C18*B18</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>124</v>
+      <c r="A19" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <f t="shared" ref="D19:D25" si="1">C19*B19</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>125</v>
+      <c r="A20" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>131</v>
+      <c r="A21" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B21" s="3">
         <v>0.15</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B22" s="3">
         <v>0.15</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>129</v>
+      <c r="A23" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B23" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>128</v>
+      <c r="A24" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>127</v>
+      <c r="A25" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B25" s="3">
         <v>0.1</v>
       </c>
       <c r="C25">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>126</v>
+      <c r="A26" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B26" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4">
         <f>SUM(B18:B26)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G28" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -6121,201 +6023,201 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>123</v>
+      <c r="A31" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31">
         <f>C31*B31</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>124</v>
+      <c r="A32" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D38" si="2">C32*B32</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>125</v>
+      <c r="A33" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>131</v>
+      <c r="A34" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B34" s="3">
         <v>0.15</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B35" s="3">
         <v>0.15</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>129</v>
+      <c r="A36" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B36" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>128</v>
+      <c r="A37" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>127</v>
+      <c r="A38" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B38" s="3">
         <v>0.1</v>
       </c>
       <c r="C38">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>126</v>
+      <c r="A39" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B39" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4">
         <f>SUM(B31:B39)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -6326,201 +6228,201 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>123</v>
+      <c r="A44" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>124</v>
+      <c r="A45" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <f t="shared" ref="D45:D51" si="3">C45*B45</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>125</v>
+      <c r="A46" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46">
         <f t="shared" si="3"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>131</v>
+      <c r="A47" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B48" s="3">
         <v>0.15</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D48">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>129</v>
+      <c r="A49" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B49" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>128</v>
+      <c r="A50" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>127</v>
+      <c r="A51" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B51" s="3">
         <v>0.1</v>
       </c>
       <c r="C51">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D51">
         <f t="shared" si="3"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>126</v>
+      <c r="A52" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B52" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="4">
         <f>SUM(B44:B52)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -6531,198 +6433,198 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>123</v>
+      <c r="A57" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>124</v>
+      <c r="A58" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D58">
         <f t="shared" ref="D58:D64" si="4">C58*B58</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>125</v>
+      <c r="A59" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>131</v>
+      <c r="A60" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D60">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B61" s="3">
         <v>0.15</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D61">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>129</v>
+      <c r="A62" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B62" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>128</v>
+      <c r="A63" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>127</v>
+      <c r="A64" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B64" s="3">
         <v>0.1</v>
       </c>
       <c r="C64">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D64">
         <f t="shared" si="4"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>126</v>
+      <c r="A65" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B65" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="4">
         <f>SUM(B57:B65)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -6733,179 +6635,179 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>123</v>
+      <c r="A70" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <f>C70*B70</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>124</v>
+      <c r="A71" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D71">
         <f t="shared" ref="D71:D77" si="5">C71*B71</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>125</v>
+      <c r="A72" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>131</v>
+      <c r="A73" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B74" s="3">
         <v>0.15</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D74">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>129</v>
+      <c r="A75" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B75" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>128</v>
+      <c r="A76" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>127</v>
+      <c r="A77" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
       </c>
       <c r="C77">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>126</v>
+      <c r="A78" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B78" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="4">
         <f>SUM(B70:B78)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -6913,7 +6815,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G81" s="7"/>
     </row>
@@ -6925,162 +6827,162 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G82" s="7"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>123</v>
+      <c r="A83" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>124</v>
+      <c r="A84" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D84">
         <f t="shared" ref="D84:D90" si="6">C84*B84</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>125</v>
+      <c r="A85" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>131</v>
+      <c r="A86" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D86">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B87" s="3">
         <v>0.15</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D87">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>129</v>
+      <c r="A88" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B88" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>128</v>
+      <c r="A89" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>127</v>
+      <c r="A90" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B90" s="3">
         <v>0.1</v>
       </c>
       <c r="C90">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D90">
         <f t="shared" si="6"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>126</v>
+      <c r="A91" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B91" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="4">
         <f>SUM(B83:B91)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -7091,161 +6993,161 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>123</v>
+      <c r="A96" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>124</v>
+      <c r="A97" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D97">
         <f t="shared" ref="D97:D103" si="7">C97*B97</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>125</v>
+      <c r="A98" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>131</v>
+      <c r="A99" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B100" s="3">
         <v>0.15</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D100">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>129</v>
+      <c r="A101" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B101" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D101">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>128</v>
+      <c r="A102" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>127</v>
+      <c r="A103" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B103" s="3">
         <v>0.1</v>
       </c>
       <c r="C103">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D103">
         <f t="shared" si="7"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>126</v>
+      <c r="A104" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B104" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="4">
         <f>SUM(B96:B104)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -7256,155 +7158,155 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>123</v>
+      <c r="A109" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>124</v>
+      <c r="A110" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D110">
         <f t="shared" ref="D110:D116" si="8">C110*B110</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>125</v>
+      <c r="A111" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D111">
         <f t="shared" si="8"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>131</v>
+      <c r="A112" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B113" s="3">
         <v>0.15</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D113">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>129</v>
+      <c r="A114" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B114" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>128</v>
+      <c r="A115" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>127</v>
+      <c r="A116" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B116" s="3">
         <v>0.1</v>
       </c>
       <c r="C116">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D116">
         <f t="shared" si="8"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>126</v>
+      <c r="A117" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B117" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -7426,11 +7328,11 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5">
+        <f>B5*5 + B6*5 +B7*5+B8*5+B9*5+B10*5+B11*5+B12*5+B13*5</f>
         <v>5</v>
-      </c>
-      <c r="B1" s="5">
-        <f>B5*1 + B6*1 +B7*1+B8*1+B9*1+B10*1+B11*1+B12*1+B13*1</f>
-        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -7438,15 +7340,15 @@
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -7457,201 +7359,201 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>123</v>
+      <c r="A5" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D5">
         <f>C5*B5</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>124</v>
+      <c r="A6" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D12" si="0">C6*B6</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>125</v>
+      <c r="A7" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
       </c>
       <c r="C7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>131</v>
+      <c r="A8" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B8" s="3">
         <v>0.15</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B9" s="3">
         <v>0.15</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>129</v>
+      <c r="A10" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B10" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>128</v>
+      <c r="A11" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>127</v>
+      <c r="A12" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B12" s="3">
         <v>0.1</v>
       </c>
       <c r="C12">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>126</v>
+      <c r="A13" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B13" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <f>SUM(B5:B13)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -7662,201 +7564,201 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
-        <v>123</v>
+      <c r="A18" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18">
         <f>C18*B18</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>124</v>
+      <c r="A19" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D19">
         <f t="shared" ref="D19:D25" si="1">C19*B19</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>125</v>
+      <c r="A20" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
       </c>
       <c r="C20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
-        <v>131</v>
+      <c r="A21" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B21" s="3">
         <v>0.15</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B22" s="3">
         <v>0.15</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>129</v>
+      <c r="A23" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B23" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>128</v>
+      <c r="A24" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>127</v>
+      <c r="A25" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B25" s="3">
         <v>0.1</v>
       </c>
       <c r="C25">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>126</v>
+      <c r="A26" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B26" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4">
         <f>SUM(B18:B26)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G28" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -7867,201 +7769,201 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
-        <v>123</v>
+      <c r="A31" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
       </c>
       <c r="C31">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31">
         <f>C31*B31</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
-        <v>124</v>
+      <c r="A32" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D38" si="2">C32*B32</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>125</v>
+      <c r="A33" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
       </c>
       <c r="C33">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D33">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" t="s">
-        <v>131</v>
+      <c r="A34" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B34" s="3">
         <v>0.15</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D34">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B35" s="3">
         <v>0.15</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D35">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>129</v>
+      <c r="A36" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B36" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D36">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" t="s">
-        <v>128</v>
+      <c r="A37" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D37">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>127</v>
+      <c r="A38" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B38" s="3">
         <v>0.1</v>
       </c>
       <c r="C38">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D38">
         <f t="shared" si="2"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>126</v>
+      <c r="A39" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B39" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4">
         <f>SUM(B31:B39)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -8072,201 +7974,201 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" t="s">
-        <v>123</v>
+      <c r="A44" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
       </c>
       <c r="C44">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>124</v>
+      <c r="A45" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
       </c>
       <c r="C45">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D45">
         <f t="shared" ref="D45:D51" si="3">C45*B45</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" t="s">
-        <v>125</v>
+      <c r="A46" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
       </c>
       <c r="C46">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D46">
         <f t="shared" si="3"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>131</v>
+      <c r="A47" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
       </c>
       <c r="C47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B48" s="3">
         <v>0.15</v>
       </c>
       <c r="C48">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D48">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>129</v>
+      <c r="A49" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B49" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D49">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>128</v>
+      <c r="A50" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
       </c>
       <c r="C50">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D50">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>127</v>
+      <c r="A51" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B51" s="3">
         <v>0.1</v>
       </c>
       <c r="C51">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D51">
         <f t="shared" si="3"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>126</v>
+      <c r="A52" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B52" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C52">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="4">
         <f>SUM(B44:B52)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -8277,201 +8179,201 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>123</v>
+      <c r="A57" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>124</v>
+      <c r="A58" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
       </c>
       <c r="C58">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D58">
         <f t="shared" ref="D58:D64" si="4">C58*B58</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" t="s">
-        <v>125</v>
+      <c r="A59" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
       </c>
       <c r="C59">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D59">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" t="s">
-        <v>131</v>
+      <c r="A60" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D60">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B61" s="3">
         <v>0.15</v>
       </c>
       <c r="C61">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D61">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>129</v>
+      <c r="A62" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B62" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C62">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D62">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>128</v>
+      <c r="A63" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
       </c>
       <c r="C63">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D63">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>127</v>
+      <c r="A64" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B64" s="3">
         <v>0.1</v>
       </c>
       <c r="C64">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D64">
         <f t="shared" si="4"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" t="s">
-        <v>126</v>
+      <c r="A65" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B65" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="4">
         <f>SUM(B57:B65)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
       <c r="G66" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -8482,194 +8384,194 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D69" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>123</v>
+      <c r="A70" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
       </c>
       <c r="C70">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D70">
         <f>C70*B70</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G70" s="7"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>124</v>
+      <c r="A71" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
       </c>
       <c r="C71">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D71">
         <f t="shared" ref="D71:D77" si="5">C71*B71</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" t="s">
-        <v>125</v>
+      <c r="A72" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
       </c>
       <c r="C72">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>131</v>
+      <c r="A73" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D73">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G73" s="7"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B74" s="3">
         <v>0.15</v>
       </c>
       <c r="C74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D74">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>129</v>
+      <c r="A75" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B75" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C75">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G75" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>128</v>
+      <c r="A76" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
       </c>
       <c r="C76">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" t="s">
-        <v>127</v>
+      <c r="A77" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
       </c>
       <c r="C77">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" t="s">
-        <v>126</v>
+      <c r="A78" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B78" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="4">
         <f>SUM(B70:B78)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G80" s="7" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -8680,164 +8582,164 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" t="s">
-        <v>123</v>
+      <c r="A83" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" t="s">
-        <v>124</v>
+      <c r="A84" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
       </c>
       <c r="C84">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D84">
         <f t="shared" ref="D84:D90" si="6">C84*B84</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" t="s">
-        <v>125</v>
+      <c r="A85" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
       </c>
       <c r="C85">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D85">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" t="s">
-        <v>131</v>
+      <c r="A86" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
       </c>
       <c r="C86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D86">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B87" s="3">
         <v>0.15</v>
       </c>
       <c r="C87">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D87">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" t="s">
-        <v>129</v>
+      <c r="A88" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B88" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C88">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D88">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" t="s">
-        <v>128</v>
+      <c r="A89" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
       </c>
       <c r="C89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D89">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" t="s">
-        <v>127</v>
+      <c r="A90" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B90" s="3">
         <v>0.1</v>
       </c>
       <c r="C90">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D90">
         <f t="shared" si="6"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" t="s">
-        <v>126</v>
+      <c r="A91" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B91" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C91">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="4">
         <f>SUM(B83:B91)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -8848,161 +8750,161 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" t="s">
-        <v>123</v>
+      <c r="A96" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
       </c>
       <c r="C96">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" t="s">
-        <v>124</v>
+      <c r="A97" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D97">
         <f t="shared" ref="D97:D103" si="7">C97*B97</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" t="s">
-        <v>125</v>
+      <c r="A98" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
       </c>
       <c r="C98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D98">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" t="s">
-        <v>131</v>
+      <c r="A99" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
       </c>
       <c r="C99">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D99">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B100" s="3">
         <v>0.15</v>
       </c>
       <c r="C100">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D100">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" t="s">
-        <v>129</v>
+      <c r="A101" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B101" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C101">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D101">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" t="s">
-        <v>128</v>
+      <c r="A102" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
       </c>
       <c r="C102">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D102">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" t="s">
-        <v>127</v>
+      <c r="A103" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B103" s="3">
         <v>0.1</v>
       </c>
       <c r="C103">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D103">
         <f t="shared" si="7"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" t="s">
-        <v>126</v>
+      <c r="A104" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B104" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C104">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="4">
         <f>SUM(B96:B104)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -9013,155 +8915,155 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>3</v>
+        <v>249</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" t="s">
-        <v>123</v>
+      <c r="A109" s="14" t="s">
+        <v>253</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
       </c>
       <c r="C109">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" t="s">
-        <v>124</v>
+      <c r="A110" s="14" t="s">
+        <v>250</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D110">
         <f t="shared" ref="D110:D116" si="8">C110*B110</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" t="s">
-        <v>125</v>
+      <c r="A111" s="14" t="s">
+        <v>254</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
       </c>
       <c r="C111">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D111">
         <f t="shared" si="8"/>
-        <v>0.1</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" t="s">
-        <v>131</v>
+      <c r="A112" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D112">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B113" s="3">
         <v>0.15</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D113">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" t="s">
-        <v>129</v>
+      <c r="A114" s="14" t="s">
+        <v>251</v>
       </c>
       <c r="B114" s="3">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="C114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D114">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" t="s">
-        <v>128</v>
+      <c r="A115" s="14" t="s">
+        <v>252</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D115">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" t="s">
-        <v>127</v>
+      <c r="A116" s="14" t="s">
+        <v>123</v>
       </c>
       <c r="B116" s="3">
         <v>0.1</v>
       </c>
       <c r="C116">
-        <v>0.5</v>
+        <v>4</v>
       </c>
       <c r="D116">
         <f t="shared" si="8"/>
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" t="s">
-        <v>126</v>
+      <c r="A117" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B117" s="3">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="C117">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
-        <v>1</v>
+        <v>1.0000000000000002</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
-        <v>0.35000000000000003</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>

--- a/Evaluation_Schema.xlsx
+++ b/Evaluation_Schema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kim_W\Ekkono_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEE7CB72-B1BA-4EC0-95F6-F9584CBFAFA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EB0217-A1E9-4B8E-A328-82A06CC9DE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation Table" sheetId="3" r:id="rId1"/>
@@ -409,24 +409,6 @@
     <t>Is there a correct interpretation of relationships?</t>
   </si>
   <si>
-    <t>Experiment 1</t>
-  </si>
-  <si>
-    <t>Experiment 2</t>
-  </si>
-  <si>
-    <t>Experiment 3</t>
-  </si>
-  <si>
-    <t>Experiment 4</t>
-  </si>
-  <si>
-    <t>Experiment 5</t>
-  </si>
-  <si>
-    <t>Experiment 6</t>
-  </si>
-  <si>
     <t>d88</t>
   </si>
   <si>
@@ -794,6 +776,24 @@
   </si>
   <si>
     <t>Is there a coherent argumentation and reasoning provided for the interpretation?</t>
+  </si>
+  <si>
+    <t>Experiment 1 (mainly num)</t>
+  </si>
+  <si>
+    <t>Experiment 2 (mainly text)</t>
+  </si>
+  <si>
+    <t>Experiment 3 (mainly text + other model information)</t>
+  </si>
+  <si>
+    <t>Experiment 4 (mainly visual)</t>
+  </si>
+  <si>
+    <t>Experiment 5 (Combination)</t>
+  </si>
+  <si>
+    <t>Experiment 6 (Combinaiton)</t>
   </si>
 </sst>
 </file>
@@ -902,7 +902,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -925,7 +925,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1253,36 +1252,36 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D1" s="13" t="s">
-        <v>126</v>
+        <v>249</v>
       </c>
       <c r="E1" s="13"/>
       <c r="F1" s="13" t="s">
-        <v>127</v>
+        <v>250</v>
       </c>
       <c r="G1" s="13"/>
       <c r="H1" s="13" t="s">
-        <v>128</v>
+        <v>251</v>
       </c>
       <c r="I1" s="13"/>
       <c r="J1" s="13"/>
       <c r="K1" s="13"/>
       <c r="L1" s="13"/>
       <c r="M1" s="13" t="s">
-        <v>129</v>
+        <v>252</v>
       </c>
       <c r="N1" s="13"/>
       <c r="O1" s="13"/>
       <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
       <c r="R1" s="13" t="s">
-        <v>130</v>
+        <v>253</v>
       </c>
       <c r="S1" s="13"/>
       <c r="T1" s="13"/>
       <c r="U1" s="13"/>
       <c r="V1" s="13"/>
       <c r="W1" s="13" t="s">
-        <v>131</v>
+        <v>254</v>
       </c>
       <c r="X1" s="13"/>
       <c r="Y1" s="13"/>
@@ -1291,93 +1290,96 @@
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="D2" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="U2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="Z2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="AA2" s="12" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D3" s="10">
         <f>'d88 #1'!D14</f>
         <v>3.25</v>
       </c>
-      <c r="E3" s="10"/>
+      <c r="E3" s="10">
+        <f>'d131 #1'!D14</f>
+        <v>3.1499999999999995</v>
+      </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
       <c r="H3" s="10"/>
@@ -1403,13 +1405,16 @@
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D4" s="10">
         <f>'d88 #1'!D27</f>
         <v>3.4000000000000004</v>
       </c>
-      <c r="E4" s="10"/>
+      <c r="E4" s="10">
+        <f>'d131 #1'!D27</f>
+        <v>3.3</v>
+      </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
       <c r="H4" s="10"/>
@@ -1435,13 +1440,16 @@
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D5" s="10">
         <f>'d88 #1'!D40</f>
         <v>3.4000000000000004</v>
       </c>
-      <c r="E5" s="10"/>
+      <c r="E5" s="10">
+        <f>'d131 #1'!D40</f>
+        <v>3.1999999999999993</v>
+      </c>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
       <c r="H5" s="10"/>
@@ -1467,10 +1475,10 @@
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C6" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D6" s="11">
         <v>3.6</v>
@@ -1503,7 +1511,7 @@
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D7" s="11">
         <v>3.4</v>
@@ -1536,7 +1544,7 @@
     </row>
     <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D8" s="11">
         <v>3.4</v>
@@ -1569,37 +1577,40 @@
     </row>
     <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C9" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C12" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D12" s="10">
         <f>'d88 #1'!D53</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="10"/>
+        <v>3</v>
+      </c>
+      <c r="E12" s="10">
+        <f>'d131 #1'!D53</f>
+        <v>3.0999999999999996</v>
+      </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
       <c r="H12" s="10"/>
@@ -1625,13 +1636,16 @@
     </row>
     <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D13" s="10">
         <f>'d88 #1'!D66</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="10"/>
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="E13" s="10">
+        <f>'d131 #1'!D66</f>
+        <v>3.1999999999999997</v>
+      </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
       <c r="H13" s="10"/>
@@ -1657,13 +1671,16 @@
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D14" s="10">
         <f>'d88 #1'!D79</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="10"/>
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="E14" s="10">
+        <f>'d131 #1'!D79</f>
+        <v>3.3</v>
+      </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
       <c r="H14" s="10"/>
@@ -1689,10 +1706,10 @@
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B15" s="9" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C15" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D15" s="11">
         <v>3.4</v>
@@ -1725,7 +1742,7 @@
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D16" s="11">
         <v>3.4</v>
@@ -1758,7 +1775,7 @@
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D17" s="11">
         <v>3.4</v>
@@ -1791,37 +1808,40 @@
     </row>
     <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="C21" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D21" s="10">
         <f>'d88 #1'!D92</f>
-        <v>0</v>
-      </c>
-      <c r="E21" s="10"/>
+        <v>2.7</v>
+      </c>
+      <c r="E21" s="10">
+        <f>'d131 #1'!D92</f>
+        <v>3.2</v>
+      </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
       <c r="H21" s="10"/>
@@ -1847,13 +1867,16 @@
     </row>
     <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D22" s="10">
         <f>'d88 #1'!D105</f>
-        <v>0</v>
-      </c>
-      <c r="E22" s="10"/>
+        <v>3.0999999999999996</v>
+      </c>
+      <c r="E22" s="10">
+        <f>'d131 #1'!D105</f>
+        <v>3.2</v>
+      </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
       <c r="H22" s="10"/>
@@ -1879,13 +1902,16 @@
     </row>
     <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D23" s="10">
         <f>'d88 #1'!D118</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="10"/>
+        <v>3.4000000000000004</v>
+      </c>
+      <c r="E23" s="10">
+        <f>'d131 #1'!D118</f>
+        <v>3.25</v>
+      </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
       <c r="H23" s="10"/>
@@ -1911,10 +1937,10 @@
     </row>
     <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B24" s="9" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D24" s="11">
         <v>2.8</v>
@@ -1947,7 +1973,7 @@
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D25" s="11">
         <v>3.1</v>
@@ -1980,7 +2006,7 @@
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D26" s="11">
         <v>3.3</v>
@@ -2013,60 +2039,60 @@
     </row>
     <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C27" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:L1"/>
     <mergeCell ref="M1:Q1"/>
     <mergeCell ref="R1:V1"/>
     <mergeCell ref="W1:AA1"/>
-    <mergeCell ref="D1:E1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2103,7 +2129,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>6</v>
@@ -2117,7 +2143,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -2127,8 +2153,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>253</v>
+      <c r="A5" t="s">
+        <v>247</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
@@ -2145,8 +2171,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>250</v>
+      <c r="A6" t="s">
+        <v>244</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
@@ -2161,8 +2187,8 @@
       <c r="G6" s="7"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>254</v>
+      <c r="A7" t="s">
+        <v>248</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
@@ -2176,7 +2202,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" t="s">
         <v>125</v>
       </c>
       <c r="B8" s="3">
@@ -2212,8 +2238,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>251</v>
+      <c r="A10" t="s">
+        <v>245</v>
       </c>
       <c r="B10" s="3">
         <v>0.05</v>
@@ -2230,8 +2256,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>252</v>
+      <c r="A11" t="s">
+        <v>246</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
@@ -2248,7 +2274,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
+      <c r="A12" t="s">
         <v>123</v>
       </c>
       <c r="B12" s="3">
@@ -2266,7 +2292,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" t="s">
         <v>122</v>
       </c>
       <c r="B13" s="3">
@@ -2303,7 +2329,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>17</v>
@@ -2317,7 +2343,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
@@ -2327,8 +2353,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>253</v>
+      <c r="A18" t="s">
+        <v>247</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
@@ -2345,8 +2371,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>250</v>
+      <c r="A19" t="s">
+        <v>244</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
@@ -2360,8 +2386,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>254</v>
+      <c r="A20" t="s">
+        <v>248</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
@@ -2378,7 +2404,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" t="s">
         <v>125</v>
       </c>
       <c r="B21" s="3">
@@ -2414,8 +2440,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>251</v>
+      <c r="A23" t="s">
+        <v>245</v>
       </c>
       <c r="B23" s="3">
         <v>0.05</v>
@@ -2432,8 +2458,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>252</v>
+      <c r="A24" t="s">
+        <v>246</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
@@ -2450,7 +2476,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+      <c r="A25" t="s">
         <v>123</v>
       </c>
       <c r="B25" s="3">
@@ -2468,7 +2494,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+      <c r="A26" t="s">
         <v>122</v>
       </c>
       <c r="B26" s="3">
@@ -2505,7 +2531,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>22</v>
@@ -2519,7 +2545,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>3</v>
@@ -2529,8 +2555,8 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
-        <v>253</v>
+      <c r="A31" t="s">
+        <v>247</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
@@ -2547,8 +2573,8 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>250</v>
+      <c r="A32" t="s">
+        <v>244</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
@@ -2565,8 +2591,8 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
-        <v>254</v>
+      <c r="A33" t="s">
+        <v>248</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
@@ -2583,7 +2609,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="14" t="s">
+      <c r="A34" t="s">
         <v>125</v>
       </c>
       <c r="B34" s="3">
@@ -2619,8 +2645,8 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="14" t="s">
-        <v>251</v>
+      <c r="A36" t="s">
+        <v>245</v>
       </c>
       <c r="B36" s="3">
         <v>0.05</v>
@@ -2637,8 +2663,8 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
-        <v>252</v>
+      <c r="A37" t="s">
+        <v>246</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
@@ -2655,7 +2681,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="14" t="s">
+      <c r="A38" t="s">
         <v>123</v>
       </c>
       <c r="B38" s="3">
@@ -2673,7 +2699,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
+      <c r="A39" t="s">
         <v>122</v>
       </c>
       <c r="B39" s="3">
@@ -2710,7 +2736,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>40</v>
@@ -2724,7 +2750,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
@@ -2734,60 +2760,72 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
-        <v>253</v>
+      <c r="A44" t="s">
+        <v>247</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
       </c>
+      <c r="C44">
+        <v>3</v>
+      </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="14" t="s">
-        <v>250</v>
+      <c r="A45" t="s">
+        <v>244</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C45">
+        <v>4</v>
       </c>
       <c r="D45">
         <f t="shared" ref="D45:D51" si="3">C45*B45</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="14" t="s">
-        <v>254</v>
+      <c r="A46" t="s">
+        <v>248</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C46">
+        <v>3</v>
       </c>
       <c r="D46">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G46" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
+      <c r="A47" t="s">
         <v>125</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
       </c>
+      <c r="C47">
+        <v>2</v>
+      </c>
       <c r="D47">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>21</v>
@@ -2800,69 +2838,84 @@
       <c r="B48" s="3">
         <v>0.15</v>
       </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
       <c r="D48">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G48" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="14" t="s">
-        <v>251</v>
+      <c r="A49" t="s">
+        <v>245</v>
       </c>
       <c r="B49" s="3">
         <v>0.05</v>
       </c>
+      <c r="C49">
+        <v>3</v>
+      </c>
       <c r="D49">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="14" t="s">
-        <v>252</v>
+      <c r="A50" t="s">
+        <v>246</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
       </c>
+      <c r="C50">
+        <v>3</v>
+      </c>
       <c r="D50">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="14" t="s">
+      <c r="A51" t="s">
         <v>123</v>
       </c>
       <c r="B51" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
       </c>
       <c r="D51">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="14" t="s">
+      <c r="A52" t="s">
         <v>122</v>
       </c>
       <c r="B52" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C52">
+        <v>4</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>48</v>
@@ -2875,7 +2928,7 @@
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>49</v>
@@ -2888,7 +2941,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>50</v>
@@ -2902,7 +2955,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
@@ -2912,60 +2965,72 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
-        <v>253</v>
+      <c r="A57" t="s">
+        <v>247</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
       </c>
+      <c r="C57">
+        <v>3</v>
+      </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="14" t="s">
-        <v>250</v>
+      <c r="A58" t="s">
+        <v>244</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C58">
+        <v>4</v>
       </c>
       <c r="D58">
         <f t="shared" ref="D58:D64" si="4">C58*B58</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="14" t="s">
-        <v>254</v>
+      <c r="A59" t="s">
+        <v>248</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
       </c>
       <c r="D59">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="14" t="s">
+      <c r="A60" t="s">
         <v>125</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
       </c>
+      <c r="C60">
+        <v>3</v>
+      </c>
       <c r="D60">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G60" s="7" t="s">
         <v>22</v>
@@ -2978,69 +3043,84 @@
       <c r="B61" s="3">
         <v>0.15</v>
       </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
       <c r="D61">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G61" s="7" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="14" t="s">
-        <v>251</v>
+      <c r="A62" t="s">
+        <v>245</v>
       </c>
       <c r="B62" s="3">
         <v>0.05</v>
       </c>
+      <c r="C62">
+        <v>3</v>
+      </c>
       <c r="D62">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="14" t="s">
-        <v>252</v>
+      <c r="A63" t="s">
+        <v>246</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
       </c>
+      <c r="C63">
+        <v>3</v>
+      </c>
       <c r="D63">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>56</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="14" t="s">
+      <c r="A64" t="s">
         <v>123</v>
       </c>
       <c r="B64" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C64">
+        <v>4</v>
       </c>
       <c r="D64">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="14" t="s">
+      <c r="A65" t="s">
         <v>122</v>
       </c>
       <c r="B65" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C65">
+        <v>3</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>58</v>
@@ -3053,7 +3133,7 @@
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
-        <v>0</v>
+        <v>3.0999999999999996</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>59</v>
@@ -3066,7 +3146,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>60</v>
@@ -3080,7 +3160,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>3</v>
@@ -3090,60 +3170,72 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="14" t="s">
-        <v>253</v>
+      <c r="A70" t="s">
+        <v>247</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
       </c>
+      <c r="C70">
+        <v>3</v>
+      </c>
       <c r="D70">
         <f>C70*B70</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="14" t="s">
-        <v>250</v>
+      <c r="A71" t="s">
+        <v>244</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C71">
+        <v>3</v>
       </c>
       <c r="D71">
         <f t="shared" ref="D71:D77" si="5">C71*B71</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="14" t="s">
-        <v>254</v>
+      <c r="A72" t="s">
+        <v>248</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C72">
+        <v>3</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="14" t="s">
+      <c r="A73" t="s">
         <v>125</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
       </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
       <c r="D73">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G73" s="7" t="s">
         <v>34</v>
@@ -3156,69 +3248,84 @@
       <c r="B74" s="3">
         <v>0.15</v>
       </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
       <c r="D74">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G74" s="7" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="14" t="s">
-        <v>251</v>
+      <c r="A75" t="s">
+        <v>245</v>
       </c>
       <c r="B75" s="3">
         <v>0.05</v>
       </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
       <c r="D75">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G75" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="14" t="s">
-        <v>252</v>
+      <c r="A76" t="s">
+        <v>246</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
       </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
       <c r="D76">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="14" t="s">
+      <c r="A77" t="s">
         <v>123</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C77">
+        <v>4</v>
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G77" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="14" t="s">
+      <c r="A78" t="s">
         <v>122</v>
       </c>
       <c r="B78" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>59</v>
@@ -3231,7 +3338,7 @@
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
-        <v>0</v>
+        <v>3.0999999999999996</v>
       </c>
       <c r="G79" s="7" t="s">
         <v>34</v>
@@ -3244,7 +3351,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>67</v>
@@ -3258,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>3</v>
@@ -3268,60 +3375,72 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="14" t="s">
-        <v>253</v>
+      <c r="A83" t="s">
+        <v>247</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
       </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="14" t="s">
-        <v>250</v>
+      <c r="A84" t="s">
+        <v>244</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C84">
+        <v>4</v>
       </c>
       <c r="D84">
         <f t="shared" ref="D84:D90" si="6">C84*B84</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G84" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="14" t="s">
-        <v>254</v>
+      <c r="A85" t="s">
+        <v>248</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C85">
+        <v>2</v>
       </c>
       <c r="D85">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G85" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="14" t="s">
+      <c r="A86" t="s">
         <v>125</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
       </c>
+      <c r="C86">
+        <v>2</v>
+      </c>
       <c r="D86">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G86" s="7" t="s">
         <v>69</v>
@@ -3334,69 +3453,84 @@
       <c r="B87" s="3">
         <v>0.15</v>
       </c>
+      <c r="C87">
+        <v>2</v>
+      </c>
       <c r="D87">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="G87" s="7" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="14" t="s">
-        <v>251</v>
+      <c r="A88" t="s">
+        <v>245</v>
       </c>
       <c r="B88" s="3">
         <v>0.05</v>
       </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
       <c r="D88">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G88" s="7" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="14" t="s">
-        <v>252</v>
+      <c r="A89" t="s">
+        <v>246</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
       </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
       <c r="D89">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G89" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="14" t="s">
+      <c r="A90" t="s">
         <v>123</v>
       </c>
       <c r="B90" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C90">
+        <v>4</v>
       </c>
       <c r="D90">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G90" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="14" t="s">
+      <c r="A91" t="s">
         <v>122</v>
       </c>
       <c r="B91" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C91">
+        <v>2</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G91" s="7" t="s">
         <v>34</v>
@@ -3409,7 +3543,7 @@
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>73</v>
@@ -3422,7 +3556,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>75</v>
@@ -3436,7 +3570,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>3</v>
@@ -3446,60 +3580,72 @@
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="14" t="s">
-        <v>253</v>
+      <c r="A96" t="s">
+        <v>247</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
       </c>
+      <c r="C96">
+        <v>3</v>
+      </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G96" s="7" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="14" t="s">
-        <v>250</v>
+      <c r="A97" t="s">
+        <v>244</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C97">
+        <v>4</v>
       </c>
       <c r="D97">
         <f t="shared" ref="D97:D103" si="7">C97*B97</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="G97" s="7" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="14" t="s">
-        <v>254</v>
+      <c r="A98" t="s">
+        <v>248</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C98">
+        <v>2</v>
       </c>
       <c r="D98">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G98" s="7" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="14" t="s">
+      <c r="A99" t="s">
         <v>125</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
       </c>
+      <c r="C99">
+        <v>3</v>
+      </c>
       <c r="D99">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>79</v>
@@ -3512,66 +3658,81 @@
       <c r="B100" s="3">
         <v>0.15</v>
       </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
       <c r="D100">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G100" s="7" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="14" t="s">
-        <v>251</v>
+      <c r="A101" t="s">
+        <v>245</v>
       </c>
       <c r="B101" s="3">
         <v>0.05</v>
       </c>
+      <c r="C101">
+        <v>3</v>
+      </c>
       <c r="D101">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G101" s="7" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="14" t="s">
-        <v>252</v>
+      <c r="A102" t="s">
+        <v>246</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
       </c>
+      <c r="C102">
+        <v>3</v>
+      </c>
       <c r="D102">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G102" s="7" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="14" t="s">
+      <c r="A103" t="s">
         <v>123</v>
       </c>
       <c r="B103" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C103">
+        <v>4</v>
       </c>
       <c r="D103">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="14" t="s">
+      <c r="A104" t="s">
         <v>122</v>
       </c>
       <c r="B104" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C104">
+        <v>3</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G104" s="7" t="s">
         <v>83</v>
@@ -3584,13 +3745,13 @@
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
-        <v>0</v>
+        <v>3.0999999999999996</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -3601,58 +3762,70 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="14" t="s">
-        <v>253</v>
+      <c r="A109" t="s">
+        <v>247</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
       </c>
+      <c r="C109">
+        <v>4</v>
+      </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="14" t="s">
-        <v>250</v>
+      <c r="A110" t="s">
+        <v>244</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C110">
+        <v>4</v>
       </c>
       <c r="D110">
         <f t="shared" ref="D110:D116" si="8">C110*B110</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="14" t="s">
-        <v>254</v>
+      <c r="A111" t="s">
+        <v>248</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C111">
+        <v>3</v>
       </c>
       <c r="D111">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="14" t="s">
+      <c r="A112" t="s">
         <v>125</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
       </c>
+      <c r="C112">
+        <v>2</v>
+      </c>
       <c r="D112">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -3662,57 +3835,72 @@
       <c r="B113" s="3">
         <v>0.15</v>
       </c>
+      <c r="C113">
+        <v>4</v>
+      </c>
       <c r="D113">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="14" t="s">
-        <v>251</v>
+      <c r="A114" t="s">
+        <v>245</v>
       </c>
       <c r="B114" s="3">
         <v>0.05</v>
       </c>
+      <c r="C114">
+        <v>3</v>
+      </c>
       <c r="D114">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="14" t="s">
-        <v>252</v>
+      <c r="A115" t="s">
+        <v>246</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
       </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
       <c r="D115">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.15000000000000002</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="14" t="s">
+      <c r="A116" t="s">
         <v>123</v>
       </c>
       <c r="B116" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C116">
+        <v>4</v>
       </c>
       <c r="D116">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="14" t="s">
+      <c r="A117" t="s">
         <v>122</v>
       </c>
       <c r="B117" s="3">
         <v>0.1</v>
+      </c>
+      <c r="C117">
+        <v>3</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
-        <v>0</v>
+        <v>0.30000000000000004</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3722,7 +3910,7 @@
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
-        <v>0</v>
+        <v>3.4000000000000004</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
@@ -3761,7 +3949,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>6</v>
@@ -3775,7 +3963,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -3785,8 +3973,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>253</v>
+      <c r="A5" t="s">
+        <v>247</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
@@ -3803,8 +3991,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>250</v>
+      <c r="A6" t="s">
+        <v>244</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
@@ -3818,8 +4006,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>254</v>
+      <c r="A7" t="s">
+        <v>248</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
@@ -3836,18 +4024,18 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" t="s">
         <v>125</v>
       </c>
       <c r="B8" s="3">
         <v>0.15</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>10</v>
@@ -3861,83 +4049,83 @@
         <v>0.15</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0.44999999999999996</v>
+        <v>0.3</v>
       </c>
       <c r="G9" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>251</v>
+      <c r="A10" t="s">
+        <v>245</v>
       </c>
       <c r="B10" s="3">
         <v>0.05</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G10" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>252</v>
+      <c r="A11" t="s">
+        <v>246</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
       </c>
       <c r="C11">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G11" s="7" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
+      <c r="A12" t="s">
         <v>123</v>
       </c>
       <c r="B12" s="3">
         <v>0.1</v>
       </c>
       <c r="C12">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" t="s">
         <v>122</v>
       </c>
       <c r="B13" s="3">
         <v>0.1</v>
       </c>
       <c r="C13">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>87</v>
@@ -3950,20 +4138,20 @@
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
-        <v>3.25</v>
+        <v>3.1499999999999995</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>88</v>
@@ -3977,18 +4165,18 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>253</v>
+      <c r="A18" t="s">
+        <v>247</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
@@ -4001,12 +4189,12 @@
         <v>0.8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>250</v>
+      <c r="A19" t="s">
+        <v>244</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
@@ -4023,8 +4211,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>254</v>
+      <c r="A20" t="s">
+        <v>248</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
@@ -4041,18 +4229,18 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" t="s">
         <v>125</v>
       </c>
       <c r="B21" s="3">
         <v>0.15</v>
       </c>
       <c r="C21">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G21" s="7" t="s">
         <v>23</v>
@@ -4073,79 +4261,79 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>251</v>
+      <c r="A23" t="s">
+        <v>245</v>
       </c>
       <c r="B23" s="3">
         <v>0.05</v>
       </c>
       <c r="C23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G23" s="7" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>252</v>
+      <c r="A24" t="s">
+        <v>246</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
       </c>
       <c r="C24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+      <c r="A25" t="s">
         <v>123</v>
       </c>
       <c r="B25" s="3">
         <v>0.1</v>
       </c>
       <c r="C25">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+      <c r="A26" t="s">
         <v>122</v>
       </c>
       <c r="B26" s="3">
         <v>0.1</v>
       </c>
       <c r="C26">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4155,7 +4343,7 @@
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>22</v>
@@ -4168,7 +4356,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>30</v>
@@ -4182,18 +4370,18 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
-        <v>253</v>
+      <c r="A31" t="s">
+        <v>247</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
@@ -4206,30 +4394,30 @@
         <v>0.8</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>250</v>
+      <c r="A32" t="s">
+        <v>244</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
       </c>
       <c r="C32">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D38" si="2">C32*B32</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
-        <v>254</v>
+      <c r="A33" t="s">
+        <v>248</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
@@ -4246,21 +4434,21 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="14" t="s">
+      <c r="A34" t="s">
         <v>125</v>
       </c>
       <c r="B34" s="3">
         <v>0.15</v>
       </c>
       <c r="C34">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D34">
         <f t="shared" si="2"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -4282,72 +4470,72 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="14" t="s">
-        <v>251</v>
+      <c r="A36" t="s">
+        <v>245</v>
       </c>
       <c r="B36" s="3">
         <v>0.05</v>
       </c>
       <c r="C36">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D36">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
-        <v>252</v>
+      <c r="A37" t="s">
+        <v>246</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
       </c>
       <c r="C37">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D37">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="14" t="s">
+      <c r="A38" t="s">
         <v>123</v>
       </c>
       <c r="B38" s="3">
         <v>0.1</v>
       </c>
       <c r="C38">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D38">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
+      <c r="A39" t="s">
         <v>122</v>
       </c>
       <c r="B39" s="3">
         <v>0.1</v>
       </c>
       <c r="C39">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>39</v>
@@ -4360,10 +4548,10 @@
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
-        <v>3.25</v>
+        <v>3.1999999999999993</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -4373,10 +4561,10 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -4387,54 +4575,54 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
-        <v>253</v>
+      <c r="A44" t="s">
+        <v>247</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
       </c>
       <c r="C44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="14" t="s">
-        <v>250</v>
+      <c r="A45" t="s">
+        <v>244</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
       </c>
       <c r="C45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D45">
         <f t="shared" ref="D45:D51" si="3">C45*B45</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G45" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="14" t="s">
-        <v>254</v>
+      <c r="A46" t="s">
+        <v>248</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
@@ -4451,18 +4639,18 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
+      <c r="A47" t="s">
         <v>125</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
       </c>
       <c r="C47">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D47">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G47" s="7" t="s">
         <v>45</v>
@@ -4487,43 +4675,43 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="14" t="s">
-        <v>251</v>
+      <c r="A49" t="s">
+        <v>245</v>
       </c>
       <c r="B49" s="3">
         <v>0.05</v>
       </c>
       <c r="C49">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D49">
         <f t="shared" si="3"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="14" t="s">
-        <v>252</v>
+      <c r="A50" t="s">
+        <v>246</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
       </c>
       <c r="C50">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D50">
         <f t="shared" si="3"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="14" t="s">
+      <c r="A51" t="s">
         <v>123</v>
       </c>
       <c r="B51" s="3">
@@ -4537,22 +4725,22 @@
         <v>0.4</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="14" t="s">
+      <c r="A52" t="s">
         <v>122</v>
       </c>
       <c r="B52" s="3">
         <v>0.1</v>
       </c>
       <c r="C52">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>34</v>
@@ -4565,7 +4753,7 @@
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
-        <v>3.25</v>
+        <v>3.0999999999999996</v>
       </c>
       <c r="G53" s="7" t="s">
         <v>50</v>
@@ -4573,15 +4761,15 @@
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -4592,54 +4780,54 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
-        <v>253</v>
+      <c r="A57" t="s">
+        <v>247</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
       </c>
       <c r="C57">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="14" t="s">
-        <v>250</v>
+      <c r="A58" t="s">
+        <v>244</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
       </c>
       <c r="C58">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D58">
         <f t="shared" ref="D58:D64" si="4">C58*B58</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G58" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="14" t="s">
-        <v>254</v>
+      <c r="A59" t="s">
+        <v>248</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
@@ -4656,21 +4844,21 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="14" t="s">
+      <c r="A60" t="s">
         <v>125</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
       </c>
       <c r="C60">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D60">
         <f t="shared" si="4"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -4688,47 +4876,47 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="14" t="s">
-        <v>251</v>
+      <c r="A62" t="s">
+        <v>245</v>
       </c>
       <c r="B62" s="3">
         <v>0.05</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D62">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="14" t="s">
-        <v>252</v>
+      <c r="A63" t="s">
+        <v>246</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D63">
         <f t="shared" si="4"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="14" t="s">
+      <c r="A64" t="s">
         <v>123</v>
       </c>
       <c r="B64" s="3">
@@ -4746,7 +4934,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="14" t="s">
+      <c r="A65" t="s">
         <v>122</v>
       </c>
       <c r="B65" s="3">
@@ -4770,7 +4958,7 @@
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
-        <v>3.25</v>
+        <v>3.1999999999999997</v>
       </c>
       <c r="G66" s="7" t="s">
         <v>98</v>
@@ -4778,15 +4966,15 @@
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -4797,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>3</v>
@@ -4807,8 +4995,8 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="14" t="s">
-        <v>253</v>
+      <c r="A70" t="s">
+        <v>247</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
@@ -4825,57 +5013,57 @@
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="14" t="s">
-        <v>250</v>
+      <c r="A71" t="s">
+        <v>244</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
       </c>
       <c r="C71">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D71">
         <f t="shared" ref="D71:D77" si="5">C71*B71</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="G71" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="14" t="s">
-        <v>254</v>
+      <c r="A72" t="s">
+        <v>248</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
       </c>
       <c r="C72">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
-        <v>0.30000000000000004</v>
+        <v>0.4</v>
       </c>
       <c r="G72" s="7" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="14" t="s">
+      <c r="A73" t="s">
         <v>125</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
       </c>
       <c r="C73">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D73">
         <f t="shared" si="5"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
@@ -4893,47 +5081,47 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="14" t="s">
-        <v>251</v>
+      <c r="A75" t="s">
+        <v>245</v>
       </c>
       <c r="B75" s="3">
         <v>0.05</v>
       </c>
       <c r="C75">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D75">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G75" s="7" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="14" t="s">
-        <v>252</v>
+      <c r="A76" t="s">
+        <v>246</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
       </c>
       <c r="C76">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D76">
         <f t="shared" si="5"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G76" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="14" t="s">
+      <c r="A77" t="s">
         <v>123</v>
       </c>
       <c r="B77" s="3">
@@ -4951,18 +5139,18 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="14" t="s">
+      <c r="A78" t="s">
         <v>122</v>
       </c>
       <c r="B78" s="3">
         <v>0.1</v>
       </c>
       <c r="C78">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>55</v>
@@ -4975,20 +5163,20 @@
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G80" s="7" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>72</v>
@@ -5002,7 +5190,7 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>3</v>
@@ -5012,26 +5200,26 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="14" t="s">
-        <v>253</v>
+      <c r="A83" t="s">
+        <v>247</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G83" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="14" t="s">
-        <v>250</v>
+      <c r="A84" t="s">
+        <v>244</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
@@ -5048,8 +5236,8 @@
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="14" t="s">
-        <v>254</v>
+      <c r="A85" t="s">
+        <v>248</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
@@ -5062,25 +5250,25 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="14" t="s">
+      <c r="A86" t="s">
         <v>125</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
       </c>
       <c r="C86">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D86">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -5102,43 +5290,43 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="14" t="s">
-        <v>251</v>
+      <c r="A88" t="s">
+        <v>245</v>
       </c>
       <c r="B88" s="3">
         <v>0.05</v>
       </c>
       <c r="C88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D88">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G88" s="7" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="14" t="s">
-        <v>252</v>
+      <c r="A89" t="s">
+        <v>246</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
       </c>
       <c r="C89">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D89">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G89" s="7" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="14" t="s">
+      <c r="A90" t="s">
         <v>123</v>
       </c>
       <c r="B90" s="3">
@@ -5152,25 +5340,25 @@
         <v>0.4</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="14" t="s">
+      <c r="A91" t="s">
         <v>122</v>
       </c>
       <c r="B91" s="3">
         <v>0.1</v>
       </c>
       <c r="C91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5180,10 +5368,10 @@
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -5193,7 +5381,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>59</v>
@@ -5207,7 +5395,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>3</v>
@@ -5217,26 +5405,26 @@
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="14" t="s">
-        <v>253</v>
+      <c r="A96" t="s">
+        <v>247</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
       </c>
       <c r="C96">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
       <c r="G96" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A97" s="14" t="s">
-        <v>250</v>
+      <c r="A97" t="s">
+        <v>244</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
@@ -5249,12 +5437,12 @@
         <v>0.4</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A98" s="14" t="s">
-        <v>254</v>
+      <c r="A98" t="s">
+        <v>248</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
@@ -5271,18 +5459,18 @@
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A99" s="14" t="s">
+      <c r="A99" t="s">
         <v>125</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
       </c>
       <c r="C99">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D99">
         <f t="shared" si="7"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
       <c r="G99" s="7" t="s">
         <v>22</v>
@@ -5307,43 +5495,43 @@
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A101" s="14" t="s">
-        <v>251</v>
+      <c r="A101" t="s">
+        <v>245</v>
       </c>
       <c r="B101" s="3">
         <v>0.05</v>
       </c>
       <c r="C101">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D101">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A102" s="14" t="s">
-        <v>252</v>
+      <c r="A102" t="s">
+        <v>246</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
       </c>
       <c r="C102">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D102">
         <f t="shared" si="7"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
       <c r="G102" s="7" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A103" s="14" t="s">
+      <c r="A103" t="s">
         <v>123</v>
       </c>
       <c r="B103" s="3">
@@ -5361,21 +5549,21 @@
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A104" s="14" t="s">
+      <c r="A104" t="s">
         <v>122</v>
       </c>
       <c r="B104" s="3">
         <v>0.1</v>
       </c>
       <c r="C104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
-        <v>0.4</v>
+        <v>0.30000000000000004</v>
       </c>
       <c r="G104" s="7" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5385,7 +5573,7 @@
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G105" s="7" t="s">
         <v>81</v>
@@ -5398,7 +5586,7 @@
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -5409,7 +5597,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>3</v>
@@ -5419,23 +5607,23 @@
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A109" s="14" t="s">
-        <v>253</v>
+      <c r="A109" t="s">
+        <v>247</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
       </c>
       <c r="C109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0.8</v>
+        <v>0.60000000000000009</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A110" s="14" t="s">
-        <v>250</v>
+      <c r="A110" t="s">
+        <v>244</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
@@ -5449,8 +5637,8 @@
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A111" s="14" t="s">
-        <v>254</v>
+      <c r="A111" t="s">
+        <v>248</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
@@ -5464,18 +5652,18 @@
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A112" s="14" t="s">
+      <c r="A112" t="s">
         <v>125</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
       </c>
       <c r="C112">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D112">
         <f t="shared" si="8"/>
-        <v>0.3</v>
+        <v>0.44999999999999996</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
@@ -5494,23 +5682,23 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="14" t="s">
-        <v>251</v>
+      <c r="A114" t="s">
+        <v>245</v>
       </c>
       <c r="B114" s="3">
         <v>0.05</v>
       </c>
       <c r="C114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D114">
         <f t="shared" si="8"/>
-        <v>0.1</v>
+        <v>0.15000000000000002</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="14" t="s">
-        <v>252</v>
+      <c r="A115" t="s">
+        <v>246</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
@@ -5524,7 +5712,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="14" t="s">
+      <c r="A116" t="s">
         <v>123</v>
       </c>
       <c r="B116" s="3">
@@ -5539,7 +5727,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="14" t="s">
+      <c r="A117" t="s">
         <v>122</v>
       </c>
       <c r="B117" s="3">
@@ -5599,7 +5787,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>10</v>
@@ -5613,7 +5801,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
@@ -5623,8 +5811,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>253</v>
+      <c r="A5" t="s">
+        <v>247</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
@@ -5641,8 +5829,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>250</v>
+      <c r="A6" t="s">
+        <v>244</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
@@ -5659,8 +5847,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>254</v>
+      <c r="A7" t="s">
+        <v>248</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
@@ -5677,7 +5865,7 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" t="s">
         <v>125</v>
       </c>
       <c r="B8" s="3">
@@ -5713,8 +5901,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>251</v>
+      <c r="A10" t="s">
+        <v>245</v>
       </c>
       <c r="B10" s="3">
         <v>0.05</v>
@@ -5731,8 +5919,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>252</v>
+      <c r="A11" t="s">
+        <v>246</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
@@ -5749,7 +5937,7 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
+      <c r="A12" t="s">
         <v>123</v>
       </c>
       <c r="B12" s="3">
@@ -5767,7 +5955,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" t="s">
         <v>122</v>
       </c>
       <c r="B13" s="3">
@@ -5804,7 +5992,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>22</v>
@@ -5818,7 +6006,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
@@ -5828,8 +6016,8 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>253</v>
+      <c r="A18" t="s">
+        <v>247</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
@@ -5846,8 +6034,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>250</v>
+      <c r="A19" t="s">
+        <v>244</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
@@ -5864,8 +6052,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>254</v>
+      <c r="A20" t="s">
+        <v>248</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
@@ -5882,7 +6070,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" t="s">
         <v>125</v>
       </c>
       <c r="B21" s="3">
@@ -5918,8 +6106,8 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>251</v>
+      <c r="A23" t="s">
+        <v>245</v>
       </c>
       <c r="B23" s="3">
         <v>0.05</v>
@@ -5936,8 +6124,8 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>252</v>
+      <c r="A24" t="s">
+        <v>246</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
@@ -5954,7 +6142,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+      <c r="A25" t="s">
         <v>123</v>
       </c>
       <c r="B25" s="3">
@@ -5972,7 +6160,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+      <c r="A26" t="s">
         <v>122</v>
       </c>
       <c r="B26" s="3">
@@ -6009,7 +6197,7 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G29" s="7" t="s">
         <v>91</v>
@@ -6023,7 +6211,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>3</v>
@@ -6033,8 +6221,8 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
-        <v>253</v>
+      <c r="A31" t="s">
+        <v>247</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
@@ -6051,8 +6239,8 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>250</v>
+      <c r="A32" t="s">
+        <v>244</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
@@ -6069,8 +6257,8 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
-        <v>254</v>
+      <c r="A33" t="s">
+        <v>248</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
@@ -6087,7 +6275,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="14" t="s">
+      <c r="A34" t="s">
         <v>125</v>
       </c>
       <c r="B34" s="3">
@@ -6123,8 +6311,8 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="14" t="s">
-        <v>251</v>
+      <c r="A36" t="s">
+        <v>245</v>
       </c>
       <c r="B36" s="3">
         <v>0.05</v>
@@ -6141,8 +6329,8 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
-        <v>252</v>
+      <c r="A37" t="s">
+        <v>246</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
@@ -6159,7 +6347,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="14" t="s">
+      <c r="A38" t="s">
         <v>123</v>
       </c>
       <c r="B38" s="3">
@@ -6177,7 +6365,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
+      <c r="A39" t="s">
         <v>122</v>
       </c>
       <c r="B39" s="3">
@@ -6214,7 +6402,7 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G42" s="7" t="s">
         <v>60</v>
@@ -6228,7 +6416,7 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
@@ -6238,8 +6426,8 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
-        <v>253</v>
+      <c r="A44" t="s">
+        <v>247</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
@@ -6256,8 +6444,8 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="14" t="s">
-        <v>250</v>
+      <c r="A45" t="s">
+        <v>244</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
@@ -6274,8 +6462,8 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="14" t="s">
-        <v>254</v>
+      <c r="A46" t="s">
+        <v>248</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
@@ -6292,7 +6480,7 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
+      <c r="A47" t="s">
         <v>125</v>
       </c>
       <c r="B47" s="3">
@@ -6328,8 +6516,8 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="14" t="s">
-        <v>251</v>
+      <c r="A49" t="s">
+        <v>245</v>
       </c>
       <c r="B49" s="3">
         <v>0.05</v>
@@ -6346,8 +6534,8 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="14" t="s">
-        <v>252</v>
+      <c r="A50" t="s">
+        <v>246</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
@@ -6364,7 +6552,7 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="14" t="s">
+      <c r="A51" t="s">
         <v>123</v>
       </c>
       <c r="B51" s="3">
@@ -6382,7 +6570,7 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="14" t="s">
+      <c r="A52" t="s">
         <v>122</v>
       </c>
       <c r="B52" s="3">
@@ -6419,7 +6607,7 @@
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G55" s="7" t="s">
         <v>119</v>
@@ -6433,7 +6621,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
@@ -6443,8 +6631,8 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
-        <v>253</v>
+      <c r="A57" t="s">
+        <v>247</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
@@ -6461,8 +6649,8 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="14" t="s">
-        <v>250</v>
+      <c r="A58" t="s">
+        <v>244</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
@@ -6479,8 +6667,8 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="14" t="s">
-        <v>254</v>
+      <c r="A59" t="s">
+        <v>248</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
@@ -6497,7 +6685,7 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="14" t="s">
+      <c r="A60" t="s">
         <v>125</v>
       </c>
       <c r="B60" s="3">
@@ -6533,8 +6721,8 @@
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="14" t="s">
-        <v>251</v>
+      <c r="A62" t="s">
+        <v>245</v>
       </c>
       <c r="B62" s="3">
         <v>0.05</v>
@@ -6551,8 +6739,8 @@
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="14" t="s">
-        <v>252</v>
+      <c r="A63" t="s">
+        <v>246</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
@@ -6569,7 +6757,7 @@
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="14" t="s">
+      <c r="A64" t="s">
         <v>123</v>
       </c>
       <c r="B64" s="3">
@@ -6587,7 +6775,7 @@
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="14" t="s">
+      <c r="A65" t="s">
         <v>122</v>
       </c>
       <c r="B65" s="3">
@@ -6621,7 +6809,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G68" s="7" t="s">
         <v>101</v>
@@ -6635,15 +6823,15 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="14" t="s">
-        <v>253</v>
+      <c r="A70" t="s">
+        <v>247</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
@@ -6660,8 +6848,8 @@
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="14" t="s">
-        <v>250</v>
+      <c r="A71" t="s">
+        <v>244</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
@@ -6678,8 +6866,8 @@
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="14" t="s">
-        <v>254</v>
+      <c r="A72" t="s">
+        <v>248</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
@@ -6696,7 +6884,7 @@
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="14" t="s">
+      <c r="A73" t="s">
         <v>125</v>
       </c>
       <c r="B73" s="3">
@@ -6732,8 +6920,8 @@
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="14" t="s">
-        <v>251</v>
+      <c r="A75" t="s">
+        <v>245</v>
       </c>
       <c r="B75" s="3">
         <v>0.05</v>
@@ -6747,8 +6935,8 @@
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="14" t="s">
-        <v>252</v>
+      <c r="A76" t="s">
+        <v>246</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
@@ -6765,7 +6953,7 @@
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="14" t="s">
+      <c r="A77" t="s">
         <v>123</v>
       </c>
       <c r="B77" s="3">
@@ -6783,7 +6971,7 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="14" t="s">
+      <c r="A78" t="s">
         <v>122</v>
       </c>
       <c r="B78" s="3">
@@ -6815,7 +7003,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G81" s="7"/>
     </row>
@@ -6827,7 +7015,7 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>3</v>
@@ -6835,8 +7023,8 @@
       <c r="G82" s="7"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="14" t="s">
-        <v>253</v>
+      <c r="A83" t="s">
+        <v>247</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
@@ -6850,8 +7038,8 @@
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="14" t="s">
-        <v>250</v>
+      <c r="A84" t="s">
+        <v>244</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
@@ -6865,8 +7053,8 @@
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="14" t="s">
-        <v>254</v>
+      <c r="A85" t="s">
+        <v>248</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
@@ -6880,7 +7068,7 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="14" t="s">
+      <c r="A86" t="s">
         <v>125</v>
       </c>
       <c r="B86" s="3">
@@ -6910,8 +7098,8 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="14" t="s">
-        <v>251</v>
+      <c r="A88" t="s">
+        <v>245</v>
       </c>
       <c r="B88" s="3">
         <v>0.05</v>
@@ -6925,8 +7113,8 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="14" t="s">
-        <v>252</v>
+      <c r="A89" t="s">
+        <v>246</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
@@ -6940,7 +7128,7 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="14" t="s">
+      <c r="A90" t="s">
         <v>123</v>
       </c>
       <c r="B90" s="3">
@@ -6955,7 +7143,7 @@
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="14" t="s">
+      <c r="A91" t="s">
         <v>122</v>
       </c>
       <c r="B91" s="3">
@@ -6982,7 +7170,7 @@
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -6993,15 +7181,15 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="14" t="s">
-        <v>253</v>
+      <c r="A96" t="s">
+        <v>247</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
@@ -7015,8 +7203,8 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="14" t="s">
-        <v>250</v>
+      <c r="A97" t="s">
+        <v>244</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
@@ -7030,8 +7218,8 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="14" t="s">
-        <v>254</v>
+      <c r="A98" t="s">
+        <v>248</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
@@ -7045,7 +7233,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="14" t="s">
+      <c r="A99" t="s">
         <v>125</v>
       </c>
       <c r="B99" s="3">
@@ -7075,8 +7263,8 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="14" t="s">
-        <v>251</v>
+      <c r="A101" t="s">
+        <v>245</v>
       </c>
       <c r="B101" s="3">
         <v>0.05</v>
@@ -7090,8 +7278,8 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="14" t="s">
-        <v>252</v>
+      <c r="A102" t="s">
+        <v>246</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
@@ -7105,7 +7293,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="14" t="s">
+      <c r="A103" t="s">
         <v>123</v>
       </c>
       <c r="B103" s="3">
@@ -7120,7 +7308,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="14" t="s">
+      <c r="A104" t="s">
         <v>122</v>
       </c>
       <c r="B104" s="3">
@@ -7147,7 +7335,7 @@
     <row r="106" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -7158,15 +7346,15 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="14" t="s">
-        <v>253</v>
+      <c r="A109" t="s">
+        <v>247</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
@@ -7180,8 +7368,8 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="14" t="s">
-        <v>250</v>
+      <c r="A110" t="s">
+        <v>244</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
@@ -7195,8 +7383,8 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="14" t="s">
-        <v>254</v>
+      <c r="A111" t="s">
+        <v>248</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
@@ -7210,7 +7398,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="14" t="s">
+      <c r="A112" t="s">
         <v>125</v>
       </c>
       <c r="B112" s="3">
@@ -7240,8 +7428,8 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="14" t="s">
-        <v>251</v>
+      <c r="A114" t="s">
+        <v>245</v>
       </c>
       <c r="B114" s="3">
         <v>0.05</v>
@@ -7255,8 +7443,8 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="14" t="s">
-        <v>252</v>
+      <c r="A115" t="s">
+        <v>246</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
@@ -7270,7 +7458,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="14" t="s">
+      <c r="A116" t="s">
         <v>123</v>
       </c>
       <c r="B116" s="3">
@@ -7285,7 +7473,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="14" t="s">
+      <c r="A117" t="s">
         <v>122</v>
       </c>
       <c r="B117" s="3">
@@ -7340,12 +7528,12 @@
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>10</v>
@@ -7359,18 +7547,18 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
-        <v>253</v>
+      <c r="A5" t="s">
+        <v>247</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
@@ -7383,12 +7571,12 @@
         <v>0.8</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="14" t="s">
-        <v>250</v>
+      <c r="A6" t="s">
+        <v>244</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
@@ -7401,12 +7589,12 @@
         <v>0.4</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
-        <v>254</v>
+      <c r="A7" t="s">
+        <v>248</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
@@ -7419,11 +7607,11 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="14" t="s">
+      <c r="A8" t="s">
         <v>125</v>
       </c>
       <c r="B8" s="3">
@@ -7437,7 +7625,7 @@
         <v>0.3</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -7455,12 +7643,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="14" t="s">
-        <v>251</v>
+      <c r="A10" t="s">
+        <v>245</v>
       </c>
       <c r="B10" s="3">
         <v>0.05</v>
@@ -7473,12 +7661,12 @@
         <v>0.1</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
-        <v>252</v>
+      <c r="A11" t="s">
+        <v>246</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
@@ -7491,11 +7679,11 @@
         <v>0.1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="14" t="s">
+      <c r="A12" t="s">
         <v>123</v>
       </c>
       <c r="B12" s="3">
@@ -7509,11 +7697,11 @@
         <v>0.4</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+      <c r="A13" t="s">
         <v>122</v>
       </c>
       <c r="B13" s="3">
@@ -7527,7 +7715,7 @@
         <v>0.4</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7540,20 +7728,20 @@
         <v>3.25</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -7564,18 +7752,18 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="14" t="s">
-        <v>253</v>
+      <c r="A18" t="s">
+        <v>247</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
@@ -7588,12 +7776,12 @@
         <v>0.8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
-        <v>250</v>
+      <c r="A19" t="s">
+        <v>244</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
@@ -7606,12 +7794,12 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A20" s="14" t="s">
-        <v>254</v>
+      <c r="A20" t="s">
+        <v>248</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
@@ -7624,11 +7812,11 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+      <c r="A21" t="s">
         <v>125</v>
       </c>
       <c r="B21" s="3">
@@ -7642,7 +7830,7 @@
         <v>0.3</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
@@ -7660,12 +7848,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
-        <v>251</v>
+      <c r="A23" t="s">
+        <v>245</v>
       </c>
       <c r="B23" s="3">
         <v>0.05</v>
@@ -7678,12 +7866,12 @@
         <v>0.1</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="14" t="s">
-        <v>252</v>
+      <c r="A24" t="s">
+        <v>246</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
@@ -7696,11 +7884,11 @@
         <v>0.1</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+      <c r="A25" t="s">
         <v>123</v>
       </c>
       <c r="B25" s="3">
@@ -7714,11 +7902,11 @@
         <v>0.4</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="14" t="s">
+      <c r="A26" t="s">
         <v>122</v>
       </c>
       <c r="B26" s="3">
@@ -7732,7 +7920,7 @@
         <v>0.4</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7745,20 +7933,20 @@
         <v>3.25</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G28" s="7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -7769,18 +7957,18 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
-        <v>253</v>
+      <c r="A31" t="s">
+        <v>247</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
@@ -7793,12 +7981,12 @@
         <v>0.8</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A32" s="14" t="s">
-        <v>250</v>
+      <c r="A32" t="s">
+        <v>244</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
@@ -7811,12 +7999,12 @@
         <v>0.4</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
-        <v>254</v>
+      <c r="A33" t="s">
+        <v>248</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
@@ -7829,11 +8017,11 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="14" t="s">
+      <c r="A34" t="s">
         <v>125</v>
       </c>
       <c r="B34" s="3">
@@ -7847,7 +8035,7 @@
         <v>0.3</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -7865,12 +8053,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A36" s="14" t="s">
-        <v>251</v>
+      <c r="A36" t="s">
+        <v>245</v>
       </c>
       <c r="B36" s="3">
         <v>0.05</v>
@@ -7883,12 +8071,12 @@
         <v>0.1</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
-        <v>252</v>
+      <c r="A37" t="s">
+        <v>246</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
@@ -7901,11 +8089,11 @@
         <v>0.1</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="14" t="s">
+      <c r="A38" t="s">
         <v>123</v>
       </c>
       <c r="B38" s="3">
@@ -7919,11 +8107,11 @@
         <v>0.4</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
+      <c r="A39" t="s">
         <v>122</v>
       </c>
       <c r="B39" s="3">
@@ -7937,7 +8125,7 @@
         <v>0.4</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7950,20 +8138,20 @@
         <v>3.25</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -7974,18 +8162,18 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="14" t="s">
-        <v>253</v>
+      <c r="A44" t="s">
+        <v>247</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
@@ -7998,12 +8186,12 @@
         <v>0.8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="14" t="s">
-        <v>250</v>
+      <c r="A45" t="s">
+        <v>244</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
@@ -8016,12 +8204,12 @@
         <v>0.4</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="14" t="s">
-        <v>254</v>
+      <c r="A46" t="s">
+        <v>248</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
@@ -8034,11 +8222,11 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
+      <c r="A47" t="s">
         <v>125</v>
       </c>
       <c r="B47" s="3">
@@ -8052,7 +8240,7 @@
         <v>0.3</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
@@ -8070,12 +8258,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A49" s="14" t="s">
-        <v>251</v>
+      <c r="A49" t="s">
+        <v>245</v>
       </c>
       <c r="B49" s="3">
         <v>0.05</v>
@@ -8088,12 +8276,12 @@
         <v>0.1</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A50" s="14" t="s">
-        <v>252</v>
+      <c r="A50" t="s">
+        <v>246</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
@@ -8106,11 +8294,11 @@
         <v>0.1</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A51" s="14" t="s">
+      <c r="A51" t="s">
         <v>123</v>
       </c>
       <c r="B51" s="3">
@@ -8124,11 +8312,11 @@
         <v>0.4</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A52" s="14" t="s">
+      <c r="A52" t="s">
         <v>122</v>
       </c>
       <c r="B52" s="3">
@@ -8142,7 +8330,7 @@
         <v>0.4</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8155,20 +8343,20 @@
         <v>3.25</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -8179,18 +8367,18 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
-        <v>253</v>
+      <c r="A57" t="s">
+        <v>247</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
@@ -8203,12 +8391,12 @@
         <v>0.8</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A58" s="14" t="s">
-        <v>250</v>
+      <c r="A58" t="s">
+        <v>244</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
@@ -8221,12 +8409,12 @@
         <v>0.4</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A59" s="14" t="s">
-        <v>254</v>
+      <c r="A59" t="s">
+        <v>248</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
@@ -8239,11 +8427,11 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A60" s="14" t="s">
+      <c r="A60" t="s">
         <v>125</v>
       </c>
       <c r="B60" s="3">
@@ -8257,7 +8445,7 @@
         <v>0.3</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
@@ -8275,12 +8463,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A62" s="14" t="s">
-        <v>251</v>
+      <c r="A62" t="s">
+        <v>245</v>
       </c>
       <c r="B62" s="3">
         <v>0.05</v>
@@ -8293,12 +8481,12 @@
         <v>0.1</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A63" s="14" t="s">
-        <v>252</v>
+      <c r="A63" t="s">
+        <v>246</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
@@ -8311,11 +8499,11 @@
         <v>0.1</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A64" s="14" t="s">
+      <c r="A64" t="s">
         <v>123</v>
       </c>
       <c r="B64" s="3">
@@ -8329,11 +8517,11 @@
         <v>0.4</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A65" s="14" t="s">
+      <c r="A65" t="s">
         <v>122</v>
       </c>
       <c r="B65" s="3">
@@ -8347,7 +8535,7 @@
         <v>0.4</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8360,20 +8548,20 @@
         <v>3.25</v>
       </c>
       <c r="G66" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -8384,7 +8572,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>3</v>
@@ -8394,8 +8582,8 @@
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A70" s="14" t="s">
-        <v>253</v>
+      <c r="A70" t="s">
+        <v>247</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
@@ -8410,8 +8598,8 @@
       <c r="G70" s="7"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A71" s="14" t="s">
-        <v>250</v>
+      <c r="A71" t="s">
+        <v>244</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
@@ -8424,12 +8612,12 @@
         <v>0.4</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A72" s="14" t="s">
-        <v>254</v>
+      <c r="A72" t="s">
+        <v>248</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
@@ -8442,11 +8630,11 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A73" s="14" t="s">
+      <c r="A73" t="s">
         <v>125</v>
       </c>
       <c r="B73" s="3">
@@ -8480,8 +8668,8 @@
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A75" s="14" t="s">
-        <v>251</v>
+      <c r="A75" t="s">
+        <v>245</v>
       </c>
       <c r="B75" s="3">
         <v>0.05</v>
@@ -8498,8 +8686,8 @@
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A76" s="14" t="s">
-        <v>252</v>
+      <c r="A76" t="s">
+        <v>246</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
@@ -8516,7 +8704,7 @@
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A77" s="14" t="s">
+      <c r="A77" t="s">
         <v>123</v>
       </c>
       <c r="B77" s="3">
@@ -8534,7 +8722,7 @@
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A78" s="14" t="s">
+      <c r="A78" t="s">
         <v>122</v>
       </c>
       <c r="B78" s="3">
@@ -8548,7 +8736,7 @@
         <v>0.4</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8568,7 +8756,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="G81" s="7" t="s">
         <v>108</v>
@@ -8582,7 +8770,7 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>3</v>
@@ -8592,8 +8780,8 @@
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A83" s="14" t="s">
-        <v>253</v>
+      <c r="A83" t="s">
+        <v>247</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
@@ -8607,8 +8795,8 @@
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A84" s="14" t="s">
-        <v>250</v>
+      <c r="A84" t="s">
+        <v>244</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
@@ -8622,8 +8810,8 @@
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A85" s="14" t="s">
-        <v>254</v>
+      <c r="A85" t="s">
+        <v>248</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
@@ -8637,7 +8825,7 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A86" s="14" t="s">
+      <c r="A86" t="s">
         <v>125</v>
       </c>
       <c r="B86" s="3">
@@ -8667,8 +8855,8 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A88" s="14" t="s">
-        <v>251</v>
+      <c r="A88" t="s">
+        <v>245</v>
       </c>
       <c r="B88" s="3">
         <v>0.05</v>
@@ -8682,8 +8870,8 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A89" s="14" t="s">
-        <v>252</v>
+      <c r="A89" t="s">
+        <v>246</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
@@ -8697,7 +8885,7 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A90" s="14" t="s">
+      <c r="A90" t="s">
         <v>123</v>
       </c>
       <c r="B90" s="3">
@@ -8712,7 +8900,7 @@
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A91" s="14" t="s">
+      <c r="A91" t="s">
         <v>122</v>
       </c>
       <c r="B91" s="3">
@@ -8739,7 +8927,7 @@
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -8750,15 +8938,15 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A96" s="14" t="s">
-        <v>253</v>
+      <c r="A96" t="s">
+        <v>247</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
@@ -8772,8 +8960,8 @@
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A97" s="14" t="s">
-        <v>250</v>
+      <c r="A97" t="s">
+        <v>244</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
@@ -8787,8 +8975,8 @@
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A98" s="14" t="s">
-        <v>254</v>
+      <c r="A98" t="s">
+        <v>248</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
@@ -8802,7 +8990,7 @@
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A99" s="14" t="s">
+      <c r="A99" t="s">
         <v>125</v>
       </c>
       <c r="B99" s="3">
@@ -8832,8 +9020,8 @@
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A101" s="14" t="s">
-        <v>251</v>
+      <c r="A101" t="s">
+        <v>245</v>
       </c>
       <c r="B101" s="3">
         <v>0.05</v>
@@ -8847,8 +9035,8 @@
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A102" s="14" t="s">
-        <v>252</v>
+      <c r="A102" t="s">
+        <v>246</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
@@ -8862,7 +9050,7 @@
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A103" s="14" t="s">
+      <c r="A103" t="s">
         <v>123</v>
       </c>
       <c r="B103" s="3">
@@ -8877,7 +9065,7 @@
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A104" s="14" t="s">
+      <c r="A104" t="s">
         <v>122</v>
       </c>
       <c r="B104" s="3">
@@ -8904,7 +9092,7 @@
     <row r="106" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -8915,15 +9103,15 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A109" s="14" t="s">
-        <v>253</v>
+      <c r="A109" t="s">
+        <v>247</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
@@ -8937,8 +9125,8 @@
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A110" s="14" t="s">
-        <v>250</v>
+      <c r="A110" t="s">
+        <v>244</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
@@ -8952,8 +9140,8 @@
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A111" s="14" t="s">
-        <v>254</v>
+      <c r="A111" t="s">
+        <v>248</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
@@ -8967,7 +9155,7 @@
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A112" s="14" t="s">
+      <c r="A112" t="s">
         <v>125</v>
       </c>
       <c r="B112" s="3">
@@ -8997,8 +9185,8 @@
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A114" s="14" t="s">
-        <v>251</v>
+      <c r="A114" t="s">
+        <v>245</v>
       </c>
       <c r="B114" s="3">
         <v>0.05</v>
@@ -9012,8 +9200,8 @@
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A115" s="14" t="s">
-        <v>252</v>
+      <c r="A115" t="s">
+        <v>246</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
@@ -9027,7 +9215,7 @@
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A116" s="14" t="s">
+      <c r="A116" t="s">
         <v>123</v>
       </c>
       <c r="B116" s="3">
@@ -9042,7 +9230,7 @@
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A117" s="14" t="s">
+      <c r="A117" t="s">
         <v>122</v>
       </c>
       <c r="B117" s="3">

--- a/Evaluation_Schema.xlsx
+++ b/Evaluation_Schema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kim_W\Ekkono_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EB0217-A1E9-4B8E-A328-82A06CC9DE18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EDBAC4-EF67-43B1-AAD2-895C3127530A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation Table" sheetId="3" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="943" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="282">
   <si>
     <t>Metric</t>
   </si>
@@ -46,21 +46,6 @@
     <t xml:space="preserve">Max Score: </t>
   </si>
   <si>
-    <t>Provide an easy explanation on why the following Weather Station is classified as an outlier that an engineer working with the Weather Station can understand. </t>
-  </si>
-  <si>
-    <t>    It is the 22nd June 2024 and the target variable for the machine learning model is the temperature. Each Weather Station has one active model which is indicated by having the highest version number. </t>
-  </si>
-  <si>
-    <t>    There is also data on the previous models regarding feature sensitivity and performance. Every device has multiple tags that show the attributes of the device. </t>
-  </si>
-  <si>
-    <t>    For each tag on the device a exists to different timestamps that show how different it is to the devices with the same tag. </t>
-  </si>
-  <si>
-    <t>Provide an explanation based on the following Schema:</t>
-  </si>
-  <si>
     <t>{</t>
   </si>
   <si>
@@ -280,9 +265,6 @@
     <t>}</t>
   </si>
   <si>
-    <t>Please explain why this anomaly occurred and what it means for the weather station's prediction model.</t>
-  </si>
-  <si>
     <t>  "Weather Station Information": {</t>
   </si>
   <si>
@@ -418,9 +400,6 @@
     <t>WS</t>
   </si>
   <si>
-    <t>d?</t>
-  </si>
-  <si>
     <t>FI</t>
   </si>
   <si>
@@ -778,29 +757,203 @@
     <t>Is there a coherent argumentation and reasoning provided for the interpretation?</t>
   </si>
   <si>
-    <t>Experiment 1 (mainly num)</t>
-  </si>
-  <si>
-    <t>Experiment 2 (mainly text)</t>
-  </si>
-  <si>
-    <t>Experiment 3 (mainly text + other model information)</t>
-  </si>
-  <si>
-    <t>Experiment 4 (mainly visual)</t>
-  </si>
-  <si>
-    <t>Experiment 5 (Combination)</t>
-  </si>
-  <si>
-    <t>Experiment 6 (Combinaiton)</t>
+    <r>
+      <t xml:space="preserve">Experiment 1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(mainly num)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Experiment 2 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(mainly text)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Experiment 4 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(mainly visual)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Experiment 5 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Combination)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Experiment 6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(Combinaiton)</t>
+    </r>
+  </si>
+  <si>
+    <t>qwen3.5</t>
+  </si>
+  <si>
+    <t>d1456</t>
+  </si>
+  <si>
+    <t>d1383</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Experiment 3 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="5"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(mainly text + other models)</t>
+    </r>
+  </si>
+  <si>
+    <t>You are helping users understand the behaviour of a machine learning model. Based on the information provided in the schema and additional information that helps to provide a good answer, provide an easy to understand interpretation for why the weather station 88 is an anomaly. What does that mean for future predictions of the weather station?</t>
+  </si>
+  <si>
+    <t>Important information regarding the data in the schema at hand:</t>
+  </si>
+  <si>
+    <t>The data has entries up until July 2024 treat the data as if today is the 1st July 2024.</t>
+  </si>
+  <si>
+    <t>The data consists of multiple local models that are running on the weather station to predict the temperature.</t>
+  </si>
+  <si>
+    <t>The local model on each weather station is continuously updated using federated learning.</t>
+  </si>
+  <si>
+    <t>Every weather station has multiple tags that show the attributes of the device.  For each of these tags an outlier score exists that signalizes how different the weather station performance is compared to weather stations with the same tag.</t>
+  </si>
+  <si>
+    <t>Chain of thought instructions:</t>
+  </si>
+  <si>
+    <t>Step 1: Read and understand the schema carefully.</t>
+  </si>
+  <si>
+    <t>Step 2: Identify the most important signals and determine which parts of the schema are most relevant for explaining the unusual behaviour.</t>
+  </si>
+  <si>
+    <t>Step 3: Analyze relationships between the different pieces of information and think about how the different inputs relate to each other.</t>
+  </si>
+  <si>
+    <t>Step 4: Put the weather station 88 into context (interpret the station not in isolation).</t>
+  </si>
+  <si>
+    <t>Step 5: Use additional background knowledge when helpful (domain knowledge, environmental conditions etc.).</t>
+  </si>
+  <si>
+    <t>Step 6: Generate possible reasons for the unusual behaviour.</t>
+  </si>
+  <si>
+    <t>Step 7: Check your reasoning critically.</t>
+  </si>
+  <si>
+    <t>Step 8: Create practical recommendations.</t>
+  </si>
+  <si>
+    <t>Step 9: Write the final explanation for a non-expert industrial user based on the previous steps.</t>
+  </si>
+  <si>
+    <t>Output Instructions:</t>
+  </si>
+  <si>
+    <t>The answer has to be provided in an easy language that a user without a data background can understand. Make sure to provide short and concise answers that answer the questions at hand without unnecessary information. </t>
+  </si>
+  <si>
+    <t>What is important:</t>
+  </si>
+  <si>
+    <t>Clarity: Deliver straightforward and easily comprehensible summaries. </t>
+  </si>
+  <si>
+    <t>Relevance: Ensure insights are directly applicable to the end user. </t>
+  </si>
+  <si>
+    <t>Actionability: Focus on providing practical suggestions or conclusions. </t>
+  </si>
+  <si>
+    <t>Do not include obvious elements (numbers, text) from the given input unless needed.</t>
+  </si>
+  <si>
+    <t>The output should have the following structure:</t>
+  </si>
+  <si>
+    <t>1. Interpretation: Why is this weather station 88 behaving unusually? Explain to the engineer why the weather station is showcasing this unusual behaviour!</t>
+  </si>
+  <si>
+    <t>2. Future Predictions: What does this mean for future predictions of the weather station 88? Give recommendations on what the engineer should do!</t>
+  </si>
+  <si>
+    <t>3. Reasoning: Provide a short statement of reasoning to justify your answer, but keep it concise and non-technical.</t>
+  </si>
+  <si>
+    <t>You are helping users understand the behaviour of a machine learning model. Based on the information provided in the schema and additional information that helps to provide a good answer, provide an easy to understand interpretation for why the weather station 131 is an anomaly. What does that mean for future predictions of the weather station?</t>
+  </si>
+  <si>
+    <t>Step 4: Put the weather station 131 into context (interpret the station not in isolation).</t>
+  </si>
+  <si>
+    <t>1. Interpretation: Why is this weather station 131 behaving unusually? Explain to the engineer why the weather station is showcasing this unusual behaviour!</t>
+  </si>
+  <si>
+    <t>2. Future Predictions: What does this mean for future predictions of the weather station 131? Give recommendations on what the engineer should do!</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -845,6 +998,13 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="5"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="5"/>
       <name val="Calibri"/>
@@ -902,7 +1062,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -924,6 +1084,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1240,145 +1403,138 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0ECF850D-99CD-4307-BFB4-690876BCFF53}">
-  <dimension ref="A1:AA37"/>
+  <dimension ref="A1:Y37"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.77734375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" customWidth="1"/>
-    <col min="5" max="7" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="6" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D1" s="13" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="E1" s="13"/>
       <c r="F1" s="13" t="s">
+        <v>243</v>
+      </c>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
       <c r="K1" s="13"/>
       <c r="L1" s="13"/>
-      <c r="M1" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="N1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13" t="s">
+        <v>244</v>
+      </c>
       <c r="O1" s="13"/>
       <c r="P1" s="13"/>
       <c r="Q1" s="13"/>
       <c r="R1" s="13" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="S1" s="13"/>
       <c r="T1" s="13"/>
       <c r="U1" s="13"/>
-      <c r="V1" s="13"/>
-      <c r="W1" s="13" t="s">
-        <v>254</v>
-      </c>
+      <c r="V1" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="W1" s="13"/>
       <c r="X1" s="13"/>
       <c r="Y1" s="13"/>
-      <c r="Z1" s="13"/>
-      <c r="AA1" s="13"/>
-    </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="D2" s="12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>126</v>
+        <v>249</v>
       </c>
       <c r="I2" s="12" t="s">
-        <v>146</v>
+        <v>248</v>
       </c>
       <c r="J2" s="12" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="K2" s="12" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L2" s="12" t="s">
-        <v>129</v>
+        <v>249</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>126</v>
+        <v>248</v>
       </c>
       <c r="N2" s="12" t="s">
-        <v>146</v>
+        <v>120</v>
       </c>
       <c r="O2" s="12" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>129</v>
+        <v>249</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>129</v>
+        <v>248</v>
       </c>
       <c r="R2" s="12" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="T2" s="12" t="s">
-        <v>129</v>
+        <v>249</v>
       </c>
       <c r="U2" s="12" t="s">
-        <v>129</v>
+        <v>248</v>
       </c>
       <c r="V2" s="12" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="W2" s="12" t="s">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="X2" s="12" t="s">
-        <v>146</v>
+        <v>249</v>
       </c>
       <c r="Y2" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="Z2" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA2" s="12" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
-        <v>133</v>
+        <v>247</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D3" s="10">
         <f>'d88 #1'!D14</f>
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="E3" s="10">
         <f>'d131 #1'!D14</f>
-        <v>3.1499999999999995</v>
+        <v>0</v>
       </c>
       <c r="F3" s="10"/>
       <c r="G3" s="10"/>
@@ -1400,20 +1556,18 @@
       <c r="W3" s="10"/>
       <c r="X3" s="10"/>
       <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-    </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D4" s="10">
         <f>'d88 #1'!D27</f>
-        <v>3.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="E4" s="10">
         <f>'d131 #1'!D27</f>
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="F4" s="10"/>
       <c r="G4" s="10"/>
@@ -1435,20 +1589,18 @@
       <c r="W4" s="10"/>
       <c r="X4" s="10"/>
       <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-    </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D5" s="10">
         <f>'d88 #1'!D40</f>
-        <v>3.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="E5" s="10">
         <f>'d131 #1'!D40</f>
-        <v>3.1999999999999993</v>
+        <v>0</v>
       </c>
       <c r="F5" s="10"/>
       <c r="G5" s="10"/>
@@ -1470,22 +1622,16 @@
       <c r="W5" s="10"/>
       <c r="X5" s="10"/>
       <c r="Y5" s="10"/>
-      <c r="Z5" s="10"/>
-      <c r="AA5" s="10"/>
-    </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
-        <v>130</v>
-      </c>
-      <c r="D6" s="11">
-        <v>3.6</v>
-      </c>
-      <c r="E6" s="11">
-        <v>3.3</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
       <c r="F6" s="11"/>
       <c r="G6" s="11"/>
       <c r="H6" s="11"/>
@@ -1506,19 +1652,13 @@
       <c r="W6" s="11"/>
       <c r="X6" s="11"/>
       <c r="Y6" s="11"/>
-      <c r="Z6" s="11"/>
-      <c r="AA6" s="11"/>
-    </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C7" t="s">
-        <v>131</v>
-      </c>
-      <c r="D7" s="11">
-        <v>3.4</v>
-      </c>
-      <c r="E7" s="11">
-        <v>3.6</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
       <c r="F7" s="11"/>
       <c r="G7" s="11"/>
       <c r="H7" s="11"/>
@@ -1539,19 +1679,13 @@
       <c r="W7" s="11"/>
       <c r="X7" s="11"/>
       <c r="Y7" s="11"/>
-      <c r="Z7" s="11"/>
-      <c r="AA7" s="11"/>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C8" t="s">
-        <v>132</v>
-      </c>
-      <c r="D8" s="11">
-        <v>3.4</v>
-      </c>
-      <c r="E8" s="11">
-        <v>3.4</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
       <c r="F8" s="11"/>
       <c r="G8" s="11"/>
       <c r="H8" s="11"/>
@@ -1572,44 +1706,42 @@
       <c r="W8" s="11"/>
       <c r="X8" s="11"/>
       <c r="Y8" s="11"/>
-      <c r="Z8" s="11"/>
-      <c r="AA8" s="11"/>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C9" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C10" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C11" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D12" s="10">
         <f>'d88 #1'!D53</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" s="10">
         <f>'d131 #1'!D53</f>
-        <v>3.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="F12" s="10"/>
       <c r="G12" s="10"/>
@@ -1631,20 +1763,18 @@
       <c r="W12" s="10"/>
       <c r="X12" s="10"/>
       <c r="Y12" s="10"/>
-      <c r="Z12" s="10"/>
-      <c r="AA12" s="10"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D13" s="10">
         <f>'d88 #1'!D66</f>
-        <v>3.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="E13" s="10">
         <f>'d131 #1'!D66</f>
-        <v>3.1999999999999997</v>
+        <v>0</v>
       </c>
       <c r="F13" s="10"/>
       <c r="G13" s="10"/>
@@ -1666,20 +1796,18 @@
       <c r="W13" s="10"/>
       <c r="X13" s="10"/>
       <c r="Y13" s="10"/>
-      <c r="Z13" s="10"/>
-      <c r="AA13" s="10"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D14" s="10">
         <f>'d88 #1'!D79</f>
-        <v>3.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="E14" s="10">
         <f>'d131 #1'!D79</f>
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="F14" s="10"/>
       <c r="G14" s="10"/>
@@ -1701,22 +1829,16 @@
       <c r="W14" s="10"/>
       <c r="X14" s="10"/>
       <c r="Y14" s="10"/>
-      <c r="Z14" s="10"/>
-      <c r="AA14" s="10"/>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B15" s="9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C15" t="s">
-        <v>130</v>
-      </c>
-      <c r="D15" s="11">
-        <v>3.4</v>
-      </c>
-      <c r="E15" s="11">
-        <v>3.2</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
       <c r="F15" s="11"/>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
@@ -1737,19 +1859,13 @@
       <c r="W15" s="11"/>
       <c r="X15" s="11"/>
       <c r="Y15" s="11"/>
-      <c r="Z15" s="11"/>
-      <c r="AA15" s="11"/>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C16" t="s">
-        <v>131</v>
-      </c>
-      <c r="D16" s="11">
-        <v>3.4</v>
-      </c>
-      <c r="E16" s="11">
-        <v>3.2</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
       <c r="F16" s="11"/>
       <c r="G16" s="11"/>
       <c r="H16" s="11"/>
@@ -1770,19 +1886,13 @@
       <c r="W16" s="11"/>
       <c r="X16" s="11"/>
       <c r="Y16" s="11"/>
-      <c r="Z16" s="11"/>
-      <c r="AA16" s="11"/>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>132</v>
-      </c>
-      <c r="D17" s="11">
-        <v>3.4</v>
-      </c>
-      <c r="E17" s="11">
-        <v>3.6</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
       <c r="F17" s="11"/>
       <c r="G17" s="11"/>
       <c r="H17" s="11"/>
@@ -1803,44 +1913,42 @@
       <c r="W17" s="11"/>
       <c r="X17" s="11"/>
       <c r="Y17" s="11"/>
-      <c r="Z17" s="11"/>
-      <c r="AA17" s="11"/>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C18" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C20" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="D21" s="10">
         <f>'d88 #1'!D92</f>
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="E21" s="10">
         <f>'d131 #1'!D92</f>
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="10"/>
@@ -1862,20 +1970,18 @@
       <c r="W21" s="10"/>
       <c r="X21" s="10"/>
       <c r="Y21" s="10"/>
-      <c r="Z21" s="10"/>
-      <c r="AA21" s="10"/>
-    </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C22" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="D22" s="10">
         <f>'d88 #1'!D105</f>
-        <v>3.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="E22" s="10">
         <f>'d131 #1'!D105</f>
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="10"/>
@@ -1897,20 +2003,18 @@
       <c r="W22" s="10"/>
       <c r="X22" s="10"/>
       <c r="Y22" s="10"/>
-      <c r="Z22" s="10"/>
-      <c r="AA22" s="10"/>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C23" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="D23" s="10">
         <f>'d88 #1'!D118</f>
-        <v>3.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="E23" s="10">
         <f>'d131 #1'!D118</f>
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="10"/>
@@ -1932,22 +2036,16 @@
       <c r="W23" s="10"/>
       <c r="X23" s="10"/>
       <c r="Y23" s="10"/>
-      <c r="Z23" s="10"/>
-      <c r="AA23" s="10"/>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="C24" t="s">
-        <v>130</v>
-      </c>
-      <c r="D24" s="11">
-        <v>2.8</v>
-      </c>
-      <c r="E24" s="11">
-        <v>3.6</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11"/>
@@ -1968,19 +2066,13 @@
       <c r="W24" s="11"/>
       <c r="X24" s="11"/>
       <c r="Y24" s="11"/>
-      <c r="Z24" s="11"/>
-      <c r="AA24" s="11"/>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C25" t="s">
-        <v>131</v>
-      </c>
-      <c r="D25" s="11">
-        <v>3.1</v>
-      </c>
-      <c r="E25" s="11">
-        <v>3.3</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
       <c r="F25" s="11"/>
       <c r="G25" s="11"/>
       <c r="H25" s="11"/>
@@ -2001,19 +2093,13 @@
       <c r="W25" s="11"/>
       <c r="X25" s="11"/>
       <c r="Y25" s="11"/>
-      <c r="Z25" s="11"/>
-      <c r="AA25" s="11"/>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C26" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" s="11">
-        <v>3.3</v>
-      </c>
-      <c r="E26" s="11">
-        <v>3.3</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
       <c r="F26" s="11"/>
       <c r="G26" s="11"/>
       <c r="H26" s="11"/>
@@ -2034,65 +2120,63 @@
       <c r="W26" s="11"/>
       <c r="X26" s="11"/>
       <c r="Y26" s="11"/>
-      <c r="Z26" s="11"/>
-      <c r="AA26" s="11"/>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="C27" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C28" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="C29" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
     <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="M1:Q1"/>
-    <mergeCell ref="R1:V1"/>
-    <mergeCell ref="W1:AA1"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="N1:Q1"/>
+    <mergeCell ref="R1:U1"/>
+    <mergeCell ref="V1:Y1"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2101,7 +2185,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2280AAA2-2247-4D64-B955-D76F2C3D2B75}">
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="75.77734375" bestFit="1" customWidth="1"/>
@@ -2124,15 +2208,15 @@
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -2143,170 +2227,145 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
       <c r="D5">
         <f>C5*B5</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D12" si="0">C6*B6</f>
-        <v>0.4</v>
-      </c>
-      <c r="G6" s="7"/>
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B8" s="3">
         <v>0.15</v>
       </c>
-      <c r="C8">
-        <v>2</v>
-      </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B9" s="3">
         <v>0.15</v>
       </c>
-      <c r="C9">
-        <v>3</v>
-      </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B10" s="3">
         <v>0.05</v>
       </c>
-      <c r="C10">
-        <v>2</v>
-      </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B12" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C12">
-        <v>4</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B13" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C13">
-        <v>4</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
-        <v>0.4</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2316,7 +2375,7 @@
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>15</v>
@@ -2329,7 +2388,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G16" s="7" t="s">
         <v>17</v>
@@ -2343,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
@@ -2354,17 +2413,14 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
       </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
       <c r="D18">
         <f>C18*B18</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>19</v>
@@ -2372,104 +2428,89 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C19">
-        <v>4</v>
       </c>
       <c r="D19">
         <f t="shared" ref="D19:D25" si="1">C19*B19</f>
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B21" s="3">
         <v>0.15</v>
       </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B22" s="3">
         <v>0.15</v>
       </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B23" s="3">
         <v>0.05</v>
       </c>
-      <c r="C23">
-        <v>2</v>
-      </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
       </c>
-      <c r="C24">
-        <v>2</v>
-      </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G24" s="7" t="s">
         <v>24</v>
@@ -2477,17 +2518,14 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B25" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C25">
-        <v>4</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G25" s="7" t="s">
         <v>25</v>
@@ -2495,17 +2533,14 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C26">
-        <v>4</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>26</v>
@@ -2518,7 +2553,7 @@
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
-        <v>3.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G27" s="7" t="s">
         <v>27</v>
@@ -2531,10 +2566,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -2545,100 +2580,85 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
       </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
       <c r="D31">
         <f>C31*B31</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C32">
-        <v>4</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D38" si="2">C32*B32</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C33">
-        <v>3</v>
       </c>
       <c r="D33">
         <f t="shared" si="2"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B34" s="3">
         <v>0.15</v>
       </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
       <c r="D34">
         <f t="shared" si="2"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B35" s="3">
         <v>0.15</v>
       </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
       <c r="D35">
         <f t="shared" si="2"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>34</v>
@@ -2646,17 +2666,14 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B36" s="3">
         <v>0.05</v>
       </c>
-      <c r="C36">
-        <v>2</v>
-      </c>
       <c r="D36">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="7" t="s">
         <v>35</v>
@@ -2664,17 +2681,14 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
       </c>
-      <c r="C37">
-        <v>2</v>
-      </c>
       <c r="D37">
         <f t="shared" si="2"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="7" t="s">
         <v>36</v>
@@ -2682,17 +2696,14 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B38" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C38">
-        <v>4</v>
       </c>
       <c r="D38">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G38" s="7" t="s">
         <v>37</v>
@@ -2700,17 +2711,14 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C39">
-        <v>4</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>38</v>
@@ -2723,23 +2731,23 @@
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
-        <v>3.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -2750,118 +2758,100 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
       </c>
-      <c r="C44">
-        <v>3</v>
-      </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C45">
-        <v>4</v>
       </c>
       <c r="D45">
         <f t="shared" ref="D45:D51" si="3">C45*B45</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C46">
-        <v>3</v>
       </c>
       <c r="D46">
         <f t="shared" si="3"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
       </c>
-      <c r="C47">
-        <v>2</v>
-      </c>
       <c r="D47">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B48" s="3">
         <v>0.15</v>
       </c>
-      <c r="C48">
-        <v>2</v>
-      </c>
       <c r="D48">
         <f t="shared" si="3"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B49" s="3">
         <v>0.05</v>
       </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
       <c r="D49">
         <f t="shared" si="3"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G49" s="7" t="s">
         <v>45</v>
@@ -2869,17 +2859,14 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
       </c>
-      <c r="C50">
-        <v>3</v>
-      </c>
       <c r="D50">
         <f t="shared" si="3"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G50" s="7" t="s">
         <v>46</v>
@@ -2887,17 +2874,14 @@
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B51" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C51">
-        <v>4</v>
       </c>
       <c r="D51">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G51" s="7" t="s">
         <v>47</v>
@@ -2905,17 +2889,14 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B52" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C52">
-        <v>4</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>48</v>
@@ -2928,23 +2909,23 @@
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -2955,118 +2936,100 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
       </c>
-      <c r="C57">
-        <v>3</v>
-      </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C58">
-        <v>4</v>
       </c>
       <c r="D58">
         <f t="shared" ref="D58:D64" si="4">C58*B58</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C59">
-        <v>2</v>
       </c>
       <c r="D59">
         <f t="shared" si="4"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
       </c>
-      <c r="C60">
-        <v>3</v>
-      </c>
       <c r="D60">
         <f t="shared" si="4"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B61" s="3">
         <v>0.15</v>
       </c>
-      <c r="C61">
-        <v>3</v>
-      </c>
       <c r="D61">
         <f t="shared" si="4"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B62" s="3">
         <v>0.05</v>
       </c>
-      <c r="C62">
-        <v>3</v>
-      </c>
       <c r="D62">
         <f t="shared" si="4"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G62" s="7" t="s">
         <v>55</v>
@@ -3074,17 +3037,14 @@
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
       </c>
-      <c r="C63">
-        <v>3</v>
-      </c>
       <c r="D63">
         <f t="shared" si="4"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G63" s="7" t="s">
         <v>56</v>
@@ -3092,17 +3052,14 @@
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B64" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C64">
-        <v>4</v>
       </c>
       <c r="D64">
         <f t="shared" si="4"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G64" s="7" t="s">
         <v>57</v>
@@ -3110,20 +3067,17 @@
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B65" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C65">
-        <v>3</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3133,23 +3087,23 @@
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
-        <v>3.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -3160,175 +3114,148 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
       </c>
-      <c r="C70">
-        <v>3</v>
-      </c>
       <c r="D70">
         <f>C70*B70</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C71">
-        <v>3</v>
       </c>
       <c r="D71">
         <f t="shared" ref="D71:D77" si="5">C71*B71</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C72">
-        <v>3</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
       </c>
-      <c r="C73">
-        <v>3</v>
-      </c>
       <c r="D73">
         <f t="shared" si="5"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B74" s="3">
         <v>0.15</v>
       </c>
-      <c r="C74">
-        <v>3</v>
-      </c>
       <c r="D74">
         <f t="shared" si="5"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B75" s="3">
         <v>0.05</v>
       </c>
-      <c r="C75">
-        <v>3</v>
-      </c>
       <c r="D75">
         <f t="shared" si="5"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
       </c>
-      <c r="C76">
-        <v>3</v>
-      </c>
       <c r="D76">
         <f t="shared" si="5"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C77">
-        <v>4</v>
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B78" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C78">
-        <v>3</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3338,23 +3265,23 @@
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
-        <v>3.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G80" s="7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -3365,175 +3292,148 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
       </c>
-      <c r="C83">
-        <v>3</v>
-      </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C84">
-        <v>4</v>
       </c>
       <c r="D84">
         <f t="shared" ref="D84:D90" si="6">C84*B84</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C85">
-        <v>2</v>
       </c>
       <c r="D85">
         <f t="shared" si="6"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
       </c>
-      <c r="C86">
-        <v>2</v>
-      </c>
       <c r="D86">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B87" s="3">
         <v>0.15</v>
       </c>
-      <c r="C87">
-        <v>2</v>
-      </c>
       <c r="D87">
         <f t="shared" si="6"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B88" s="3">
         <v>0.05</v>
       </c>
-      <c r="C88">
-        <v>3</v>
-      </c>
       <c r="D88">
         <f t="shared" si="6"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
       </c>
-      <c r="C89">
-        <v>3</v>
-      </c>
       <c r="D89">
         <f t="shared" si="6"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>72</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B90" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C90">
-        <v>4</v>
       </c>
       <c r="D90">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B91" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C91">
-        <v>2</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3543,7 +3443,7 @@
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="G92" s="7" t="s">
         <v>73</v>
@@ -3556,7 +3456,7 @@
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G94" s="7" t="s">
         <v>75</v>
@@ -3570,172 +3470,142 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>22</v>
+        <v>76</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
       </c>
-      <c r="C96">
-        <v>3</v>
-      </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C97">
-        <v>4</v>
       </c>
       <c r="D97">
         <f t="shared" ref="D97:D103" si="7">C97*B97</f>
-        <v>0.4</v>
-      </c>
-      <c r="G97" s="7" t="s">
-        <v>77</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C98">
-        <v>2</v>
       </c>
       <c r="D98">
         <f t="shared" si="7"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>78</v>
+        <v>251</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
       </c>
-      <c r="C99">
-        <v>3</v>
-      </c>
       <c r="D99">
         <f t="shared" si="7"/>
-        <v>0.44999999999999996</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B100" s="3">
         <v>0.15</v>
       </c>
-      <c r="C100">
-        <v>3</v>
-      </c>
       <c r="D100">
         <f t="shared" si="7"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G100" s="7" t="s">
-        <v>80</v>
+        <v>252</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B101" s="3">
         <v>0.05</v>
       </c>
-      <c r="C101">
-        <v>3</v>
-      </c>
       <c r="D101">
         <f t="shared" si="7"/>
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="G101" s="7" t="s">
-        <v>81</v>
+        <v>0</v>
+      </c>
+      <c r="G101" s="14" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
       </c>
-      <c r="C102">
-        <v>3</v>
-      </c>
       <c r="D102">
         <f t="shared" si="7"/>
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>82</v>
+        <v>0</v>
+      </c>
+      <c r="G102" s="14" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B103" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C103">
-        <v>4</v>
       </c>
       <c r="D103">
         <f t="shared" si="7"/>
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="G103" s="14" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B104" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C104">
-        <v>3</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>83</v>
+        <v>0</v>
+      </c>
+      <c r="G104" s="14" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3745,13 +3615,20 @@
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
-        <v>3.0999999999999996</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G106" s="7" t="s">
+        <v>257</v>
+      </c>
+    </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>145</v>
+        <v>138</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -3762,158 +3639,206 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="G108" s="14" t="s">
+        <v>259</v>
+      </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
       </c>
-      <c r="C109">
-        <v>4</v>
-      </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0.8</v>
+        <v>0</v>
+      </c>
+      <c r="G109" s="14" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C110">
-        <v>4</v>
       </c>
       <c r="D110">
         <f t="shared" ref="D110:D116" si="8">C110*B110</f>
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="G110" s="14" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C111">
-        <v>3</v>
       </c>
       <c r="D111">
         <f t="shared" si="8"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
+      </c>
+      <c r="G111" s="14" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
       </c>
-      <c r="C112">
-        <v>2</v>
-      </c>
       <c r="D112">
         <f t="shared" si="8"/>
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G112" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B113" s="3">
         <v>0.15</v>
       </c>
-      <c r="C113">
-        <v>4</v>
-      </c>
       <c r="D113">
         <f t="shared" si="8"/>
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G113" s="14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B114" s="3">
         <v>0.05</v>
       </c>
-      <c r="C114">
-        <v>3</v>
-      </c>
       <c r="D114">
         <f t="shared" si="8"/>
-        <v>0.15000000000000002</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G114" s="14" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
       </c>
-      <c r="C115">
-        <v>3</v>
-      </c>
       <c r="D115">
         <f t="shared" si="8"/>
-        <v>0.15000000000000002</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G115" s="14" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B116" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C116">
-        <v>4</v>
       </c>
       <c r="D116">
         <f t="shared" si="8"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B117" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C117">
-        <v>3</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
-        <v>0.30000000000000004</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="G117" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
         <v>1.0000000000000002</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
-        <v>3.4000000000000004</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+        <v>0</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G120" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G121" s="14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G122" s="14" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G123" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G125" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G127" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G128" s="14" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="129" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G129" s="14" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="130" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G130" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3921,7 +3846,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BDBC0AD-197E-4D10-AF87-015CB58E32B7}">
-  <dimension ref="A1:G119"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="59.44140625" bestFit="1" customWidth="1"/>
@@ -3944,15 +3869,15 @@
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -3963,172 +3888,148 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
       </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
       <c r="D5">
         <f>C5*B5</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
       </c>
       <c r="D6">
         <f t="shared" ref="D6:D12" si="0">C6*B6</f>
-        <v>0.4</v>
+        <v>0</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
       </c>
       <c r="D7">
         <f t="shared" si="0"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>9</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B8" s="3">
         <v>0.15</v>
       </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
       <c r="D8">
         <f t="shared" si="0"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>10</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B9" s="3">
         <v>0.15</v>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
       <c r="D9">
         <f t="shared" si="0"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>11</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B10" s="3">
         <v>0.05</v>
       </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>12</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
       </c>
-      <c r="C11">
-        <v>3</v>
-      </c>
       <c r="D11">
         <f t="shared" si="0"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B12" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
       </c>
       <c r="D12">
         <f t="shared" si="0"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B13" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>87</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4138,23 +4039,23 @@
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
-        <v>3.1499999999999995</v>
+        <v>0</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
-        <v>149</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>88</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -4165,46 +4066,40 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
       </c>
-      <c r="C18">
-        <v>4</v>
-      </c>
       <c r="D18">
         <f>C18*B18</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>151</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C19">
-        <v>4</v>
       </c>
       <c r="D19">
         <f t="shared" ref="D19:D25" si="1">C19*B19</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G19" s="7" t="s">
         <v>21</v>
@@ -4212,128 +4107,107 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C20">
-        <v>3</v>
       </c>
       <c r="D20">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B21" s="3">
         <v>0.15</v>
       </c>
-      <c r="C21">
-        <v>3</v>
-      </c>
       <c r="D21">
         <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>23</v>
+        <v>147</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B22" s="3">
         <v>0.15</v>
       </c>
-      <c r="C22">
-        <v>3</v>
-      </c>
       <c r="D22">
         <f t="shared" si="1"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>152</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B23" s="3">
         <v>0.05</v>
       </c>
-      <c r="C23">
-        <v>3</v>
-      </c>
       <c r="D23">
         <f t="shared" si="1"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
       </c>
-      <c r="C24">
-        <v>3</v>
-      </c>
       <c r="D24">
         <f t="shared" si="1"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B25" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C25">
-        <v>3</v>
       </c>
       <c r="D25">
         <f t="shared" si="1"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C26">
-        <v>3</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4343,10 +4217,10 @@
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>22</v>
+        <v>150</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -4356,10 +4230,10 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>30</v>
+        <v>151</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -4370,172 +4244,145 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>155</v>
+        <v>31</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
       </c>
-      <c r="C31">
-        <v>4</v>
-      </c>
       <c r="D31">
         <f>C31*B31</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D38" si="2">C32*B32</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C33">
-        <v>3</v>
       </c>
       <c r="D33">
         <f t="shared" si="2"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B34" s="3">
         <v>0.15</v>
       </c>
-      <c r="C34">
-        <v>3</v>
-      </c>
       <c r="D34">
         <f t="shared" si="2"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>158</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B35" s="3">
         <v>0.15</v>
       </c>
-      <c r="C35">
-        <v>3</v>
-      </c>
       <c r="D35">
         <f t="shared" si="2"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>36</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B36" s="3">
         <v>0.05</v>
       </c>
-      <c r="C36">
-        <v>3</v>
-      </c>
       <c r="D36">
         <f t="shared" si="2"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>159</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
       </c>
-      <c r="C37">
-        <v>3</v>
-      </c>
       <c r="D37">
         <f t="shared" si="2"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B38" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C38">
-        <v>3</v>
       </c>
       <c r="D38">
         <f t="shared" si="2"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>22</v>
+        <v>156</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C39">
-        <v>3</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>39</v>
@@ -4548,23 +4395,23 @@
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
-        <v>3.1999999999999993</v>
+        <v>0</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>161</v>
+        <v>16</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>162</v>
+        <v>40</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -4575,175 +4422,148 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>163</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
       </c>
-      <c r="C44">
-        <v>3</v>
-      </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>44</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C45">
-        <v>3</v>
       </c>
       <c r="D45">
         <f t="shared" ref="D45:D51" si="3">C45*B45</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>21</v>
+        <v>158</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C46">
-        <v>3</v>
       </c>
       <c r="D46">
         <f t="shared" si="3"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>22</v>
+        <v>159</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
       </c>
-      <c r="C47">
-        <v>3</v>
-      </c>
       <c r="D47">
         <f t="shared" si="3"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B48" s="3">
         <v>0.15</v>
       </c>
-      <c r="C48">
-        <v>3</v>
-      </c>
       <c r="D48">
         <f t="shared" si="3"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B49" s="3">
         <v>0.05</v>
       </c>
-      <c r="C49">
-        <v>3</v>
-      </c>
       <c r="D49">
         <f t="shared" si="3"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
       </c>
-      <c r="C50">
-        <v>3</v>
-      </c>
       <c r="D50">
         <f t="shared" si="3"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B51" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C51">
-        <v>4</v>
       </c>
       <c r="D51">
         <f t="shared" si="3"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B52" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C52">
-        <v>3</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4753,23 +4573,23 @@
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
-        <v>3.0999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -4780,64 +4600,55 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
       </c>
-      <c r="C57">
-        <v>3</v>
-      </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>21</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C58">
-        <v>3</v>
       </c>
       <c r="D58">
         <f t="shared" ref="D58:D64" si="4">C58*B58</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C59">
-        <v>3</v>
       </c>
       <c r="D59">
         <f t="shared" si="4"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G59" s="7" t="s">
         <v>54</v>
@@ -4845,110 +4656,92 @@
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
       </c>
-      <c r="C60">
-        <v>3</v>
-      </c>
       <c r="D60">
         <f t="shared" si="4"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>170</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B61" s="3">
         <v>0.15</v>
       </c>
-      <c r="C61">
-        <v>3</v>
-      </c>
       <c r="D61">
         <f t="shared" si="4"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>171</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B62" s="3">
         <v>0.05</v>
       </c>
-      <c r="C62">
-        <v>3</v>
-      </c>
       <c r="D62">
         <f t="shared" si="4"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
       </c>
-      <c r="C63">
-        <v>3</v>
-      </c>
       <c r="D63">
         <f t="shared" si="4"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>72</v>
+        <v>167</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B64" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C64">
-        <v>4</v>
       </c>
       <c r="D64">
         <f t="shared" si="4"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B65" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C65">
-        <v>4</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -4958,23 +4751,23 @@
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
-        <v>3.1999999999999997</v>
+        <v>0</v>
       </c>
       <c r="G66" s="7" t="s">
-        <v>98</v>
+        <v>29</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>173</v>
+        <v>88</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -4985,175 +4778,148 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G69" s="7" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
       </c>
-      <c r="C70">
-        <v>4</v>
-      </c>
       <c r="D70">
         <f>C70*B70</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C71">
-        <v>2</v>
       </c>
       <c r="D71">
         <f t="shared" ref="D71:D77" si="5">C71*B71</f>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C72">
-        <v>4</v>
       </c>
       <c r="D72">
         <f t="shared" si="5"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>94</v>
+        <v>29</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
       </c>
-      <c r="C73">
-        <v>3</v>
-      </c>
       <c r="D73">
         <f t="shared" si="5"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>175</v>
+        <v>50</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B74" s="3">
         <v>0.15</v>
       </c>
-      <c r="C74">
-        <v>3</v>
-      </c>
       <c r="D74">
         <f t="shared" si="5"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B75" s="3">
         <v>0.05</v>
       </c>
-      <c r="C75">
-        <v>3</v>
-      </c>
       <c r="D75">
         <f t="shared" si="5"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G75" s="7" t="s">
-        <v>72</v>
+        <v>171</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
       </c>
-      <c r="C76">
-        <v>3</v>
-      </c>
       <c r="D76">
         <f t="shared" si="5"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C77">
-        <v>4</v>
       </c>
       <c r="D77">
         <f t="shared" si="5"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B78" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C78">
-        <v>3</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5163,23 +4929,23 @@
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="G79" s="7" t="s">
-        <v>177</v>
+        <v>90</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G80" s="7" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>72</v>
+        <v>173</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -5190,175 +4956,148 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
       </c>
-      <c r="C83">
-        <v>3</v>
-      </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G83" s="7" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C84">
-        <v>4</v>
       </c>
       <c r="D84">
         <f t="shared" ref="D84:D90" si="6">C84*B84</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G84" s="7" t="s">
-        <v>96</v>
+        <v>29</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C85">
-        <v>3</v>
       </c>
       <c r="D85">
         <f t="shared" si="6"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G85" s="7" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
       </c>
-      <c r="C86">
-        <v>3</v>
-      </c>
       <c r="D86">
         <f t="shared" si="6"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G86" s="7" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B87" s="3">
         <v>0.15</v>
       </c>
-      <c r="C87">
-        <v>3</v>
-      </c>
       <c r="D87">
         <f t="shared" si="6"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G87" s="7" t="s">
-        <v>72</v>
+        <v>176</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B88" s="3">
         <v>0.05</v>
       </c>
-      <c r="C88">
-        <v>3</v>
-      </c>
       <c r="D88">
         <f t="shared" si="6"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G88" s="7" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
       </c>
-      <c r="C89">
-        <v>3</v>
-      </c>
       <c r="D89">
         <f t="shared" si="6"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G89" s="7" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B90" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C90">
-        <v>4</v>
       </c>
       <c r="D90">
         <f t="shared" si="6"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G90" s="7" t="s">
-        <v>181</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B91" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C91">
-        <v>3</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G91" s="7" t="s">
-        <v>182</v>
+        <v>68</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5368,23 +5107,23 @@
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G92" s="7" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G93" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="G94" s="7" t="s">
-        <v>59</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -5395,100 +5134,85 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G95" s="7" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
       </c>
-      <c r="C96">
-        <v>3</v>
-      </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
       </c>
       <c r="G96" s="7" t="s">
-        <v>73</v>
+        <v>178</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C97">
-        <v>4</v>
       </c>
       <c r="D97">
         <f t="shared" ref="D97:D103" si="7">C97*B97</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G97" s="7" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C98">
-        <v>3</v>
       </c>
       <c r="D98">
         <f t="shared" si="7"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
       </c>
       <c r="G98" s="7" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
       </c>
-      <c r="C99">
-        <v>3</v>
-      </c>
       <c r="D99">
         <f t="shared" si="7"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G99" s="7" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B100" s="3">
         <v>0.15</v>
       </c>
-      <c r="C100">
-        <v>3</v>
-      </c>
       <c r="D100">
         <f t="shared" si="7"/>
-        <v>0.44999999999999996</v>
+        <v>0</v>
       </c>
       <c r="G100" s="7" t="s">
         <v>76</v>
@@ -5496,74 +5220,56 @@
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B101" s="3">
         <v>0.05</v>
       </c>
-      <c r="C101">
-        <v>3</v>
-      </c>
       <c r="D101">
         <f t="shared" si="7"/>
-        <v>0.15000000000000002</v>
+        <v>0</v>
       </c>
       <c r="G101" s="7" t="s">
-        <v>185</v>
+        <v>77</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
       </c>
-      <c r="C102">
-        <v>3</v>
-      </c>
       <c r="D102">
         <f t="shared" si="7"/>
-        <v>0.15000000000000002</v>
-      </c>
-      <c r="G102" s="7" t="s">
-        <v>186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B103" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C103">
-        <v>4</v>
       </c>
       <c r="D103">
         <f t="shared" si="7"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="G103" s="7" t="s">
-        <v>99</v>
+        <v>278</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B104" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C104">
-        <v>3</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
-        <v>0.30000000000000004</v>
-      </c>
-      <c r="G104" s="7" t="s">
-        <v>187</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5573,20 +5279,23 @@
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="G105" s="7" t="s">
-        <v>81</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="G106" s="7" t="s">
-        <v>82</v>
+      <c r="G106" s="14" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>145</v>
+        <v>138</v>
+      </c>
+      <c r="G107" s="14" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
@@ -5597,161 +5306,225 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G108" s="7" t="s">
-        <v>83</v>
+      <c r="G108" s="14" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
       </c>
-      <c r="C109">
-        <v>3</v>
-      </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0.60000000000000009</v>
+        <v>0</v>
+      </c>
+      <c r="G109" s="14" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C110">
-        <v>4</v>
       </c>
       <c r="D110">
         <f t="shared" ref="D110:D116" si="8">C110*B110</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C111">
-        <v>3</v>
       </c>
       <c r="D111">
         <f t="shared" si="8"/>
-        <v>0.30000000000000004</v>
+        <v>0</v>
+      </c>
+      <c r="G111" s="7" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
       </c>
-      <c r="C112">
-        <v>3</v>
-      </c>
       <c r="D112">
         <f t="shared" si="8"/>
-        <v>0.44999999999999996</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G112" s="14" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B113" s="3">
         <v>0.15</v>
       </c>
-      <c r="C113">
-        <v>3</v>
-      </c>
       <c r="D113">
         <f t="shared" si="8"/>
-        <v>0.44999999999999996</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G113" s="14" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B114" s="3">
         <v>0.05</v>
       </c>
-      <c r="C114">
-        <v>3</v>
-      </c>
       <c r="D114">
         <f t="shared" si="8"/>
-        <v>0.15000000000000002</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G114" s="14" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
       </c>
-      <c r="C115">
-        <v>2</v>
-      </c>
       <c r="D115">
         <f t="shared" si="8"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G115" s="14" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B116" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C116">
-        <v>4</v>
       </c>
       <c r="D116">
         <f t="shared" si="8"/>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="G116" s="14" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B117" s="3">
         <v>0.1</v>
-      </c>
-      <c r="C117">
-        <v>4</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+      <c r="G117" s="14" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
         <v>1.0000000000000002</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+        <v>0</v>
+      </c>
+      <c r="G118" s="14" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G119" s="14" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G120" s="14" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G122" s="7" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G123" s="7" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G125" s="7" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G126" s="14" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G127" s="14" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G128" s="14" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="130" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G130" s="7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="132" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G132" s="7" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="133" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G133" s="14" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="134" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G134" s="14" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="135" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G135" s="14" t="s">
+        <v>277</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5782,15 +5555,15 @@
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -5801,18 +5574,18 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
@@ -5825,12 +5598,12 @@
         <v>0.8</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
@@ -5843,12 +5616,12 @@
         <v>0.4</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
@@ -5861,12 +5634,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B8" s="3">
         <v>0.15</v>
@@ -5879,12 +5652,12 @@
         <v>0.3</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B9" s="3">
         <v>0.15</v>
@@ -5897,12 +5670,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B10" s="3">
         <v>0.05</v>
@@ -5915,12 +5688,12 @@
         <v>0.1</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
@@ -5933,12 +5706,12 @@
         <v>0.1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B12" s="3">
         <v>0.1</v>
@@ -5951,12 +5724,12 @@
         <v>0.4</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B13" s="3">
         <v>0.1</v>
@@ -5969,7 +5742,7 @@
         <v>0.4</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -5982,20 +5755,20 @@
         <v>3.25</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -6006,18 +5779,18 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
@@ -6030,12 +5803,12 @@
         <v>0.8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
@@ -6048,12 +5821,12 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
@@ -6066,12 +5839,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B21" s="3">
         <v>0.15</v>
@@ -6084,12 +5857,12 @@
         <v>0.3</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B22" s="3">
         <v>0.15</v>
@@ -6102,12 +5875,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B23" s="3">
         <v>0.05</v>
@@ -6120,12 +5893,12 @@
         <v>0.1</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
@@ -6138,12 +5911,12 @@
         <v>0.1</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B25" s="3">
         <v>0.1</v>
@@ -6156,12 +5929,12 @@
         <v>0.4</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3">
         <v>0.1</v>
@@ -6174,7 +5947,7 @@
         <v>0.4</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6187,20 +5960,20 @@
         <v>3.25</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G28" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -6211,18 +5984,18 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
@@ -6235,12 +6008,12 @@
         <v>0.8</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
@@ -6253,12 +6026,12 @@
         <v>0.4</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
@@ -6271,12 +6044,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B34" s="3">
         <v>0.15</v>
@@ -6289,12 +6062,12 @@
         <v>0.3</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B35" s="3">
         <v>0.15</v>
@@ -6307,12 +6080,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B36" s="3">
         <v>0.05</v>
@@ -6325,12 +6098,12 @@
         <v>0.1</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
@@ -6343,12 +6116,12 @@
         <v>0.1</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B38" s="3">
         <v>0.1</v>
@@ -6361,12 +6134,12 @@
         <v>0.4</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3">
         <v>0.1</v>
@@ -6379,7 +6152,7 @@
         <v>0.4</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6392,20 +6165,20 @@
         <v>3.25</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -6416,18 +6189,18 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
@@ -6440,12 +6213,12 @@
         <v>0.8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
@@ -6458,12 +6231,12 @@
         <v>0.4</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
@@ -6476,12 +6249,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
@@ -6494,12 +6267,12 @@
         <v>0.3</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B48" s="3">
         <v>0.15</v>
@@ -6512,12 +6285,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B49" s="3">
         <v>0.05</v>
@@ -6530,12 +6303,12 @@
         <v>0.1</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
@@ -6548,12 +6321,12 @@
         <v>0.1</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B51" s="3">
         <v>0.1</v>
@@ -6566,12 +6339,12 @@
         <v>0.4</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B52" s="3">
         <v>0.1</v>
@@ -6584,7 +6357,7 @@
         <v>0.4</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6597,20 +6370,20 @@
         <v>3.25</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -6621,18 +6394,18 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
@@ -6645,12 +6418,12 @@
         <v>0.8</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
@@ -6663,12 +6436,12 @@
         <v>0.4</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
@@ -6681,12 +6454,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
@@ -6699,12 +6472,12 @@
         <v>0.3</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B61" s="3">
         <v>0.15</v>
@@ -6717,12 +6490,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B62" s="3">
         <v>0.05</v>
@@ -6735,12 +6508,12 @@
         <v>0.1</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
@@ -6753,12 +6526,12 @@
         <v>0.1</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B64" s="3">
         <v>0.1</v>
@@ -6771,12 +6544,12 @@
         <v>0.4</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B65" s="3">
         <v>0.1</v>
@@ -6789,7 +6562,7 @@
         <v>0.4</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -6804,15 +6577,15 @@
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -6823,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>3</v>
@@ -6831,7 +6604,7 @@
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
@@ -6844,12 +6617,12 @@
         <v>0.8</v>
       </c>
       <c r="G70" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
@@ -6862,12 +6635,12 @@
         <v>0.4</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
@@ -6880,12 +6653,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
@@ -6898,12 +6671,12 @@
         <v>0.3</v>
       </c>
       <c r="G73" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B74" s="3">
         <v>0.15</v>
@@ -6916,12 +6689,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B75" s="3">
         <v>0.05</v>
@@ -6936,7 +6709,7 @@
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
@@ -6949,12 +6722,12 @@
         <v>0.1</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
@@ -6967,12 +6740,12 @@
         <v>0.4</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B78" s="3">
         <v>0.1</v>
@@ -6985,7 +6758,7 @@
         <v>0.4</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7003,7 +6776,7 @@
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G81" s="7"/>
     </row>
@@ -7015,7 +6788,7 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>3</v>
@@ -7024,7 +6797,7 @@
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
@@ -7039,7 +6812,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
@@ -7054,7 +6827,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
@@ -7069,7 +6842,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
@@ -7084,7 +6857,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B87" s="3">
         <v>0.15</v>
@@ -7099,7 +6872,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B88" s="3">
         <v>0.05</v>
@@ -7114,7 +6887,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
@@ -7129,7 +6902,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B90" s="3">
         <v>0.1</v>
@@ -7144,7 +6917,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B91" s="3">
         <v>0.1</v>
@@ -7170,7 +6943,7 @@
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -7181,7 +6954,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>3</v>
@@ -7189,7 +6962,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
@@ -7204,7 +6977,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
@@ -7219,7 +6992,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
@@ -7234,7 +7007,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
@@ -7249,7 +7022,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B100" s="3">
         <v>0.15</v>
@@ -7264,7 +7037,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B101" s="3">
         <v>0.05</v>
@@ -7279,7 +7052,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
@@ -7294,7 +7067,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B103" s="3">
         <v>0.1</v>
@@ -7309,7 +7082,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B104" s="3">
         <v>0.1</v>
@@ -7335,7 +7108,7 @@
     <row r="106" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -7346,7 +7119,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>3</v>
@@ -7354,7 +7127,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
@@ -7369,7 +7142,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
@@ -7384,7 +7157,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
@@ -7399,7 +7172,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
@@ -7414,7 +7187,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B113" s="3">
         <v>0.15</v>
@@ -7429,7 +7202,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B114" s="3">
         <v>0.05</v>
@@ -7444,7 +7217,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
@@ -7459,7 +7232,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B116" s="3">
         <v>0.1</v>
@@ -7474,7 +7247,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B117" s="3">
         <v>0.1</v>
@@ -7528,15 +7301,15 @@
         <v>2</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -7547,18 +7320,18 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>189</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B5" s="3">
         <v>0.2</v>
@@ -7571,12 +7344,12 @@
         <v>0.8</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B6" s="3">
         <v>0.1</v>
@@ -7589,12 +7362,12 @@
         <v>0.4</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B7" s="3">
         <v>0.1</v>
@@ -7607,12 +7380,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B8" s="3">
         <v>0.15</v>
@@ -7625,12 +7398,12 @@
         <v>0.3</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B9" s="3">
         <v>0.15</v>
@@ -7643,12 +7416,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B10" s="3">
         <v>0.05</v>
@@ -7661,12 +7434,12 @@
         <v>0.1</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B11" s="3">
         <v>0.05</v>
@@ -7679,12 +7452,12 @@
         <v>0.1</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B12" s="3">
         <v>0.1</v>
@@ -7697,12 +7470,12 @@
         <v>0.4</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B13" s="3">
         <v>0.1</v>
@@ -7715,7 +7488,7 @@
         <v>0.4</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7728,20 +7501,20 @@
         <v>3.25</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G15" s="7" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
@@ -7752,18 +7525,18 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B18" s="3">
         <v>0.2</v>
@@ -7776,12 +7549,12 @@
         <v>0.8</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B19" s="3">
         <v>0.1</v>
@@ -7794,12 +7567,12 @@
         <v>0.4</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B20" s="3">
         <v>0.1</v>
@@ -7812,12 +7585,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B21" s="3">
         <v>0.15</v>
@@ -7830,12 +7603,12 @@
         <v>0.3</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B22" s="3">
         <v>0.15</v>
@@ -7848,12 +7621,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B23" s="3">
         <v>0.05</v>
@@ -7866,12 +7639,12 @@
         <v>0.1</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B24" s="3">
         <v>0.05</v>
@@ -7884,12 +7657,12 @@
         <v>0.1</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B25" s="3">
         <v>0.1</v>
@@ -7902,12 +7675,12 @@
         <v>0.4</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B26" s="3">
         <v>0.1</v>
@@ -7920,7 +7693,7 @@
         <v>0.4</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -7933,20 +7706,20 @@
         <v>3.25</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G28" s="7" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
@@ -7957,18 +7730,18 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B31" s="3">
         <v>0.2</v>
@@ -7981,12 +7754,12 @@
         <v>0.8</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B32" s="3">
         <v>0.1</v>
@@ -7999,12 +7772,12 @@
         <v>0.4</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B33" s="3">
         <v>0.1</v>
@@ -8017,12 +7790,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B34" s="3">
         <v>0.15</v>
@@ -8035,12 +7808,12 @@
         <v>0.3</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B35" s="3">
         <v>0.15</v>
@@ -8053,12 +7826,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B36" s="3">
         <v>0.05</v>
@@ -8071,12 +7844,12 @@
         <v>0.1</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B37" s="3">
         <v>0.05</v>
@@ -8089,12 +7862,12 @@
         <v>0.1</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B38" s="3">
         <v>0.1</v>
@@ -8107,12 +7880,12 @@
         <v>0.4</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B39" s="3">
         <v>0.1</v>
@@ -8125,7 +7898,7 @@
         <v>0.4</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8138,20 +7911,20 @@
         <v>3.25</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G41" s="7" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
@@ -8162,18 +7935,18 @@
         <v>1</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B44" s="3">
         <v>0.2</v>
@@ -8186,12 +7959,12 @@
         <v>0.8</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B45" s="3">
         <v>0.1</v>
@@ -8204,12 +7977,12 @@
         <v>0.4</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B46" s="3">
         <v>0.1</v>
@@ -8222,12 +7995,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B47" s="3">
         <v>0.15</v>
@@ -8240,12 +8013,12 @@
         <v>0.3</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B48" s="3">
         <v>0.15</v>
@@ -8258,12 +8031,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B49" s="3">
         <v>0.05</v>
@@ -8276,12 +8049,12 @@
         <v>0.1</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B50" s="3">
         <v>0.05</v>
@@ -8294,12 +8067,12 @@
         <v>0.1</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B51" s="3">
         <v>0.1</v>
@@ -8312,12 +8085,12 @@
         <v>0.4</v>
       </c>
       <c r="G51" s="7" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B52" s="3">
         <v>0.1</v>
@@ -8330,7 +8103,7 @@
         <v>0.4</v>
       </c>
       <c r="G52" s="7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8343,20 +8116,20 @@
         <v>3.25</v>
       </c>
       <c r="G53" s="7" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G54" s="7" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="G55" s="7" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
@@ -8367,18 +8140,18 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G56" s="7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B57" s="3">
         <v>0.2</v>
@@ -8391,12 +8164,12 @@
         <v>0.8</v>
       </c>
       <c r="G57" s="7" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B58" s="3">
         <v>0.1</v>
@@ -8409,12 +8182,12 @@
         <v>0.4</v>
       </c>
       <c r="G58" s="7" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B59" s="3">
         <v>0.1</v>
@@ -8427,12 +8200,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G59" s="7" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B60" s="3">
         <v>0.15</v>
@@ -8445,12 +8218,12 @@
         <v>0.3</v>
       </c>
       <c r="G60" s="7" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B61" s="3">
         <v>0.15</v>
@@ -8463,12 +8236,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G61" s="7" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B62" s="3">
         <v>0.05</v>
@@ -8481,12 +8254,12 @@
         <v>0.1</v>
       </c>
       <c r="G62" s="7" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B63" s="3">
         <v>0.05</v>
@@ -8499,12 +8272,12 @@
         <v>0.1</v>
       </c>
       <c r="G63" s="7" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B64" s="3">
         <v>0.1</v>
@@ -8517,12 +8290,12 @@
         <v>0.4</v>
       </c>
       <c r="G64" s="7" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B65" s="3">
         <v>0.1</v>
@@ -8535,7 +8308,7 @@
         <v>0.4</v>
       </c>
       <c r="G65" s="7" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8548,20 +8321,20 @@
         <v>3.25</v>
       </c>
       <c r="G66" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G67" s="7" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="G68" s="7" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
@@ -8572,18 +8345,18 @@
         <v>1</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G69" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B70" s="3">
         <v>0.2</v>
@@ -8599,7 +8372,7 @@
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B71" s="3">
         <v>0.1</v>
@@ -8612,12 +8385,12 @@
         <v>0.4</v>
       </c>
       <c r="G71" s="7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B72" s="3">
         <v>0.1</v>
@@ -8630,12 +8403,12 @@
         <v>0.30000000000000004</v>
       </c>
       <c r="G72" s="7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B73" s="3">
         <v>0.15</v>
@@ -8651,7 +8424,7 @@
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B74" s="3">
         <v>0.15</v>
@@ -8664,12 +8437,12 @@
         <v>0.44999999999999996</v>
       </c>
       <c r="G74" s="7" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B75" s="3">
         <v>0.05</v>
@@ -8682,12 +8455,12 @@
         <v>0.1</v>
       </c>
       <c r="G75" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B76" s="3">
         <v>0.05</v>
@@ -8700,12 +8473,12 @@
         <v>0.1</v>
       </c>
       <c r="G76" s="7" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B77" s="3">
         <v>0.1</v>
@@ -8718,12 +8491,12 @@
         <v>0.4</v>
       </c>
       <c r="G77" s="7" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B78" s="3">
         <v>0.1</v>
@@ -8736,7 +8509,7 @@
         <v>0.4</v>
       </c>
       <c r="G78" s="7" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -8751,15 +8524,15 @@
     </row>
     <row r="80" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3">
       <c r="G80" s="7" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G81" s="7" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
@@ -8770,18 +8543,18 @@
         <v>1</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G82" s="7" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B83" s="3">
         <v>0.2</v>
@@ -8796,7 +8569,7 @@
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B84" s="3">
         <v>0.1</v>
@@ -8811,7 +8584,7 @@
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B85" s="3">
         <v>0.1</v>
@@ -8826,7 +8599,7 @@
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B86" s="3">
         <v>0.15</v>
@@ -8841,7 +8614,7 @@
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B87" s="3">
         <v>0.15</v>
@@ -8856,7 +8629,7 @@
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B88" s="3">
         <v>0.05</v>
@@ -8871,7 +8644,7 @@
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B89" s="3">
         <v>0.05</v>
@@ -8886,7 +8659,7 @@
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B90" s="3">
         <v>0.1</v>
@@ -8901,7 +8674,7 @@
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B91" s="3">
         <v>0.1</v>
@@ -8927,7 +8700,7 @@
     <row r="93" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
@@ -8938,7 +8711,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>3</v>
@@ -8946,7 +8719,7 @@
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B96" s="3">
         <v>0.2</v>
@@ -8961,7 +8734,7 @@
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B97" s="3">
         <v>0.1</v>
@@ -8976,7 +8749,7 @@
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B98" s="3">
         <v>0.1</v>
@@ -8991,7 +8764,7 @@
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B99" s="3">
         <v>0.15</v>
@@ -9006,7 +8779,7 @@
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B100" s="3">
         <v>0.15</v>
@@ -9021,7 +8794,7 @@
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B101" s="3">
         <v>0.05</v>
@@ -9036,7 +8809,7 @@
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B102" s="3">
         <v>0.05</v>
@@ -9051,7 +8824,7 @@
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B103" s="3">
         <v>0.1</v>
@@ -9066,7 +8839,7 @@
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B104" s="3">
         <v>0.1</v>
@@ -9092,7 +8865,7 @@
     <row r="106" spans="1:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.3">
@@ -9103,7 +8876,7 @@
         <v>1</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="D108" s="1" t="s">
         <v>3</v>
@@ -9111,7 +8884,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="B109" s="3">
         <v>0.2</v>
@@ -9126,7 +8899,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="B110" s="3">
         <v>0.1</v>
@@ -9141,7 +8914,7 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B111" s="3">
         <v>0.1</v>
@@ -9156,7 +8929,7 @@
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="B112" s="3">
         <v>0.15</v>
@@ -9171,7 +8944,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B113" s="3">
         <v>0.15</v>
@@ -9186,7 +8959,7 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="B114" s="3">
         <v>0.05</v>
@@ -9201,7 +8974,7 @@
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="B115" s="3">
         <v>0.05</v>
@@ -9216,7 +8989,7 @@
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B116" s="3">
         <v>0.1</v>
@@ -9231,7 +9004,7 @@
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B117" s="3">
         <v>0.1</v>

--- a/Evaluation_Schema.xlsx
+++ b/Evaluation_Schema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kim_W\Ekkono_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29EDBAC4-EF67-43B1-AAD2-895C3127530A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B24294-1121-4556-ADCE-FEB267DA9B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="2" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation Table" sheetId="3" r:id="rId1"/>
@@ -1062,7 +1062,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1088,6 +1088,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1751,10 +1752,10 @@
       <c r="K12" s="10"/>
       <c r="L12" s="10"/>
       <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
+      <c r="N12" s="15"/>
+      <c r="O12" s="15"/>
+      <c r="P12" s="15"/>
+      <c r="Q12" s="15"/>
       <c r="R12" s="10"/>
       <c r="S12" s="10"/>
       <c r="T12" s="10"/>
@@ -1784,10 +1785,10 @@
       <c r="K13" s="10"/>
       <c r="L13" s="10"/>
       <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
+      <c r="N13" s="15"/>
+      <c r="O13" s="15"/>
+      <c r="P13" s="15"/>
+      <c r="Q13" s="15"/>
       <c r="R13" s="10"/>
       <c r="S13" s="10"/>
       <c r="T13" s="10"/>
@@ -1817,10 +1818,10 @@
       <c r="K14" s="10"/>
       <c r="L14" s="10"/>
       <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
+      <c r="N14" s="15"/>
+      <c r="O14" s="15"/>
+      <c r="P14" s="15"/>
+      <c r="Q14" s="15"/>
       <c r="R14" s="10"/>
       <c r="S14" s="10"/>
       <c r="T14" s="10"/>
@@ -1847,10 +1848,10 @@
       <c r="K15" s="11"/>
       <c r="L15" s="11"/>
       <c r="M15" s="11"/>
-      <c r="N15" s="11"/>
-      <c r="O15" s="11"/>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="11"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
       <c r="R15" s="11"/>
       <c r="S15" s="11"/>
       <c r="T15" s="11"/>
@@ -1874,10 +1875,10 @@
       <c r="K16" s="11"/>
       <c r="L16" s="11"/>
       <c r="M16" s="11"/>
-      <c r="N16" s="11"/>
-      <c r="O16" s="11"/>
-      <c r="P16" s="11"/>
-      <c r="Q16" s="11"/>
+      <c r="N16" s="15"/>
+      <c r="O16" s="15"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="15"/>
       <c r="R16" s="11"/>
       <c r="S16" s="11"/>
       <c r="T16" s="11"/>
@@ -1901,10 +1902,10 @@
       <c r="K17" s="11"/>
       <c r="L17" s="11"/>
       <c r="M17" s="11"/>
-      <c r="N17" s="11"/>
-      <c r="O17" s="11"/>
-      <c r="P17" s="11"/>
-      <c r="Q17" s="11"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
       <c r="R17" s="11"/>
       <c r="S17" s="11"/>
       <c r="T17" s="11"/>

--- a/Evaluation_Schema.xlsx
+++ b/Evaluation_Schema.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kim_W\Ekkono_Code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4B24294-1121-4556-ADCE-FEB267DA9B2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5E17F6E-DB41-469C-B8C8-9D9AF82DAC12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="1" activeTab="4" xr2:uid="{E8F4F112-DC9E-445D-AE6E-08B98EFB1B63}"/>
   </bookViews>
   <sheets>
     <sheet name="Evaluation Table" sheetId="3" r:id="rId1"/>
@@ -2242,7 +2242,7 @@
         <v>240</v>
       </c>
       <c r="B5" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D5">
         <f>C5*B5</f>
@@ -2362,7 +2362,7 @@
         <v>116</v>
       </c>
       <c r="B13" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
@@ -2372,7 +2372,7 @@
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <f>SUM(B5:B13)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
@@ -2417,7 +2417,7 @@
         <v>240</v>
       </c>
       <c r="B18" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D18">
         <f>C18*B18</f>
@@ -2537,7 +2537,7 @@
         <v>116</v>
       </c>
       <c r="B26" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
@@ -2550,7 +2550,7 @@
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4">
         <f>SUM(B18:B26)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
@@ -2595,7 +2595,7 @@
         <v>240</v>
       </c>
       <c r="B31" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D31">
         <f>C31*B31</f>
@@ -2715,7 +2715,7 @@
         <v>116</v>
       </c>
       <c r="B39" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
@@ -2728,7 +2728,7 @@
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4">
         <f>SUM(B31:B39)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
@@ -2773,7 +2773,7 @@
         <v>240</v>
       </c>
       <c r="B44" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D44">
         <f>C44*B44</f>
@@ -2893,7 +2893,7 @@
         <v>116</v>
       </c>
       <c r="B52" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
@@ -2906,7 +2906,7 @@
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="4">
         <f>SUM(B44:B52)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
@@ -2951,7 +2951,7 @@
         <v>240</v>
       </c>
       <c r="B57" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D57">
         <f>C57*B57</f>
@@ -3071,7 +3071,7 @@
         <v>116</v>
       </c>
       <c r="B65" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
@@ -3084,7 +3084,7 @@
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="4">
         <f>SUM(B57:B65)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
@@ -3129,7 +3129,7 @@
         <v>240</v>
       </c>
       <c r="B70" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D70">
         <f>C70*B70</f>
@@ -3249,7 +3249,7 @@
         <v>116</v>
       </c>
       <c r="B78" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
@@ -3262,7 +3262,7 @@
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="4">
         <f>SUM(B70:B78)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
@@ -3307,7 +3307,7 @@
         <v>240</v>
       </c>
       <c r="B83" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D83">
         <f>C83*B83</f>
@@ -3427,7 +3427,7 @@
         <v>116</v>
       </c>
       <c r="B91" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
@@ -3440,7 +3440,7 @@
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="4">
         <f>SUM(B83:B91)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
@@ -3485,7 +3485,7 @@
         <v>240</v>
       </c>
       <c r="B96" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D96">
         <f>C96*B96</f>
@@ -3599,7 +3599,7 @@
         <v>116</v>
       </c>
       <c r="B104" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
@@ -3612,7 +3612,7 @@
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="4">
         <f>SUM(B96:B104)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
@@ -3654,7 +3654,7 @@
         <v>240</v>
       </c>
       <c r="B109" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D109">
         <f>C109*B109</f>
@@ -3771,7 +3771,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
@@ -3784,7 +3784,7 @@
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
@@ -3903,7 +3903,7 @@
         <v>240</v>
       </c>
       <c r="B5" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D5">
         <f>C5*B5</f>
@@ -4023,7 +4023,7 @@
         <v>116</v>
       </c>
       <c r="B13" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
@@ -4036,7 +4036,7 @@
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <f>SUM(B5:B13)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
@@ -4081,7 +4081,7 @@
         <v>240</v>
       </c>
       <c r="B18" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D18">
         <f>C18*B18</f>
@@ -4201,7 +4201,7 @@
         <v>116</v>
       </c>
       <c r="B26" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
@@ -4214,7 +4214,7 @@
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4">
         <f>SUM(B18:B26)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
@@ -4259,7 +4259,7 @@
         <v>240</v>
       </c>
       <c r="B31" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D31">
         <f>C31*B31</f>
@@ -4379,7 +4379,7 @@
         <v>116</v>
       </c>
       <c r="B39" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
@@ -4392,7 +4392,7 @@
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4">
         <f>SUM(B31:B39)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
@@ -4437,7 +4437,7 @@
         <v>240</v>
       </c>
       <c r="B44" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D44">
         <f>C44*B44</f>
@@ -4557,7 +4557,7 @@
         <v>116</v>
       </c>
       <c r="B52" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
@@ -4570,7 +4570,7 @@
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="4">
         <f>SUM(B44:B52)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
@@ -4615,7 +4615,7 @@
         <v>240</v>
       </c>
       <c r="B57" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D57">
         <f>C57*B57</f>
@@ -4735,7 +4735,7 @@
         <v>116</v>
       </c>
       <c r="B65" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
@@ -4748,7 +4748,7 @@
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="4">
         <f>SUM(B57:B65)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
@@ -4793,7 +4793,7 @@
         <v>240</v>
       </c>
       <c r="B70" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D70">
         <f>C70*B70</f>
@@ -4913,7 +4913,7 @@
         <v>116</v>
       </c>
       <c r="B78" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
@@ -4926,7 +4926,7 @@
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="4">
         <f>SUM(B70:B78)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
@@ -4971,7 +4971,7 @@
         <v>240</v>
       </c>
       <c r="B83" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D83">
         <f>C83*B83</f>
@@ -5091,7 +5091,7 @@
         <v>116</v>
       </c>
       <c r="B91" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
@@ -5104,7 +5104,7 @@
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="4">
         <f>SUM(B83:B91)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
@@ -5149,7 +5149,7 @@
         <v>240</v>
       </c>
       <c r="B96" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D96">
         <f>C96*B96</f>
@@ -5266,7 +5266,7 @@
         <v>116</v>
       </c>
       <c r="B104" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
@@ -5276,7 +5276,7 @@
     <row r="105" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="4">
         <f>SUM(B96:B104)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
@@ -5321,7 +5321,7 @@
         <v>240</v>
       </c>
       <c r="B109" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D109">
         <f>C109*B109</f>
@@ -5438,7 +5438,7 @@
         <v>116</v>
       </c>
       <c r="B117" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
@@ -5451,7 +5451,7 @@
     <row r="118" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
@@ -5589,14 +5589,14 @@
         <v>240</v>
       </c>
       <c r="B5" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
         <f>C5*B5</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>79</v>
@@ -5733,14 +5733,14 @@
         <v>116</v>
       </c>
       <c r="B13" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>14</v>
@@ -5749,7 +5749,7 @@
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <f>SUM(B5:B13)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
@@ -5794,14 +5794,14 @@
         <v>240</v>
       </c>
       <c r="B18" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C18">
         <v>4</v>
       </c>
       <c r="D18">
         <f>C18*B18</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>105</v>
@@ -5938,14 +5938,14 @@
         <v>116</v>
       </c>
       <c r="B26" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>108</v>
@@ -5954,7 +5954,7 @@
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4">
         <f>SUM(B18:B26)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
@@ -5999,14 +5999,14 @@
         <v>240</v>
       </c>
       <c r="B31" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31">
         <f>C31*B31</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>42</v>
@@ -6143,14 +6143,14 @@
         <v>116</v>
       </c>
       <c r="B39" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>16</v>
@@ -6159,7 +6159,7 @@
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4">
         <f>SUM(B31:B39)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
@@ -6204,14 +6204,14 @@
         <v>240</v>
       </c>
       <c r="B44" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C44">
         <v>4</v>
       </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>89</v>
@@ -6348,14 +6348,14 @@
         <v>116</v>
       </c>
       <c r="B52" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C52">
         <v>4</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>89</v>
@@ -6364,7 +6364,7 @@
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="4">
         <f>SUM(B44:B52)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
@@ -6409,14 +6409,14 @@
         <v>240</v>
       </c>
       <c r="B57" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C57">
         <v>4</v>
       </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>16</v>
@@ -6553,14 +6553,14 @@
         <v>116</v>
       </c>
       <c r="B65" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C65">
         <v>4</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>77</v>
@@ -6569,7 +6569,7 @@
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="4">
         <f>SUM(B57:B65)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
@@ -6608,14 +6608,14 @@
         <v>240</v>
       </c>
       <c r="B70" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C70">
         <v>4</v>
       </c>
       <c r="D70">
         <f>C70*B70</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G70" s="7" t="s">
         <v>96</v>
@@ -6749,14 +6749,14 @@
         <v>116</v>
       </c>
       <c r="B78" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C78">
         <v>4</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>103</v>
@@ -6765,7 +6765,7 @@
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="4">
         <f>SUM(B70:B78)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
@@ -6801,14 +6801,14 @@
         <v>240</v>
       </c>
       <c r="B83" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C83">
         <v>4</v>
       </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -6921,20 +6921,20 @@
         <v>116</v>
       </c>
       <c r="B91" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C91">
         <v>4</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="4">
         <f>SUM(B83:B91)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
@@ -6966,14 +6966,14 @@
         <v>240</v>
       </c>
       <c r="B96" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C96">
         <v>4</v>
       </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -7086,20 +7086,20 @@
         <v>116</v>
       </c>
       <c r="B104" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C104">
         <v>4</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="4">
         <f>SUM(B96:B104)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
@@ -7131,14 +7131,14 @@
         <v>240</v>
       </c>
       <c r="B109" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C109">
         <v>4</v>
       </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -7251,20 +7251,20 @@
         <v>116</v>
       </c>
       <c r="B117" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C117">
         <v>4</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
@@ -7335,14 +7335,14 @@
         <v>240</v>
       </c>
       <c r="B5" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5">
         <f>C5*B5</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G5" s="7" t="s">
         <v>183</v>
@@ -7479,14 +7479,14 @@
         <v>116</v>
       </c>
       <c r="B13" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C13">
         <v>4</v>
       </c>
       <c r="D13">
         <f>C13*B13</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>191</v>
@@ -7495,7 +7495,7 @@
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B14" s="4">
         <f>SUM(B5:B13)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D14" s="6">
         <f>SUM(D5:D13)</f>
@@ -7540,14 +7540,14 @@
         <v>240</v>
       </c>
       <c r="B18" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C18">
         <v>4</v>
       </c>
       <c r="D18">
         <f>C18*B18</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G18" s="7" t="s">
         <v>196</v>
@@ -7684,14 +7684,14 @@
         <v>116</v>
       </c>
       <c r="B26" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C26">
         <v>4</v>
       </c>
       <c r="D26">
         <f>C26*B26</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G26" s="7" t="s">
         <v>203</v>
@@ -7700,7 +7700,7 @@
     <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="4">
         <f>SUM(B18:B26)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D27" s="6">
         <f>SUM(D18:D26)</f>
@@ -7745,14 +7745,14 @@
         <v>240</v>
       </c>
       <c r="B31" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C31">
         <v>4</v>
       </c>
       <c r="D31">
         <f>C31*B31</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G31" s="7" t="s">
         <v>207</v>
@@ -7889,14 +7889,14 @@
         <v>116</v>
       </c>
       <c r="B39" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C39">
         <v>4</v>
       </c>
       <c r="D39">
         <f>C39*B39</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G39" s="7" t="s">
         <v>193</v>
@@ -7905,7 +7905,7 @@
     <row r="40" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="4">
         <f>SUM(B31:B39)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(D31:D39)</f>
@@ -7950,14 +7950,14 @@
         <v>240</v>
       </c>
       <c r="B44" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C44">
         <v>4</v>
       </c>
       <c r="D44">
         <f>C44*B44</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>218</v>
@@ -8094,14 +8094,14 @@
         <v>116</v>
       </c>
       <c r="B52" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C52">
         <v>4</v>
       </c>
       <c r="D52">
         <f>C52*B52</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G52" s="7" t="s">
         <v>218</v>
@@ -8110,7 +8110,7 @@
     <row r="53" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="4">
         <f>SUM(B44:B52)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D53" s="6">
         <f>SUM(D44:D52)</f>
@@ -8155,14 +8155,14 @@
         <v>240</v>
       </c>
       <c r="B57" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C57">
         <v>4</v>
       </c>
       <c r="D57">
         <f>C57*B57</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G57" s="7" t="s">
         <v>210</v>
@@ -8299,14 +8299,14 @@
         <v>116</v>
       </c>
       <c r="B65" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C65">
         <v>4</v>
       </c>
       <c r="D65">
         <f>C65*B65</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G65" s="7" t="s">
         <v>229</v>
@@ -8315,7 +8315,7 @@
     <row r="66" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="4">
         <f>SUM(B57:B65)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D66" s="6">
         <f>SUM(D57:D65)</f>
@@ -8360,14 +8360,14 @@
         <v>240</v>
       </c>
       <c r="B70" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C70">
         <v>4</v>
       </c>
       <c r="D70">
         <f>C70*B70</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="G70" s="7"/>
     </row>
@@ -8500,14 +8500,14 @@
         <v>116</v>
       </c>
       <c r="B78" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C78">
         <v>4</v>
       </c>
       <c r="D78">
         <f>C78*B78</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="G78" s="7" t="s">
         <v>235</v>
@@ -8516,7 +8516,7 @@
     <row r="79" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B79" s="4">
         <f>SUM(B70:B78)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D79" s="6">
         <f>SUM(D70:D78)</f>
@@ -8558,14 +8558,14 @@
         <v>240</v>
       </c>
       <c r="B83" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C83">
         <v>4</v>
       </c>
       <c r="D83">
         <f>C83*B83</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
@@ -8678,20 +8678,20 @@
         <v>116</v>
       </c>
       <c r="B91" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C91">
         <v>4</v>
       </c>
       <c r="D91">
         <f>C91*B91</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B92" s="4">
         <f>SUM(B83:B91)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D92" s="6">
         <f>SUM(D83:D91)</f>
@@ -8723,14 +8723,14 @@
         <v>240</v>
       </c>
       <c r="B96" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C96">
         <v>4</v>
       </c>
       <c r="D96">
         <f>C96*B96</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -8843,20 +8843,20 @@
         <v>116</v>
       </c>
       <c r="B104" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C104">
         <v>4</v>
       </c>
       <c r="D104">
         <f>C104*B104</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="4">
         <f>SUM(B96:B104)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D105" s="6">
         <f>SUM(D96:D104)</f>
@@ -8888,14 +8888,14 @@
         <v>240</v>
       </c>
       <c r="B109" s="3">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="C109">
         <v>4</v>
       </c>
       <c r="D109">
         <f>C109*B109</f>
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.3">
@@ -9008,20 +9008,20 @@
         <v>116</v>
       </c>
       <c r="B117" s="3">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="C117">
         <v>4</v>
       </c>
       <c r="D117">
         <f>C117*B117</f>
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B118" s="4">
         <f>SUM(B109:B117)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
       <c r="D118" s="6">
         <f>SUM(D109:D117)</f>
